--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BH18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,6 +727,3304 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Turkish 1 Lig</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Serik Belediyespor</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Van Buyuksehir Belediyespor</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Italian Serie C</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Inter Milan (Res)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>A.C. Trento S.C.S.D.</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Turkish 1 Lig</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>76 Igdir Belediyespor</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Keciorengucu</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Montana</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CSKA Sofia</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Wadi Degla</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pharco FC</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Turkish Super League</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Goztepe</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Turkish 1 Lig</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Umraniyespor</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sakaryaspor</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K8" t="n">
+        <v>950</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>German 3 Liga</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stuttgart II</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SSV Ulm</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>German 3 Liga</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Verl</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Hansa Rostock</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>German 3 Liga</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Wehen Wiesbaden</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TSV Havelse</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K11" t="n">
+        <v>950</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>German 3 Liga</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Saarbrucken</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Alemannia Aachen</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>German 3 Liga</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ingolstadt</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Viktoria Koln</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Botev Plovdiv</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Lokomotiv Plovdiv</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Haras El Hodood</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Modern Sport FC</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ghazl El Mahallah</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>El Gounah</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N17" t="n">
+        <v>8</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="X17" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Paris St-G</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X18" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-04-06 02:33:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>5.1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G11" t="n">
         <v>1.76</v>
@@ -2512,10 +2512,10 @@
         <v>4.3</v>
       </c>
       <c r="I11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K11" t="n">
         <v>950</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="H12" t="n">
         <v>2.72</v>
       </c>
       <c r="I12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G14" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I14" t="n">
         <v>5.7</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q14" t="n">
         <v>2.08</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O17" t="n">
         <v>1.13</v>
@@ -3703,10 +3703,10 @@
         <v>1.41</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S17" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T17" t="n">
         <v>1.54</v>
@@ -3724,16 +3724,16 @@
         <v>40</v>
       </c>
       <c r="Y17" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z17" t="n">
         <v>70</v>
       </c>
       <c r="AA17" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="AB17" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC17" t="n">
         <v>13.5</v>
@@ -3772,13 +3772,13 @@
         <v>4.9</v>
       </c>
       <c r="AO17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP17" t="n">
         <v>34</v>
       </c>
       <c r="AQ17" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3820,17 +3820,17 @@
         <v>19.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG17" t="n">
         <v>24</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G18" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I18" t="n">
         <v>4.8</v>
       </c>
       <c r="J18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K18" t="n">
         <v>4.5</v>
@@ -3882,10 +3882,10 @@
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O18" t="n">
         <v>1.17</v>
@@ -3900,7 +3900,7 @@
         <v>1.73</v>
       </c>
       <c r="S18" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T18" t="n">
         <v>1.57</v>
@@ -3912,19 +3912,19 @@
         <v>1.26</v>
       </c>
       <c r="W18" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X18" t="n">
         <v>27</v>
       </c>
       <c r="Y18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA18" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB18" t="n">
         <v>14.5</v>
@@ -3933,10 +3933,10 @@
         <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF18" t="n">
         <v>14</v>
@@ -3948,13 +3948,13 @@
         <v>15.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK18" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL18" t="n">
         <v>25</v>
@@ -3963,34 +3963,34 @@
         <v>60</v>
       </c>
       <c r="AN18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP18" t="n">
         <v>24</v>
       </c>
       <c r="AQ18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS18" t="n">
         <v>55</v>
       </c>
       <c r="AT18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU18" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX18" t="n">
         <v>13</v>
@@ -4002,10 +4002,10 @@
         <v>15</v>
       </c>
       <c r="BA18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB18" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC18" t="n">
         <v>14.5</v>
@@ -4014,17 +4014,17 @@
         <v>23</v>
       </c>
       <c r="BE18" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 02:33:27</t>
+          <t>2026-04-06 04:52:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
         <v>2.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>1.27</v>
       </c>
       <c r="I5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="J5" t="n">
         <v>5.4</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G6" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I6" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J6" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1566,7 +1566,7 @@
         <v>1.37</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1730,19 @@
         <v>5.5</v>
       </c>
       <c r="G7" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="H7" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="I7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="J7" t="n">
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -1924,19 +1924,19 @@
         <v>2.04</v>
       </c>
       <c r="G8" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="G10" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="H10" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G11" t="n">
         <v>1.76</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>5.8</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="H12" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -2894,19 +2894,19 @@
         <v>2.24</v>
       </c>
       <c r="G13" t="n">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="H13" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="I13" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G14" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I14" t="n">
         <v>5.7</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q14" t="n">
         <v>2.08</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G17" t="n">
         <v>1.57</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.58</v>
       </c>
       <c r="H17" t="n">
         <v>5.6</v>
@@ -3679,19 +3679,19 @@
         <v>5.8</v>
       </c>
       <c r="J17" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="K17" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
         <v>1.13</v>
@@ -3703,10 +3703,10 @@
         <v>1.41</v>
       </c>
       <c r="R17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S17" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T17" t="n">
         <v>1.54</v>
@@ -3718,7 +3718,7 @@
         <v>1.2</v>
       </c>
       <c r="W17" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="X17" t="n">
         <v>40</v>
@@ -3727,16 +3727,16 @@
         <v>34</v>
       </c>
       <c r="Z17" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AA17" t="n">
         <v>130</v>
       </c>
       <c r="AB17" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD17" t="n">
         <v>23</v>
@@ -3760,7 +3760,7 @@
         <v>17</v>
       </c>
       <c r="AK17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AL17" t="n">
         <v>23</v>
@@ -3769,10 +3769,10 @@
         <v>70</v>
       </c>
       <c r="AN17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP17" t="n">
         <v>34</v>
@@ -3808,7 +3808,7 @@
         <v>15.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="BB17" t="n">
         <v>15</v>
@@ -3820,7 +3820,7 @@
         <v>19.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="BF17" t="n">
         <v>4.6</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G18" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J18" t="n">
         <v>4.3</v>
@@ -3885,7 +3885,7 @@
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O18" t="n">
         <v>1.17</v>
@@ -3909,10 +3909,10 @@
         <v>2.64</v>
       </c>
       <c r="V18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W18" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="X18" t="n">
         <v>27</v>
@@ -3936,7 +3936,7 @@
         <v>18.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF18" t="n">
         <v>14</v>
@@ -3951,7 +3951,7 @@
         <v>44</v>
       </c>
       <c r="AJ18" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK18" t="n">
         <v>16</v>
@@ -3969,7 +3969,7 @@
         <v>34</v>
       </c>
       <c r="AP18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ18" t="n">
         <v>22</v>
@@ -3990,7 +3990,7 @@
         <v>17</v>
       </c>
       <c r="AW18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX18" t="n">
         <v>13</v>
@@ -4002,10 +4002,10 @@
         <v>15</v>
       </c>
       <c r="BA18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB18" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC18" t="n">
         <v>14.5</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 04:52:09</t>
+          <t>2026-04-06 07:11:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="G2" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="I2" t="n">
-        <v>2.78</v>
+        <v>2.28</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
         <v>1.84</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>2.1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="n">
         <v>3.25</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G6" t="n">
         <v>1.98</v>
@@ -1566,7 +1566,7 @@
         <v>1.37</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
         <v>2.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
         <v>4.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
         <v>4.7</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -2312,10 +2312,10 @@
         <v>2.14</v>
       </c>
       <c r="G10" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I10" t="n">
         <v>3.75</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G11" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="H11" t="n">
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K11" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -2700,13 +2700,13 @@
         <v>2.22</v>
       </c>
       <c r="G12" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="H12" t="n">
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="J12" t="n">
         <v>3.45</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>2.86</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="J13" t="n">
         <v>3.7</v>
@@ -2924,7 +2924,7 @@
         <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -3282,10 +3282,10 @@
         <v>4.5</v>
       </c>
       <c r="G15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H15" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="I15" t="n">
         <v>2.28</v>
@@ -3294,7 +3294,7 @@
         <v>2.66</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
         <v>2.42</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="G17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H17" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I17" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K17" t="n">
         <v>5.4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>5.5</v>
       </c>
       <c r="L17" t="n">
         <v>1.19</v>
@@ -3697,16 +3697,16 @@
         <v>1.13</v>
       </c>
       <c r="P17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R17" t="n">
         <v>1.9</v>
       </c>
       <c r="S17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T17" t="n">
         <v>1.54</v>
@@ -3715,10 +3715,10 @@
         <v>2.74</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W17" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="X17" t="n">
         <v>40</v>
@@ -3727,13 +3727,13 @@
         <v>34</v>
       </c>
       <c r="Z17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA17" t="n">
         <v>130</v>
       </c>
       <c r="AB17" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC17" t="n">
         <v>13</v>
@@ -3751,7 +3751,7 @@
         <v>10.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI17" t="n">
         <v>48</v>
@@ -3760,7 +3760,7 @@
         <v>17</v>
       </c>
       <c r="AK17" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AL17" t="n">
         <v>23</v>
@@ -3769,19 +3769,19 @@
         <v>70</v>
       </c>
       <c r="AN17" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AO17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP17" t="n">
         <v>34</v>
       </c>
       <c r="AQ17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR17" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="AS17" t="n">
         <v>42</v>
@@ -3790,25 +3790,25 @@
         <v>14</v>
       </c>
       <c r="AU17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW17" t="n">
         <v>29</v>
       </c>
       <c r="AX17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
         <v>15.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BB17" t="n">
         <v>15</v>
@@ -3820,17 +3820,17 @@
         <v>19.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG17" t="n">
         <v>24</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G18" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H18" t="n">
         <v>4.5</v>
       </c>
       <c r="I18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J18" t="n">
         <v>4.3</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3891,10 +3891,10 @@
         <v>1.17</v>
       </c>
       <c r="P18" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R18" t="n">
         <v>1.73</v>
@@ -3906,13 +3906,13 @@
         <v>1.57</v>
       </c>
       <c r="U18" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V18" t="n">
         <v>1.27</v>
       </c>
       <c r="W18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X18" t="n">
         <v>27</v>
@@ -3924,7 +3924,7 @@
         <v>40</v>
       </c>
       <c r="AA18" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB18" t="n">
         <v>14.5</v>
@@ -3933,10 +3933,10 @@
         <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AF18" t="n">
         <v>14</v>
@@ -3951,7 +3951,7 @@
         <v>44</v>
       </c>
       <c r="AJ18" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK18" t="n">
         <v>16</v>
@@ -3969,13 +3969,13 @@
         <v>34</v>
       </c>
       <c r="AP18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ18" t="n">
         <v>22</v>
       </c>
       <c r="AR18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS18" t="n">
         <v>55</v>
@@ -3987,10 +3987,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV18" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AX18" t="n">
         <v>13</v>
@@ -3999,13 +3999,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB18" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC18" t="n">
         <v>14.5</v>
@@ -4020,11 +4020,11 @@
         <v>6.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 07:11:44</t>
+          <t>2026-04-06 09:33:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH18"/>
+  <dimension ref="A1:BH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,22 +787,22 @@
         <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q2" t="n">
         <v>1.84</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
         <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
         <v>1.78</v>
@@ -814,7 +814,7 @@
         <v>18.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
         <v>17</v>
@@ -829,10 +829,10 @@
         <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AF2" t="n">
         <v>36</v>
@@ -859,7 +859,7 @@
         <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO2" t="n">
         <v>18.5</v>
@@ -868,34 +868,34 @@
         <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
         <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
         <v>1.03</v>
@@ -913,21 +913,21 @@
         <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BG2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -942,186 +942,186 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Inter Milan (Res)</t>
+          <t>Athlitiki Enosi Larissa</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A.C. Trento S.C.S.D.</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>76 Igdir Belediyespor</t>
+          <t>Inter Milan (Res)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Keciorengucu</t>
+          <t>A.C. Trento S.C.S.D.</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.1</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>1.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>3.15</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>3.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.27</v>
+        <v>2.54</v>
       </c>
       <c r="I5" t="n">
-        <v>1.32</v>
+        <v>2.68</v>
       </c>
       <c r="J5" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU5" t="n">
         <v>6.4</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>76 Igdir Belediyespor</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>Keciorengucu</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="I6" t="n">
-        <v>19</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>1.37</v>
+        <v>2.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.68</v>
+        <v>1.71</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Goztepe</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5.5</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="I7" t="n">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,36 +1907,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Umraniyespor</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.04</v>
+        <v>1.64</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="H8" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.72</v>
+        <v>2.68</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SSV Ulm</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="G9" t="n">
-        <v>2.36</v>
+        <v>110</v>
       </c>
       <c r="H9" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="I9" t="n">
-        <v>3.75</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P9" t="n">
-        <v>2.46</v>
+        <v>1.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.49</v>
+        <v>1.98</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,49 +2300,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Goztepe</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>2.14</v>
       </c>
-      <c r="G10" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.18</v>
-      </c>
       <c r="Q10" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Umraniyespor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TSV Havelse</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.59</v>
+        <v>2.04</v>
       </c>
       <c r="G11" t="n">
-        <v>1.78</v>
+        <v>2.42</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="I11" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>SSV Ulm</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="G12" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.08</v>
+        <v>2.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
@@ -2882,31 +2882,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Viktoria Koln</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G13" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="H13" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>TSV Havelse</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.89</v>
+        <v>1.59</v>
       </c>
       <c r="G14" t="n">
-        <v>2.16</v>
+        <v>1.78</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="K14" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,33 +3265,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Viktoria Koln</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.5</v>
+        <v>2.24</v>
       </c>
       <c r="G15" t="n">
-        <v>7.6</v>
+        <v>2.52</v>
       </c>
       <c r="H15" t="n">
-        <v>1.85</v>
+        <v>2.86</v>
       </c>
       <c r="I15" t="n">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="J15" t="n">
-        <v>2.66</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
         <v>4.3</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.43</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.84</v>
+        <v>1.61</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,36 +3459,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.94</v>
+        <v>2.14</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>2.42</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="I16" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="J16" t="n">
-        <v>2.42</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.05</v>
+        <v>1.52</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,378 +3653,960 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="G17" t="n">
-        <v>1.58</v>
+        <v>2.16</v>
       </c>
       <c r="H17" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="n">
         <v>5.7</v>
       </c>
       <c r="J17" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>5.4</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.2</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.42</v>
+        <v>2.08</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 09:33:34</t>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Haras El Hodood</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Modern Sport FC</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-04-06 11:50:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ghazl El Mahallah</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>El Gounah</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-04-06 11:50:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>UEFA Champions League</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>16:00:00</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="X20" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-06 11:50:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Paris St-G</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Liverpool</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G21" t="n">
         <v>1.82</v>
       </c>
-      <c r="G18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H18" t="n">
+      <c r="H21" t="n">
         <v>4.5</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I21" t="n">
         <v>4.6</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J21" t="n">
         <v>4.3</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K21" t="n">
         <v>4.4</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L21" t="n">
         <v>1.01</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M21" t="n">
         <v>1.04</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N21" t="n">
         <v>6.4</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O21" t="n">
         <v>1.17</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="P21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.73</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S21" t="n">
         <v>2.3</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T21" t="n">
         <v>1.57</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U21" t="n">
         <v>2.66</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V21" t="n">
         <v>1.27</v>
       </c>
-      <c r="W18" t="n">
+      <c r="W21" t="n">
         <v>2.2</v>
       </c>
-      <c r="X18" t="n">
+      <c r="X21" t="n">
         <v>27</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y21" t="n">
         <v>25</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="Z21" t="n">
         <v>40</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AA21" t="n">
         <v>90</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AB21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD18" t="n">
+      <c r="BA21" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB21" t="n">
         <v>18</v>
       </c>
-      <c r="AE18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ18" t="n">
+      <c r="BC21" t="n">
         <v>14.5</v>
       </c>
-      <c r="BA18" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD18" t="n">
+      <c r="BD21" t="n">
         <v>23</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BE21" t="n">
         <v>50</v>
       </c>
-      <c r="BF18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG18" t="n">
+      <c r="BF21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG21" t="n">
         <v>29</v>
       </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>2026-04-06 09:33:34</t>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-06 11:50:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BH30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I2" t="n">
         <v>2.28</v>
@@ -775,13 +775,13 @@
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
         <v>1.28</v>
@@ -823,7 +823,7 @@
         <v>34</v>
       </c>
       <c r="AB2" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AC2" t="n">
         <v>9.6</v>
@@ -841,7 +841,7 @@
         <v>20</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AI2" t="n">
         <v>42</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>1.46</v>
@@ -981,10 +981,10 @@
         <v>1.46</v>
       </c>
       <c r="P3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="R3" t="n">
         <v>1.21</v>
@@ -1086,7 +1086,7 @@
         <v>11</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
         <v>19.5</v>
@@ -1101,7 +1101,7 @@
         <v>5.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE3" t="n">
         <v>6.2</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -1169,13 +1169,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="O4" t="n">
         <v>1.33</v>
       </c>
       <c r="P4" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q4" t="n">
         <v>1.33</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="G5" t="n">
         <v>3.2</v>
@@ -1348,13 +1348,13 @@
         <v>2.54</v>
       </c>
       <c r="I5" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
         <v>1.46</v>
@@ -1363,37 +1363,37 @@
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O5" t="n">
         <v>1.48</v>
       </c>
       <c r="P5" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.69</v>
+        <v>2.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V5" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="W5" t="n">
         <v>1.45</v>
       </c>
       <c r="X5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="n">
         <v>9.4</v>
@@ -1405,7 +1405,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC5" t="n">
         <v>8.4</v>
@@ -1447,19 +1447,19 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.55</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.5</v>
+        <v>4.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
@@ -1468,41 +1468,41 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX5" t="n">
-        <v>17</v>
+        <v>4.8</v>
       </c>
       <c r="AY5" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -1545,22 +1545,22 @@
         <v>4.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K6" t="n">
         <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
         <v>2.18</v>
@@ -1569,118 +1569,118 @@
         <v>1.71</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>1.95</v>
+        <v>2.78</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AS6" t="n">
         <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
         <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA6" t="n">
         <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BD6" t="n">
         <v>1.03</v>
@@ -1689,14 +1689,14 @@
         <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="H7" t="n">
         <v>1.27</v>
@@ -1745,152 +1745,152 @@
         <v>6.4</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
         <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
@@ -1921,177 +1921,177 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="G8" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S8" t="n">
         <v>5.5</v>
       </c>
-      <c r="I8" t="n">
-        <v>19</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="T8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC8" t="n">
         <v>4.9</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Greek Super League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,60 +2101,60 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>FK Backa Topola</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>FK IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7</v>
+        <v>1.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.98</v>
+        <v>1.34</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>1.34</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2163,16 +2163,16 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2181,10 +2181,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2193,10 +2193,10 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
         <v>1000</v>
@@ -2214,7 +2214,7 @@
         <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
         <v>1000</v>
@@ -2223,69 +2223,69 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:55:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Goztepe</t>
+          <t>Al-Feiha</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="G10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD10" t="n">
         <v>5.9</v>
       </c>
-      <c r="H10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Umraniyespor</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2.42</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SSV Ulm</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.32</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P12" t="n">
-        <v>2.46</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.49</v>
+        <v>1.08</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="G13" t="n">
-        <v>2.66</v>
+        <v>2.26</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="I13" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="K13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS13" t="n">
         <v>4.1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TSV Havelse</t>
+          <t>Radnicki Nis</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.59</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>1.78</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Viktoria Koln</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="G15" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="H15" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.61</v>
+        <v>2.06</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,49 +3464,49 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Goztepe</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.14</v>
       </c>
-      <c r="G16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Q16" t="n">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,36 +3653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Umraniyespor</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="G17" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="I17" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.08</v>
+        <v>1.72</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,36 +3847,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>FK Napredak</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>2.28</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>2.66</v>
+        <v>1.03</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.43</v>
+        <v>1.07</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,36 +4041,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>SSV Ulm</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.94</v>
+        <v>2.08</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>2.32</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="I19" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="J19" t="n">
-        <v>2.42</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.38</v>
+        <v>2.46</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.05</v>
+        <v>1.49</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,378 +4235,2124 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Viktoria Koln</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.57</v>
+        <v>2.24</v>
       </c>
       <c r="G20" t="n">
-        <v>1.58</v>
+        <v>2.52</v>
       </c>
       <c r="H20" t="n">
-        <v>5.6</v>
+        <v>2.86</v>
       </c>
       <c r="I20" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="J20" t="n">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="R20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-06 11:50:08</t>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>German 3 Liga</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Wehen Wiesbaden</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TSV Havelse</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:02:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>German 3 Liga</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Saarbrucken</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Alemannia Aachen</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:02:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>German 3 Liga</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Verl</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Hansa Rostock</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:02:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Botev Plovdiv</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Lokomotiv Plovdiv</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:02:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Haras El Hodood</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Modern Sport FC</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:02:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ghazl El Mahallah</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>El Gounah</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:02:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Al-Ittihad</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NEOM Sports Club</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:02:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Al-Hilal</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Al-Kholood Club</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H28" t="n">
+        <v>14</v>
+      </c>
+      <c r="I28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="X28" t="n">
+        <v>65</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>190</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>220</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:02:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>UEFA Champions League</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>16:00:00</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N29" t="n">
+        <v>8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="X29" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>34</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:02:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Paris St-G</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Liverpool</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F30" t="n">
         <v>1.8</v>
       </c>
-      <c r="G21" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="H21" t="n">
+      <c r="G30" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H30" t="n">
         <v>4.5</v>
       </c>
-      <c r="I21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="I30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J30" t="n">
         <v>4.3</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K30" t="n">
         <v>4.4</v>
       </c>
-      <c r="L21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="L30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M30" t="n">
         <v>1.04</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N30" t="n">
         <v>6.4</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O30" t="n">
         <v>1.17</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P30" t="n">
         <v>2.78</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q30" t="n">
         <v>1.53</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R30" t="n">
         <v>1.73</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S30" t="n">
         <v>2.3</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T30" t="n">
         <v>1.57</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U30" t="n">
         <v>2.66</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V30" t="n">
         <v>1.27</v>
       </c>
-      <c r="W21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X21" t="n">
+      <c r="W30" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X30" t="n">
         <v>27</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Y30" t="n">
         <v>25</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="Z30" t="n">
         <v>40</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AA30" t="n">
         <v>90</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AB30" t="n">
         <v>15</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AC30" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AD30" t="n">
         <v>18.5</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AE30" t="n">
         <v>44</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AF30" t="n">
         <v>14</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AG30" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AH30" t="n">
         <v>15.5</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AI30" t="n">
         <v>44</v>
       </c>
-      <c r="AJ21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK21" t="n">
+      <c r="AJ30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK30" t="n">
         <v>16</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AL30" t="n">
         <v>25</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AM30" t="n">
         <v>60</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AN30" t="n">
         <v>6.8</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AO30" t="n">
         <v>32</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AP30" t="n">
         <v>24</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AQ30" t="n">
         <v>22</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="AR30" t="n">
         <v>34</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="AS30" t="n">
         <v>60</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="AT30" t="n">
         <v>14</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="AU30" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="AV30" t="n">
         <v>16.5</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="AW30" t="n">
         <v>38</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="AX30" t="n">
         <v>13</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="AY30" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="AZ30" t="n">
         <v>14.5</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BA30" t="n">
         <v>38</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BB30" t="n">
         <v>18</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BC30" t="n">
         <v>14.5</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BD30" t="n">
         <v>23</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BE30" t="n">
         <v>50</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BF30" t="n">
         <v>6.2</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BG30" t="n">
         <v>29</v>
       </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>2026-04-06 11:50:08</t>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-06 14:02:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G2" t="n">
         <v>4.3</v>
@@ -835,7 +835,7 @@
         <v>24</v>
       </c>
       <c r="AF2" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AG2" t="n">
         <v>20</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
@@ -984,7 +984,7 @@
         <v>1.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="R3" t="n">
         <v>1.21</v>
@@ -999,7 +999,7 @@
         <v>1.82</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
         <v>1.72</v>
@@ -1008,10 +1008,10 @@
         <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1032,10 +1032,10 @@
         <v>13.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1068,7 +1068,7 @@
         <v>21</v>
       </c>
       <c r="AS3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT3" t="n">
         <v>6.4</v>
@@ -1080,7 +1080,7 @@
         <v>13.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AX3" t="n">
         <v>11</v>
@@ -1092,29 +1092,29 @@
         <v>19.5</v>
       </c>
       <c r="BA3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF3" t="n">
         <v>6</v>
       </c>
-      <c r="BB3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BG3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -1169,13 +1169,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="O4" t="n">
         <v>1.33</v>
       </c>
       <c r="P4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q4" t="n">
         <v>1.33</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -1468,10 +1468,10 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AY5" t="n">
         <v>11.5</v>
@@ -1480,16 +1480,16 @@
         <v>4.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC5" t="n">
         <v>5.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE5" t="n">
         <v>5.8</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
         <v>3.25</v>
@@ -1581,10 +1581,10 @@
         <v>2.32</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="X6" t="n">
         <v>22</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="G7" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="I7" t="n">
         <v>1.32</v>
@@ -1742,31 +1742,31 @@
         <v>5.4</v>
       </c>
       <c r="K7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
         <v>2.5</v>
@@ -1784,37 +1784,37 @@
         <v>17.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AA7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AB7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH7" t="n">
         <v>46</v>
       </c>
-      <c r="AC7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>55</v>
-      </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
         <v>1000</v>
@@ -1832,7 +1832,7 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AP7" t="n">
         <v>14</v>
@@ -1847,7 +1847,7 @@
         <v>8</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
         <v>11.5</v>
@@ -1859,38 +1859,38 @@
         <v>14</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G8" t="n">
         <v>1.9</v>
@@ -1945,22 +1945,22 @@
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="O8" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="P8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R8" t="n">
         <v>1.16</v>
       </c>
       <c r="S8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T8" t="n">
         <v>2.4</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I10" t="n">
         <v>1.58</v>
@@ -2351,22 +2351,22 @@
         <v>2.84</v>
       </c>
       <c r="T10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U10" t="n">
         <v>1.92</v>
       </c>
       <c r="V10" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="W10" t="n">
         <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z10" t="n">
         <v>10.5</v>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
@@ -2423,56 +2423,56 @@
         <v>7.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.95</v>
+        <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AV10" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AW10" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AX10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA10" t="n">
         <v>5.8</v>
       </c>
-      <c r="AY10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BB10" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG10" t="n">
         <v>5.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
         <v>1.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R13" t="n">
         <v>1.26</v>
@@ -2939,10 +2939,10 @@
         <v>1.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X13" t="n">
         <v>14</v>
@@ -2960,7 +2960,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD13" t="n">
         <v>21</v>
@@ -2999,10 +2999,10 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.35</v>
+        <v>9.6</v>
       </c>
       <c r="AR13" t="n">
         <v>21</v>
@@ -3032,7 +3032,7 @@
         <v>3.65</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BB13" t="n">
         <v>3.8</v>
@@ -3041,20 +3041,20 @@
         <v>18</v>
       </c>
       <c r="BD13" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF13" t="n">
         <v>15</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -3279,28 +3279,28 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G15" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H15" t="n">
         <v>2.92</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K15" t="n">
         <v>3.5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.55</v>
       </c>
       <c r="L15" t="n">
         <v>1.41</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
         <v>3.7</v>
@@ -3327,16 +3327,16 @@
         <v>2.14</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X15" t="n">
         <v>14</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z15" t="n">
         <v>20</v>
@@ -3378,7 +3378,7 @@
         <v>44</v>
       </c>
       <c r="AM15" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
         <v>26</v>
@@ -3399,13 +3399,13 @@
         <v>38</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU15" t="n">
         <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW15" t="n">
         <v>21</v>
@@ -3426,7 +3426,7 @@
         <v>23</v>
       </c>
       <c r="BC15" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD15" t="n">
         <v>34</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -3491,16 +3491,16 @@
         <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P16" t="n">
         <v>2.14</v>
@@ -3509,134 +3509,134 @@
         <v>1.74</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -3670,10 +3670,10 @@
         <v>2.04</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
         <v>4.4</v>
@@ -3685,152 +3685,152 @@
         <v>4.7</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -3879,152 +3879,152 @@
         <v>950</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -4073,16 +4073,16 @@
         <v>4.4</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P19" t="n">
         <v>2.46</v>
@@ -4091,134 +4091,134 @@
         <v>1.49</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G20" t="n">
         <v>2.52</v>
@@ -4267,16 +4267,16 @@
         <v>4.3</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P20" t="n">
         <v>2.32</v>
@@ -4285,134 +4285,134 @@
         <v>1.61</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G22" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="I22" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J22" t="n">
         <v>3.45</v>
@@ -4655,152 +4655,152 @@
         <v>4.1</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P22" t="n">
         <v>2.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -4834,13 +4834,13 @@
         <v>2.14</v>
       </c>
       <c r="G23" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H23" t="n">
         <v>3.1</v>
       </c>
       <c r="I23" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="J23" t="n">
         <v>3.8</v>
@@ -4849,16 +4849,16 @@
         <v>4.3</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P23" t="n">
         <v>2.4</v>
@@ -4867,134 +4867,134 @@
         <v>1.52</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -5028,167 +5028,167 @@
         <v>1.89</v>
       </c>
       <c r="G24" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H24" t="n">
         <v>4.3</v>
       </c>
       <c r="I24" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J24" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K24" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P24" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -5222,10 +5222,10 @@
         <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="I25" t="n">
         <v>2.12</v>
@@ -5237,16 +5237,16 @@
         <v>3.45</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="P25" t="n">
         <v>1.43</v>
@@ -5255,134 +5255,134 @@
         <v>2.84</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -5422,25 +5422,25 @@
         <v>2.7</v>
       </c>
       <c r="I26" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J26" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="K26" t="n">
         <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="P26" t="n">
         <v>1.38</v>
@@ -5449,134 +5449,134 @@
         <v>3.05</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N27" t="n">
         <v>2.36</v>
@@ -5715,52 +5715,52 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
         <v>1.01</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -5801,19 +5801,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="G28" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="H28" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="I28" t="n">
-        <v>17.5</v>
+        <v>32</v>
       </c>
       <c r="J28" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K28" t="n">
         <v>10.5</v>
@@ -5825,19 +5825,19 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O28" t="n">
         <v>1.09</v>
       </c>
       <c r="P28" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q28" t="n">
         <v>1.28</v>
       </c>
       <c r="R28" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S28" t="n">
         <v>1.72</v>
@@ -5849,19 +5849,19 @@
         <v>2.02</v>
       </c>
       <c r="V28" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="X28" t="n">
         <v>65</v>
       </c>
       <c r="Y28" t="n">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="Z28" t="n">
-        <v>190</v>
+        <v>310</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
@@ -5873,10 +5873,10 @@
         <v>25</v>
       </c>
       <c r="AD28" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AE28" t="n">
-        <v>220</v>
+        <v>350</v>
       </c>
       <c r="AF28" t="n">
         <v>12</v>
@@ -5888,10 +5888,10 @@
         <v>36</v>
       </c>
       <c r="AI28" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK28" t="n">
         <v>15</v>
@@ -5906,31 +5906,31 @@
         <v>2.92</v>
       </c>
       <c r="AO28" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="AP28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AS28" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AT28" t="n">
         <v>13.5</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX28" t="n">
         <v>9.6</v>
@@ -5939,10 +5939,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BA28" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB28" t="n">
         <v>9</v>
@@ -5951,20 +5951,20 @@
         <v>11</v>
       </c>
       <c r="BD28" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE28" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>7.4</v>
       </c>
       <c r="BF28" t="n">
         <v>2.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G29" t="n">
         <v>1.59</v>
@@ -6013,7 +6013,7 @@
         <v>5.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="M29" t="n">
         <v>1.02</v>
@@ -6049,7 +6049,7 @@
         <v>2.72</v>
       </c>
       <c r="X29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y29" t="n">
         <v>34</v>
@@ -6067,19 +6067,19 @@
         <v>13</v>
       </c>
       <c r="AD29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE29" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF29" t="n">
         <v>14</v>
       </c>
       <c r="AG29" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH29" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI29" t="n">
         <v>48</v>
@@ -6091,40 +6091,40 @@
         <v>13.5</v>
       </c>
       <c r="AL29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM29" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AN29" t="n">
         <v>5.1</v>
       </c>
       <c r="AO29" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP29" t="n">
         <v>34</v>
       </c>
       <c r="AQ29" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AR29" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AS29" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AT29" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU29" t="n">
         <v>11.5</v>
       </c>
       <c r="AV29" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW29" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AX29" t="n">
         <v>12</v>
@@ -6136,10 +6136,10 @@
         <v>16</v>
       </c>
       <c r="BA29" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BB29" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC29" t="n">
         <v>13</v>
@@ -6148,17 +6148,17 @@
         <v>19.5</v>
       </c>
       <c r="BE29" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF29" t="n">
         <v>4.7</v>
       </c>
       <c r="BG29" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G30" t="n">
         <v>1.8</v>
       </c>
-      <c r="G30" t="n">
-        <v>1.81</v>
-      </c>
       <c r="H30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J30" t="n">
         <v>4.3</v>
@@ -6207,7 +6207,7 @@
         <v>4.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="M30" t="n">
         <v>1.04</v>
@@ -6225,10 +6225,10 @@
         <v>1.53</v>
       </c>
       <c r="R30" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S30" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T30" t="n">
         <v>1.57</v>
@@ -6237,13 +6237,13 @@
         <v>2.66</v>
       </c>
       <c r="V30" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W30" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y30" t="n">
         <v>25</v>
@@ -6255,13 +6255,13 @@
         <v>90</v>
       </c>
       <c r="AB30" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC30" t="n">
         <v>10.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE30" t="n">
         <v>44</v>
@@ -6270,7 +6270,7 @@
         <v>14</v>
       </c>
       <c r="AG30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH30" t="n">
         <v>15.5</v>
@@ -6279,13 +6279,13 @@
         <v>44</v>
       </c>
       <c r="AJ30" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK30" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM30" t="n">
         <v>60</v>
@@ -6300,25 +6300,25 @@
         <v>24</v>
       </c>
       <c r="AQ30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AR30" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AS30" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU30" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV30" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW30" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX30" t="n">
         <v>13</v>
@@ -6330,10 +6330,10 @@
         <v>14.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB30" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC30" t="n">
         <v>14.5</v>
@@ -6345,14 +6345,14 @@
         <v>50</v>
       </c>
       <c r="BF30" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG30" t="n">
         <v>29</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-06 14:02:57</t>
+          <t>2026-04-06 16:14:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -966,10 +966,10 @@
         <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
@@ -1059,7 +1059,7 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>9.199999999999999</v>
@@ -1074,7 +1074,7 @@
         <v>6.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
         <v>13.5</v>
@@ -1107,14 +1107,14 @@
         <v>7.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG3" t="n">
         <v>6.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -1169,13 +1169,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="O4" t="n">
         <v>1.33</v>
       </c>
       <c r="P4" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
         <v>1.33</v>
@@ -1184,7 +1184,7 @@
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
         <v>8.4</v>
@@ -1417,10 +1417,10 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG5" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
         <v>25</v>
@@ -1429,7 +1429,7 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="n">
         <v>1000</v>
@@ -1453,10 +1453,10 @@
         <v>7.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AT5" t="n">
         <v>8.199999999999999</v>
@@ -1468,41 +1468,41 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AY5" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BA5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG5" t="n">
         <v>5.5</v>
       </c>
-      <c r="BB5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -1581,10 +1581,10 @@
         <v>2.32</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="X6" t="n">
         <v>22</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
         <v>7</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AB7" t="n">
         <v>44</v>
@@ -1832,7 +1832,7 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AP7" t="n">
         <v>14</v>
@@ -1847,7 +1847,7 @@
         <v>8</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AU7" t="n">
         <v>11.5</v>
@@ -1859,38 +1859,38 @@
         <v>14</v>
       </c>
       <c r="AX7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB7" t="n">
         <v>7</v>
       </c>
-      <c r="AY7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BC7" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BG7" t="n">
         <v>5.7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -1948,19 +1948,19 @@
         <v>2.42</v>
       </c>
       <c r="O8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="P8" t="n">
         <v>1.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="R8" t="n">
         <v>1.16</v>
       </c>
       <c r="S8" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="T8" t="n">
         <v>2.4</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>3.9</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
         <v>3.2</v>
@@ -2924,7 +2924,7 @@
         <v>1.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="R13" t="n">
         <v>1.26</v>
@@ -2939,7 +2939,7 @@
         <v>1.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
         <v>1.8</v>
@@ -2999,16 +2999,16 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.6</v>
+        <v>3.45</v>
       </c>
       <c r="AR13" t="n">
-        <v>21</v>
+        <v>3.9</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
@@ -3017,44 +3017,44 @@
         <v>6.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AW13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.199999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BA13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BC13" t="n">
-        <v>18</v>
+        <v>3.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF13" t="n">
         <v>15</v>
       </c>
       <c r="BG13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>2.64</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H15" t="n">
         <v>2.92</v>
       </c>
       <c r="I15" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>3.45</v>
@@ -3297,19 +3297,19 @@
         <v>3.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O15" t="n">
         <v>1.35</v>
       </c>
       <c r="P15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q15" t="n">
         <v>2.06</v>
@@ -3324,10 +3324,10 @@
         <v>1.81</v>
       </c>
       <c r="U15" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W15" t="n">
         <v>1.58</v>
@@ -3378,7 +3378,7 @@
         <v>44</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN15" t="n">
         <v>26</v>
@@ -3390,13 +3390,13 @@
         <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR15" t="n">
         <v>16.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AT15" t="n">
         <v>9.6</v>
@@ -3411,10 +3411,10 @@
         <v>21</v>
       </c>
       <c r="AX15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15" t="n">
         <v>15.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -3479,10 +3479,10 @@
         <v>5.7</v>
       </c>
       <c r="H16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="I16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="J16" t="n">
         <v>4</v>
@@ -3497,10 +3497,10 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>2.28</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
         <v>2.14</v>
@@ -3521,7 +3521,7 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="W16" t="n">
         <v>1.21</v>
@@ -3530,113 +3530,113 @@
         <v>1000</v>
       </c>
       <c r="Y16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW16" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AX16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>16</v>
       </c>
-      <c r="AA16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>95</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>2.56</v>
-      </c>
       <c r="BA16" t="n">
-        <v>2.66</v>
+        <v>23</v>
       </c>
       <c r="BB16" t="n">
-        <v>2.82</v>
+        <v>8</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.74</v>
+        <v>7.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.74</v>
+        <v>7.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.82</v>
+        <v>7.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.74</v>
+        <v>7.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -3697,10 +3697,10 @@
         <v>1.26</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="R17" t="n">
         <v>1.25</v>
@@ -3718,7 +3718,7 @@
         <v>1.29</v>
       </c>
       <c r="W17" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4163,7 @@
         <v>34</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="AQ19" t="n">
         <v>11.5</v>
@@ -4172,7 +4172,7 @@
         <v>16.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AT19" t="n">
         <v>8.4</v>
@@ -4184,7 +4184,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="AX19" t="n">
         <v>10</v>
@@ -4196,7 +4196,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="BB19" t="n">
         <v>16.5</v>
@@ -4208,7 +4208,7 @@
         <v>16.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="BF19" t="n">
         <v>6.6</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G20" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="H20" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="I20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J20" t="n">
         <v>3.7</v>
@@ -4300,7 +4300,7 @@
         <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>2.26</v>
       </c>
       <c r="G22" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="H22" t="n">
         <v>2.92</v>
       </c>
       <c r="I22" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="J22" t="n">
         <v>3.45</v>
@@ -4685,10 +4685,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W22" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
         <v>3.1</v>
       </c>
       <c r="I23" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J23" t="n">
         <v>3.8</v>
@@ -4870,7 +4870,7 @@
         <v>1.56</v>
       </c>
       <c r="S23" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="T23" t="n">
         <v>1.56</v>
@@ -4879,7 +4879,7 @@
         <v>2.5</v>
       </c>
       <c r="V23" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
         <v>1.72</v>
@@ -4975,7 +4975,7 @@
         <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
         <v>15</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>1.89</v>
       </c>
       <c r="G24" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H24" t="n">
         <v>4.3</v>
@@ -5046,7 +5046,7 @@
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N24" t="n">
         <v>3.05</v>
@@ -5076,119 +5076,119 @@
         <v>1.24</v>
       </c>
       <c r="W24" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z24" t="n">
         <v>42</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="AC24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG24" t="n">
         <v>11</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AH24" t="n">
         <v>22</v>
       </c>
-      <c r="AE24" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>25</v>
-      </c>
       <c r="AI24" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ24" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AK24" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AL24" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN24" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.05</v>
+        <v>5.3</v>
       </c>
       <c r="AQ24" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.86</v>
+        <v>7.2</v>
       </c>
       <c r="AS24" t="n">
-        <v>3.05</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BB24" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>2.76</v>
-      </c>
       <c r="BC24" t="n">
-        <v>2.76</v>
+        <v>6.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.92</v>
+        <v>7.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>3.05</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF24" t="n">
-        <v>11</v>
+        <v>5.9</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.05</v>
+        <v>1.79</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -5222,13 +5222,13 @@
         <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="H25" t="n">
         <v>1.89</v>
       </c>
       <c r="I25" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="J25" t="n">
         <v>2.94</v>
@@ -5237,7 +5237,7 @@
         <v>3.45</v>
       </c>
       <c r="L25" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
         <v>1.12</v>
@@ -5246,7 +5246,7 @@
         <v>1.95</v>
       </c>
       <c r="O25" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P25" t="n">
         <v>1.43</v>
@@ -5267,10 +5267,10 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -5428,10 +5428,10 @@
         <v>2.56</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="L26" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -5625,13 +5625,13 @@
         <v>4.7</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M27" t="n">
         <v>1.04</v>
       </c>
       <c r="N27" t="n">
-        <v>2.36</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
         <v>1.2</v>
@@ -5643,10 +5643,10 @@
         <v>1.65</v>
       </c>
       <c r="R27" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="S27" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="T27" t="n">
         <v>1.01</v>
@@ -5664,7 +5664,7 @@
         <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z27" t="n">
         <v>1000</v>
@@ -5673,104 +5673,104 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -5998,13 +5998,13 @@
         <v>1.57</v>
       </c>
       <c r="G29" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H29" t="n">
         <v>5.6</v>
       </c>
       <c r="I29" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J29" t="n">
         <v>5.3</v>
@@ -6028,7 +6028,7 @@
         <v>3.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R29" t="n">
         <v>1.89</v>
@@ -6064,7 +6064,7 @@
         <v>16</v>
       </c>
       <c r="AC29" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD29" t="n">
         <v>22</v>
@@ -6073,7 +6073,7 @@
         <v>65</v>
       </c>
       <c r="AF29" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG29" t="n">
         <v>9.800000000000001</v>
@@ -6112,13 +6112,13 @@
         <v>46</v>
       </c>
       <c r="AS29" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AT29" t="n">
         <v>14.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV29" t="n">
         <v>20</v>
@@ -6145,20 +6145,20 @@
         <v>13</v>
       </c>
       <c r="BD29" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE29" t="n">
         <v>50</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG29" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>
@@ -6198,13 +6198,13 @@
         <v>4.6</v>
       </c>
       <c r="I30" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J30" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L30" t="n">
         <v>1.27</v>
@@ -6228,7 +6228,7 @@
         <v>1.74</v>
       </c>
       <c r="S30" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T30" t="n">
         <v>1.57</v>
@@ -6237,7 +6237,7 @@
         <v>2.66</v>
       </c>
       <c r="V30" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W30" t="n">
         <v>2.24</v>
@@ -6288,7 +6288,7 @@
         <v>24</v>
       </c>
       <c r="AM30" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN30" t="n">
         <v>6.8</v>
@@ -6303,10 +6303,10 @@
         <v>24</v>
       </c>
       <c r="AR30" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS30" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AT30" t="n">
         <v>13.5</v>
@@ -6339,7 +6339,7 @@
         <v>14.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE30" t="n">
         <v>50</v>
@@ -6348,11 +6348,11 @@
         <v>6.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-06 16:14:12</t>
+          <t>2026-04-06 18:24:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH30"/>
+  <dimension ref="A1:BH31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,7 +814,7 @@
         <v>18.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
         <v>17</v>
@@ -823,13 +823,13 @@
         <v>34</v>
       </c>
       <c r="AB2" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
         <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
         <v>24</v>
@@ -841,7 +841,7 @@
         <v>20</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AI2" t="n">
         <v>42</v>
@@ -868,59 +868,59 @@
         <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AU2" t="n">
         <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>34</v>
+        <v>5.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>12.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>2.4</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I3" t="n">
         <v>4.1</v>
@@ -1041,7 +1041,7 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK3" t="n">
         <v>34</v>
@@ -1095,26 +1095,26 @@
         <v>6.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE3" t="n">
         <v>7.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BG3" t="n">
         <v>6.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -1468,28 +1468,28 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY5" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BA5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC5" t="n">
         <v>5.9</v>
       </c>
-      <c r="BB5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BD5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE5" t="n">
         <v>6.2</v>
@@ -1498,11 +1498,11 @@
         <v>5.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="H6" t="n">
         <v>3.25</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="J6" t="n">
         <v>3.65</v>
@@ -1581,7 +1581,7 @@
         <v>2.32</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
         <v>1.77</v>
@@ -1650,7 +1650,7 @@
         <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT6" t="n">
         <v>9.199999999999999</v>
@@ -1662,7 +1662,7 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX6" t="n">
         <v>11.5</v>
@@ -1674,7 +1674,7 @@
         <v>12</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB6" t="n">
         <v>20</v>
@@ -1683,20 +1683,20 @@
         <v>16.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF6" t="n">
         <v>10</v>
       </c>
       <c r="BG6" t="n">
-        <v>22</v>
+        <v>4.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -1859,10 +1859,10 @@
         <v>14</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ7" t="n">
         <v>6</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -1948,13 +1948,13 @@
         <v>2.42</v>
       </c>
       <c r="O8" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="P8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="R8" t="n">
         <v>1.16</v>
@@ -1993,7 +1993,7 @@
         <v>9.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2059,13 +2059,13 @@
         <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA8" t="n">
         <v>5.7</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BC8" t="n">
         <v>4.9</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Greek Super League</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,73 +2882,73 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>2.26</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.08</v>
+        <v>1.17</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>1.17</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
@@ -2957,25 +2957,25 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
@@ -2990,7 +2990,7 @@
         <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
         <v>1000</v>
@@ -2999,69 +2999,69 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,73 +3076,73 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Radnicki Nis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>2.2</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.08</v>
+        <v>1.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.27</v>
+        <v>2.08</v>
       </c>
       <c r="R14" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="S14" t="n">
-        <v>1.27</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3151,25 +3151,25 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
@@ -3184,7 +3184,7 @@
         <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN14" t="n">
         <v>1000</v>
@@ -3193,69 +3193,69 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Radnicki Nis</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>950</v>
       </c>
       <c r="L15" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P15" t="n">
         <v>1.08</v>
       </c>
-      <c r="N15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.9</v>
-      </c>
       <c r="Q15" t="n">
-        <v>2.06</v>
+        <v>1.27</v>
       </c>
       <c r="R15" t="n">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="S15" t="n">
-        <v>3.7</v>
+        <v>1.27</v>
       </c>
       <c r="T15" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Goztepe</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5.5</v>
+        <v>2.64</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7</v>
+        <v>2.7</v>
       </c>
       <c r="H16" t="n">
-        <v>1.68</v>
+        <v>2.92</v>
       </c>
       <c r="I16" t="n">
-        <v>1.76</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.74</v>
+        <v>2.06</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>2.58</v>
+        <v>3.7</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V16" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AR16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV16" t="n">
         <v>12</v>
       </c>
-      <c r="AA16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD16" t="n">
+      <c r="AW16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY16" t="n">
         <v>11</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>17.5</v>
       </c>
       <c r="AZ16" t="n">
         <v>16</v>
       </c>
       <c r="BA16" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF16" t="n">
         <v>23</v>
       </c>
-      <c r="BB16" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BG16" t="n">
-        <v>7.8</v>
+        <v>27</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,55 +3658,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Umraniyespor</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Viktoria Koln</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I17" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>2.92</v>
+        <v>2.32</v>
       </c>
       <c r="O17" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -3715,129 +3715,129 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="W17" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,31 +3852,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK Napredak</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="J18" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,22 +3885,22 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>1.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="R18" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4</v>
+        <v>2.58</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -4046,179 +4046,179 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SSV Ulm</t>
+          <t>TSV Havelse</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.08</v>
+        <v>1.59</v>
       </c>
       <c r="G19" t="n">
-        <v>2.32</v>
+        <v>1.78</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K19" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -4240,28 +4240,28 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Viktoria Koln</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="H20" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="I20" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K20" t="n">
         <v>4.3</v>
@@ -4270,149 +4270,149 @@
         <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>2.32</v>
+        <v>5.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="R20" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="S20" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TSV Havelse</t>
+          <t>SSV Ulm</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.59</v>
+        <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>1.78</v>
+        <v>2.26</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="I21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BF21" t="n">
         <v>6.6</v>
       </c>
-      <c r="J21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
-      </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,31 +4628,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>FK Napredak</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4661,22 +4661,22 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="O22" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>1.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="S22" t="n">
-        <v>2.58</v>
+        <v>1.4</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -4685,10 +4685,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4800,14 +4800,14 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Umraniyespor</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="G23" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="H23" t="n">
         <v>3.1</v>
       </c>
       <c r="I23" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="J23" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="K23" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>5.1</v>
+        <v>2.92</v>
       </c>
       <c r="O23" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="R23" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="T23" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="X23" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z23" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI23" t="n">
         <v>65</v>
       </c>
-      <c r="AB23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>44</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK23" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AL23" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AM23" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AO23" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="AP23" t="n">
-        <v>16.5</v>
+        <v>2.62</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AR23" t="n">
-        <v>19</v>
+        <v>2.46</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>2.64</v>
       </c>
       <c r="AT23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AU23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY23" t="n">
         <v>7.2</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>8.4</v>
       </c>
       <c r="AZ23" t="n">
         <v>11</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>2.54</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>2.46</v>
       </c>
       <c r="BC23" t="n">
-        <v>15</v>
+        <v>2.42</v>
       </c>
       <c r="BD23" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>2.64</v>
       </c>
       <c r="BF23" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG23" t="n">
-        <v>16</v>
+        <v>2.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Goztepe</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.89</v>
+        <v>5.5</v>
       </c>
       <c r="G24" t="n">
-        <v>2.1</v>
+        <v>5.7</v>
       </c>
       <c r="H24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N24" t="n">
         <v>4.3</v>
       </c>
-      <c r="I24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O24" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="P24" t="n">
-        <v>1.71</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.14</v>
+        <v>1.74</v>
       </c>
       <c r="R24" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>2.58</v>
       </c>
       <c r="T24" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="W24" t="n">
-        <v>1.91</v>
+        <v>1.21</v>
       </c>
       <c r="X24" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS24" t="n">
         <v>15</v>
       </c>
-      <c r="Z24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>38</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS24" t="n">
+      <c r="AT24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU24" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AT24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AV24" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.8</v>
+        <v>14.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY24" t="n">
-        <v>4.8</v>
+        <v>17.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.77</v>
+        <v>23</v>
       </c>
       <c r="BB24" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC24" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.79</v>
+        <v>7</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,184 +5205,184 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="X25" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AX25" t="n">
         <v>5</v>
       </c>
-      <c r="G25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -5404,28 +5404,28 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J26" t="n">
         <v>2.94</v>
-      </c>
-      <c r="G26" t="n">
-        <v>4</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.56</v>
       </c>
       <c r="K26" t="n">
         <v>3.45</v>
@@ -5434,25 +5434,25 @@
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N26" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O26" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="P26" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="R26" t="n">
         <v>1.12</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="T26" t="n">
         <v>1.01</v>
@@ -5461,13 +5461,13 @@
         <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="W26" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="X26" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
         <v>1000</v>
@@ -5524,66 +5524,66 @@
         <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,55 +5598,55 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>NEOM Sports Club</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.66</v>
+        <v>2.94</v>
       </c>
       <c r="G27" t="n">
-        <v>1.81</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="I27" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="J27" t="n">
-        <v>4</v>
+        <v>2.56</v>
       </c>
       <c r="K27" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="L27" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="O27" t="n">
-        <v>1.2</v>
+        <v>1.58</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.65</v>
+        <v>3.05</v>
       </c>
       <c r="R27" t="n">
-        <v>1.47</v>
+        <v>1.12</v>
       </c>
       <c r="S27" t="n">
-        <v>2.54</v>
+        <v>6</v>
       </c>
       <c r="T27" t="n">
         <v>1.01</v>
@@ -5655,16 +5655,16 @@
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="W27" t="n">
-        <v>2.22</v>
+        <v>1.33</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y27" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
         <v>1000</v>
@@ -5673,104 +5673,104 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>2.9</v>
+        <v>1.11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2.64</v>
+        <v>1.16</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.76</v>
+        <v>1.16</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.9</v>
+        <v>1.16</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.42</v>
+        <v>1.16</v>
       </c>
       <c r="AU27" t="n">
-        <v>2.36</v>
+        <v>1.16</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.62</v>
+        <v>1.16</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.8</v>
+        <v>1.16</v>
       </c>
       <c r="AX27" t="n">
-        <v>8.800000000000001</v>
+        <v>1.16</v>
       </c>
       <c r="AY27" t="n">
-        <v>2.38</v>
+        <v>1.16</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2.6</v>
+        <v>1.16</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.8</v>
+        <v>1.16</v>
       </c>
       <c r="BB27" t="n">
-        <v>2.58</v>
+        <v>1.16</v>
       </c>
       <c r="BC27" t="n">
-        <v>12.5</v>
+        <v>1.16</v>
       </c>
       <c r="BD27" t="n">
-        <v>2.72</v>
+        <v>1.16</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.9</v>
+        <v>1.16</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.8</v>
+        <v>1.16</v>
       </c>
       <c r="BG27" t="n">
-        <v>2.8</v>
+        <v>1.16</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -5792,186 +5792,186 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.16</v>
+        <v>1.66</v>
       </c>
       <c r="G28" t="n">
-        <v>1.21</v>
+        <v>1.81</v>
       </c>
       <c r="H28" t="n">
-        <v>17.5</v>
+        <v>4.8</v>
       </c>
       <c r="I28" t="n">
-        <v>32</v>
+        <v>6.4</v>
       </c>
       <c r="J28" t="n">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
-        <v>10.5</v>
+        <v>4.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N28" t="n">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="P28" t="n">
-        <v>3.85</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="R28" t="n">
-        <v>2.14</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>1.72</v>
+        <v>2.48</v>
       </c>
       <c r="T28" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="W28" t="n">
-        <v>5.8</v>
+        <v>2.22</v>
       </c>
       <c r="X28" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="Z28" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AD28" t="n">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="AE28" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AG28" t="n">
         <v>13.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AI28" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AK28" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AL28" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AM28" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.92</v>
+        <v>11</v>
       </c>
       <c r="AO28" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6.4</v>
+        <v>2.64</v>
       </c>
       <c r="AR28" t="n">
-        <v>6.6</v>
+        <v>2.76</v>
       </c>
       <c r="AS28" t="n">
-        <v>6.8</v>
+        <v>2.9</v>
       </c>
       <c r="AT28" t="n">
-        <v>13.5</v>
+        <v>2.42</v>
       </c>
       <c r="AU28" t="n">
-        <v>5.4</v>
+        <v>2.36</v>
       </c>
       <c r="AV28" t="n">
-        <v>6.4</v>
+        <v>2.62</v>
       </c>
       <c r="AW28" t="n">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="AX28" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY28" t="n">
-        <v>10.5</v>
+        <v>2.38</v>
       </c>
       <c r="AZ28" t="n">
-        <v>5.7</v>
+        <v>2.6</v>
       </c>
       <c r="BA28" t="n">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>9</v>
+        <v>2.58</v>
       </c>
       <c r="BC28" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.7</v>
+        <v>2.72</v>
       </c>
       <c r="BE28" t="n">
-        <v>6.4</v>
+        <v>2.9</v>
       </c>
       <c r="BF28" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="BG28" t="n">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,184 +5981,184 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="G29" t="n">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="H29" t="n">
-        <v>5.6</v>
+        <v>17.5</v>
       </c>
       <c r="I29" t="n">
+        <v>28</v>
+      </c>
+      <c r="J29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W29" t="n">
         <v>5.8</v>
       </c>
-      <c r="J29" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="K29" t="n">
+      <c r="X29" t="n">
+        <v>65</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>140</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>310</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>110</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>350</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>300</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU29" t="n">
         <v>5.4</v>
       </c>
-      <c r="L29" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N29" t="n">
-        <v>8</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="X29" t="n">
-        <v>38</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>34</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>30</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>46</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>12</v>
-      </c>
       <c r="AV29" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>48</v>
+        <v>6.6</v>
       </c>
       <c r="AX29" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>16</v>
+        <v>5.7</v>
       </c>
       <c r="BA29" t="n">
-        <v>40</v>
+        <v>6.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="BC29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD29" t="n">
-        <v>20</v>
+        <v>5.7</v>
       </c>
       <c r="BE29" t="n">
-        <v>50</v>
+        <v>6.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>32</v>
+        <v>6.6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-06 18:24:21</t>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>
@@ -6180,179 +6180,373 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="G30" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="H30" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="I30" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="J30" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="K30" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="M30" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N30" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="O30" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="P30" t="n">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="R30" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="S30" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="T30" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="U30" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="V30" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="W30" t="n">
-        <v>2.24</v>
+        <v>2.72</v>
       </c>
       <c r="X30" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="Y30" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="Z30" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AA30" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AB30" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AC30" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE30" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AF30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG30" t="n">
         <v>10</v>
       </c>
       <c r="AH30" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AJ30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV30" t="n">
         <v>20</v>
       </c>
-      <c r="AK30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>24</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>80</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>17</v>
-      </c>
       <c r="AW30" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AX30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA30" t="n">
         <v>40</v>
       </c>
       <c r="BB30" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BD30" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BE30" t="n">
         <v>50</v>
       </c>
       <c r="BF30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-06 20:33:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Paris St-G</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N31" t="n">
         <v>6.4</v>
       </c>
-      <c r="BG30" t="n">
-        <v>28</v>
-      </c>
-      <c r="BH30" t="inlineStr">
-        <is>
-          <t>2026-04-06 18:24:21</t>
+      <c r="O31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X31" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>80</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>27</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-06 20:33:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -763,7 +763,7 @@
         <v>4.3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I2" t="n">
         <v>2.28</v>
@@ -772,7 +772,7 @@
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
         <v>1.32</v>
@@ -781,19 +781,19 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
         <v>3.1</v>
@@ -805,10 +805,10 @@
         <v>2.02</v>
       </c>
       <c r="V2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X2" t="n">
         <v>18.5</v>
@@ -817,7 +817,7 @@
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AA2" t="n">
         <v>34</v>
@@ -862,65 +862,65 @@
         <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AP2" t="n">
         <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AU2" t="n">
         <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AW2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>4.6</v>
       </c>
-      <c r="AX2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY2" t="n">
+      <c r="BA2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG2" t="n">
         <v>4.5</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H3" t="n">
         <v>3.55</v>
@@ -966,16 +966,16 @@
         <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O3" t="n">
         <v>1.46</v>
@@ -1020,7 +1020,7 @@
         <v>8.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD3" t="n">
         <v>17</v>
@@ -1053,7 +1053,7 @@
         <v>190</v>
       </c>
       <c r="AN3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
@@ -1068,7 +1068,7 @@
         <v>21</v>
       </c>
       <c r="AS3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT3" t="n">
         <v>6.4</v>
@@ -1080,7 +1080,7 @@
         <v>13.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX3" t="n">
         <v>11</v>
@@ -1092,29 +1092,29 @@
         <v>19.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
         <v>1.11</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>3.25</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
         <v>3.65</v>
@@ -1581,7 +1581,7 @@
         <v>2.32</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
         <v>1.77</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -1951,16 +1951,16 @@
         <v>1.58</v>
       </c>
       <c r="P8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R8" t="n">
         <v>1.16</v>
       </c>
       <c r="S8" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
         <v>2.4</v>
@@ -2059,13 +2059,13 @@
         <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BA8" t="n">
         <v>5.7</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BC8" t="n">
         <v>4.9</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -2142,19 +2142,19 @@
         <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
         <v>1.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="R9" t="n">
         <v>1.08</v>
       </c>
       <c r="S9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
         <v>15.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
         <v>25</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="AU14" t="n">
         <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF14" t="n">
         <v>15</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
         <v>3.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
@@ -3518,7 +3518,7 @@
         <v>1.81</v>
       </c>
       <c r="U16" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V16" t="n">
         <v>1.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -3670,10 +3670,10 @@
         <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I17" t="n">
         <v>3.35</v>
@@ -3691,22 +3691,22 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
         <v>1.18</v>
       </c>
       <c r="P17" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R17" t="n">
         <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -3718,7 +3718,7 @@
         <v>1.43</v>
       </c>
       <c r="W17" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -3864,13 +3864,13 @@
         <v>2.28</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="H18" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="I18" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J18" t="n">
         <v>3.45</v>
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -4055,19 +4055,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="G19" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K19" t="n">
         <v>5.1</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>2.14</v>
       </c>
       <c r="G20" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I20" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="J20" t="n">
         <v>3.8</v>
@@ -4285,10 +4285,10 @@
         <v>1.52</v>
       </c>
       <c r="R20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S20" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="T20" t="n">
         <v>1.56</v>
@@ -4297,7 +4297,7 @@
         <v>2.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W20" t="n">
         <v>1.72</v>
@@ -4312,7 +4312,7 @@
         <v>32</v>
       </c>
       <c r="AA20" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB20" t="n">
         <v>17</v>
@@ -4321,7 +4321,7 @@
         <v>12</v>
       </c>
       <c r="AD20" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
         <v>40</v>
@@ -4339,10 +4339,10 @@
         <v>44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL20" t="n">
         <v>36</v>
@@ -4351,10 +4351,10 @@
         <v>75</v>
       </c>
       <c r="AN20" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP20" t="n">
         <v>16.5</v>
@@ -4366,7 +4366,7 @@
         <v>19</v>
       </c>
       <c r="AS20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT20" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
         <v>3.8</v>
       </c>
       <c r="AX20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY20" t="n">
         <v>8.4</v>
@@ -4402,17 +4402,17 @@
         <v>20</v>
       </c>
       <c r="BE20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G21" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H21" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="J21" t="n">
         <v>3.9</v>
@@ -4470,7 +4470,7 @@
         <v>2.48</v>
       </c>
       <c r="O21" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P21" t="n">
         <v>2.46</v>
@@ -4494,7 +4494,7 @@
         <v>1.38</v>
       </c>
       <c r="W21" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4515,13 +4515,13 @@
         <v>14.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE21" t="n">
         <v>50</v>
       </c>
       <c r="AF21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG21" t="n">
         <v>17</v>
@@ -4533,25 +4533,25 @@
         <v>50</v>
       </c>
       <c r="AJ21" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL21" t="n">
         <v>40</v>
       </c>
       <c r="AM21" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
         <v>34</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AQ21" t="n">
         <v>11.5</v>
@@ -4560,7 +4560,7 @@
         <v>16.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AT21" t="n">
         <v>8.4</v>
@@ -4572,7 +4572,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AX21" t="n">
         <v>10</v>
@@ -4584,10 +4584,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC21" t="n">
         <v>12</v>
@@ -4596,7 +4596,7 @@
         <v>16.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BF21" t="n">
         <v>6.6</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -4861,16 +4861,16 @@
         <v>1.26</v>
       </c>
       <c r="P23" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
         <v>1.72</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -5184,11 +5184,11 @@
         <v>7.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
         <v>2.84</v>
       </c>
       <c r="AX25" t="n">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY25" t="n">
         <v>4.8</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H27" t="n">
         <v>2.7</v>
       </c>
       <c r="I27" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J27" t="n">
         <v>2.56</v>
       </c>
       <c r="K27" t="n">
-        <v>3.45</v>
+        <v>950</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -5658,7 +5658,7 @@
         <v>1.4</v>
       </c>
       <c r="W27" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X27" t="n">
         <v>8</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
         <v>1.66</v>
       </c>
       <c r="G28" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H28" t="n">
         <v>4.8</v>
@@ -5840,7 +5840,7 @@
         <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -5852,7 +5852,7 @@
         <v>1.18</v>
       </c>
       <c r="W28" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5927,19 +5927,19 @@
         <v>2.36</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.62</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
         <v>2.8</v>
       </c>
       <c r="AX28" t="n">
-        <v>8.800000000000001</v>
+        <v>2.44</v>
       </c>
       <c r="AY28" t="n">
         <v>2.38</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2.6</v>
+        <v>13.5</v>
       </c>
       <c r="BA28" t="n">
         <v>2.8</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
         <v>1.09</v>
       </c>
       <c r="P29" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="Q29" t="n">
         <v>1.28</v>
@@ -6049,7 +6049,7 @@
         <v>5.8</v>
       </c>
       <c r="X29" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="Y29" t="n">
         <v>140</v>
@@ -6061,7 +6061,7 @@
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC29" t="n">
         <v>25</v>
@@ -6103,13 +6103,13 @@
         <v>300</v>
       </c>
       <c r="AP29" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR29" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS29" t="n">
         <v>6.8</v>
@@ -6118,13 +6118,13 @@
         <v>13.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AV29" t="n">
         <v>6.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX29" t="n">
         <v>9.6</v>
@@ -6133,7 +6133,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BA29" t="n">
         <v>6.6</v>
@@ -6145,10 +6145,10 @@
         <v>11</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF29" t="n">
         <v>2.5</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
         <v>5.8</v>
       </c>
       <c r="J30" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K30" t="n">
         <v>5.4</v>
@@ -6231,13 +6231,13 @@
         <v>2.06</v>
       </c>
       <c r="T30" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U30" t="n">
         <v>2.74</v>
       </c>
       <c r="V30" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W30" t="n">
         <v>2.72</v>
@@ -6276,7 +6276,7 @@
         <v>17.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ30" t="n">
         <v>17</v>
@@ -6303,16 +6303,16 @@
         <v>30</v>
       </c>
       <c r="AR30" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AS30" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AT30" t="n">
         <v>14.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV30" t="n">
         <v>20</v>
@@ -6321,13 +6321,13 @@
         <v>48</v>
       </c>
       <c r="AX30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY30" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA30" t="n">
         <v>40</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G31" t="n">
         <v>1.81</v>
@@ -6392,13 +6392,13 @@
         <v>4.5</v>
       </c>
       <c r="I31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J31" t="n">
         <v>4.3</v>
       </c>
       <c r="K31" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L31" t="n">
         <v>1.27</v>
@@ -6473,7 +6473,7 @@
         <v>44</v>
       </c>
       <c r="AJ31" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK31" t="n">
         <v>15.5</v>
@@ -6524,7 +6524,7 @@
         <v>14.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB31" t="n">
         <v>18.5</v>
@@ -6533,7 +6533,7 @@
         <v>14.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE31" t="n">
         <v>50</v>
@@ -6542,11 +6542,11 @@
         <v>6.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-06 20:33:57</t>
+          <t>2026-04-06 22:43:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH31"/>
+  <dimension ref="A1:BH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="I2" t="n">
         <v>2.28</v>
@@ -775,7 +775,7 @@
         <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -799,16 +799,16 @@
         <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="U2" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
         <v>1.79</v>
       </c>
       <c r="W2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
         <v>18.5</v>
@@ -820,13 +820,13 @@
         <v>970</v>
       </c>
       <c r="AA2" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AB2" t="n">
         <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
         <v>970</v>
@@ -835,31 +835,31 @@
         <v>24</v>
       </c>
       <c r="AF2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG2" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
         <v>970</v>
       </c>
       <c r="AI2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="n">
         <v>55</v>
       </c>
       <c r="AL2" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
         <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO2" t="n">
         <v>970</v>
@@ -868,59 +868,59 @@
         <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU2" t="n">
         <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BA2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG2" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H3" t="n">
         <v>3.55</v>
@@ -969,7 +969,7 @@
         <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -1345,16 +1345,16 @@
         <v>3.2</v>
       </c>
       <c r="H5" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I5" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1363,13 +1363,13 @@
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.48</v>
       </c>
       <c r="P5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q5" t="n">
         <v>2.42</v>
@@ -1387,7 +1387,7 @@
         <v>1.87</v>
       </c>
       <c r="V5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
         <v>1.45</v>
@@ -1429,7 +1429,7 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
         <v>1000</v>
@@ -1489,7 +1489,7 @@
         <v>5.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="BE5" t="n">
         <v>6.2</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>2.3</v>
       </c>
       <c r="H6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I6" t="n">
         <v>4.1</v>
@@ -1575,19 +1575,19 @@
         <v>2.78</v>
       </c>
       <c r="T6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U6" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
         <v>1.77</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y6" t="n">
         <v>18.5</v>
@@ -1608,7 +1608,7 @@
         <v>17</v>
       </c>
       <c r="AE6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF6" t="n">
         <v>18</v>
@@ -1650,7 +1650,7 @@
         <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT6" t="n">
         <v>9.199999999999999</v>
@@ -1662,7 +1662,7 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX6" t="n">
         <v>11.5</v>
@@ -1680,10 +1680,10 @@
         <v>20</v>
       </c>
       <c r="BC6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE6" t="n">
         <v>4.8</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>18.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="I7" t="n">
         <v>1.32</v>
@@ -1751,13 +1751,13 @@
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O7" t="n">
         <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
         <v>1.9</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>1.72</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
@@ -1948,19 +1948,19 @@
         <v>2.42</v>
       </c>
       <c r="O8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="P8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R8" t="n">
         <v>1.16</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="T8" t="n">
         <v>2.4</v>
@@ -1972,7 +1972,7 @@
         <v>1.14</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X8" t="n">
         <v>9.199999999999999</v>
@@ -2038,7 +2038,7 @@
         <v>5.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT8" t="n">
         <v>5</v>
@@ -2068,7 +2068,7 @@
         <v>5</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
         <v>5.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2345,7 @@
         <v>1.83</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
         <v>2.84</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Parnu JK Vaprus</t>
+          <t>Radnicki Nis</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -2527,22 +2527,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="S11" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,73 +2688,73 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nomme Utd</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>2.2</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.08</v>
+        <v>2.16</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S12" t="n">
-        <v>1.08</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z12" t="n">
         <v>1000</v>
@@ -2763,25 +2763,25 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG12" t="n">
         <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
@@ -2796,7 +2796,7 @@
         <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -2882,12 +2882,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -2906,7 +2906,7 @@
         <v>1.03</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2918,19 +2918,19 @@
         <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="P13" t="n">
         <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Greek Super League</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,73 +3076,73 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.08</v>
+        <v>1.08</v>
       </c>
       <c r="R14" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>1.08</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3151,25 +3151,25 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
         <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
@@ -3184,7 +3184,7 @@
         <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
         <v>1000</v>
@@ -3193,69 +3193,69 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Radnicki Nis</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -3294,7 +3294,7 @@
         <v>1.03</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3303,22 +3303,22 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="P15" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="R15" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -3473,13 +3473,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G16" t="n">
         <v>2.7</v>
       </c>
       <c r="H16" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
@@ -3533,7 +3533,7 @@
         <v>11.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA16" t="n">
         <v>48</v>
@@ -3545,7 +3545,7 @@
         <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>34</v>
@@ -3605,7 +3605,7 @@
         <v>30</v>
       </c>
       <c r="AX16" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY16" t="n">
         <v>11</v>
@@ -3629,21 +3629,21 @@
         <v>38</v>
       </c>
       <c r="BF16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BG16" t="n">
         <v>27</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,55 +3658,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Viktoria Koln</t>
+          <t>FK Napredak</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="G17" t="n">
-        <v>2.48</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="O17" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>1.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>1.08</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -3715,10 +3715,10 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3775,52 +3775,52 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
         <v>1.01</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,52 +3852,52 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Goztepe</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.28</v>
+        <v>5.5</v>
       </c>
       <c r="G18" t="n">
-        <v>2.72</v>
+        <v>5.7</v>
       </c>
       <c r="H18" t="n">
-        <v>2.94</v>
+        <v>1.68</v>
       </c>
       <c r="I18" t="n">
-        <v>3.7</v>
+        <v>1.76</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>2.22</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
         <v>2.58</v>
@@ -3909,129 +3909,129 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.64</v>
+        <v>1.21</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,179 +4046,179 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Umraniyespor</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TSV Havelse</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="G19" t="n">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="H19" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="I19" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="J19" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="K19" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>SSV Ulm</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="H20" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I20" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="J20" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>5.1</v>
+        <v>2.48</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="R20" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW20" t="n">
         <v>2.5</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="X20" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="AX20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC20" t="n">
         <v>12</v>
       </c>
-      <c r="AD20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG20" t="n">
+      <c r="BD20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG20" t="n">
         <v>14</v>
       </c>
-      <c r="AH20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -4434,55 +4434,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SSV Ulm</t>
+          <t>Viktoria Koln</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="G21" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="H21" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="I21" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="J21" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="K21" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P21" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="R21" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -4491,129 +4491,129 @@
         <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FK Napredak</t>
+          <t>TSV Havelse</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>1.74</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="J22" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>5.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,55 +4822,55 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Umraniyespor</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="G23" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="H23" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="I23" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="J23" t="n">
         <v>3.45</v>
       </c>
       <c r="K23" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>2.92</v>
+        <v>2.22</v>
       </c>
       <c r="O23" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -4879,129 +4879,129 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.46</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.64</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU23" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV23" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.52</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.54</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>2.46</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.42</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.64</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,179 +5016,179 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Goztepe</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5.5</v>
+        <v>2.12</v>
       </c>
       <c r="G24" t="n">
-        <v>5.7</v>
+        <v>2.36</v>
       </c>
       <c r="H24" t="n">
-        <v>1.68</v>
+        <v>3.15</v>
       </c>
       <c r="I24" t="n">
-        <v>1.76</v>
+        <v>3.6</v>
       </c>
       <c r="J24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X24" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE24" t="n">
         <v>4</v>
       </c>
-      <c r="K24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>970</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>970</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>85</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ24" t="n">
+      <c r="BF24" t="n">
         <v>8.4</v>
       </c>
-      <c r="AR24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BG24" t="n">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         <v>1.89</v>
       </c>
       <c r="I26" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="J26" t="n">
         <v>2.94</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="G27" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="H27" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="I27" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J27" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="K27" t="n">
-        <v>950</v>
+        <v>3.05</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -5655,10 +5655,10 @@
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.4</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.34</v>
       </c>
       <c r="X27" t="n">
         <v>8</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -5837,10 +5837,10 @@
         <v>1.65</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S28" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -6004,13 +6004,13 @@
         <v>17.5</v>
       </c>
       <c r="I29" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J29" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="L29" t="n">
         <v>1.16</v>
@@ -6043,7 +6043,7 @@
         <v>2.02</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
         <v>5.8</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -6180,179 +6180,179 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Paris St-G</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F30" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T30" t="n">
         <v>1.57</v>
       </c>
-      <c r="G30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="H30" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I30" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J30" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K30" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N30" t="n">
-        <v>8</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.53</v>
-      </c>
       <c r="U30" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="V30" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="W30" t="n">
-        <v>2.72</v>
+        <v>2.24</v>
       </c>
       <c r="X30" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="Y30" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="Z30" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AA30" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AB30" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE30" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF30" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG30" t="n">
         <v>10</v>
       </c>
       <c r="AH30" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV30" t="n">
         <v>17</v>
       </c>
-      <c r="AK30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>34</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>30</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>46</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>100</v>
-      </c>
-      <c r="AT30" t="n">
+      <c r="AW30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ30" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>15.5</v>
       </c>
       <c r="BA30" t="n">
         <v>40</v>
       </c>
       <c r="BB30" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BE30" t="n">
         <v>50</v>
       </c>
       <c r="BF30" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>
@@ -6374,179 +6374,373 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="G31" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="H31" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="I31" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="J31" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="K31" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="L31" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="M31" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N31" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="P31" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="R31" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="S31" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="T31" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="U31" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="V31" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="W31" t="n">
-        <v>2.22</v>
+        <v>2.72</v>
       </c>
       <c r="X31" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="Y31" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="Z31" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AA31" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AB31" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AC31" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AF31" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG31" t="n">
         <v>10</v>
       </c>
       <c r="AH31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ31" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>24</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>80</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>14.5</v>
       </c>
       <c r="BA31" t="n">
         <v>40</v>
       </c>
       <c r="BB31" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BD31" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BE31" t="n">
         <v>50</v>
       </c>
       <c r="BF31" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BG31" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-06 22:43:25</t>
+          <t>2026-04-07 00:53:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Ecu)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-07 00:53:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G2" t="n">
         <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I2" t="n">
         <v>2.28</v>
@@ -775,7 +775,7 @@
         <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -808,7 +808,7 @@
         <v>1.79</v>
       </c>
       <c r="W2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X2" t="n">
         <v>18.5</v>
@@ -859,7 +859,7 @@
         <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO2" t="n">
         <v>970</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G3" t="n">
         <v>2.4</v>
@@ -960,13 +960,13 @@
         <v>3.55</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
         <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
         <v>1.46</v>
@@ -984,10 +984,10 @@
         <v>1.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
         <v>4.5</v>
@@ -1050,7 +1050,7 @@
         <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN3" t="n">
         <v>1000</v>
@@ -1089,7 +1089,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
         <v>7.4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>2.74</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
         <v>3.4</v>
@@ -1399,7 +1399,7 @@
         <v>9.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
@@ -1411,7 +1411,7 @@
         <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1420,10 +1420,10 @@
         <v>24</v>
       </c>
       <c r="AG5" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
@@ -1456,7 +1456,7 @@
         <v>13.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AT5" t="n">
         <v>8.199999999999999</v>
@@ -1468,41 +1468,41 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AY5" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BA5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB5" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB5" t="n">
-        <v>6</v>
-      </c>
       <c r="BC5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BD5" t="n">
         <v>50</v>
       </c>
       <c r="BE5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG5" t="n">
         <v>6.2</v>
       </c>
-      <c r="BF5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="H6" t="n">
         <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J6" t="n">
         <v>3.65</v>
@@ -1557,7 +1557,7 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.24</v>
@@ -1581,16 +1581,16 @@
         <v>2.34</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="X6" t="n">
         <v>23</v>
       </c>
       <c r="Y6" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z6" t="n">
         <v>32</v>
@@ -1605,10 +1605,10 @@
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF6" t="n">
         <v>18</v>
@@ -1635,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO6" t="n">
         <v>34</v>
@@ -1644,7 +1644,7 @@
         <v>14.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR6" t="n">
         <v>20</v>
@@ -1659,7 +1659,7 @@
         <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW6" t="n">
         <v>4.5</v>
@@ -1674,7 +1674,7 @@
         <v>12</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BB6" t="n">
         <v>20</v>
@@ -1686,7 +1686,7 @@
         <v>4.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF6" t="n">
         <v>10</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="G7" t="n">
         <v>18.5</v>
@@ -1739,13 +1739,13 @@
         <v>1.32</v>
       </c>
       <c r="J7" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
@@ -1757,16 +1757,16 @@
         <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
         <v>2.5</v>
@@ -1793,7 +1793,7 @@
         <v>11</v>
       </c>
       <c r="AB7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC7" t="n">
         <v>15.5</v>
@@ -1856,7 +1856,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX7" t="n">
         <v>6.8</v>
@@ -1886,11 +1886,11 @@
         <v>7</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="G8" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
@@ -1933,7 +1933,7 @@
         <v>8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
         <v>3.65</v>
@@ -1945,16 +1945,16 @@
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="O8" t="n">
         <v>1.6</v>
       </c>
       <c r="P8" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
         <v>1.16</v>
@@ -1963,7 +1963,7 @@
         <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="U8" t="n">
         <v>1.56</v>
@@ -1972,10 +1972,10 @@
         <v>1.14</v>
       </c>
       <c r="W8" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y8" t="n">
         <v>17</v>
@@ -1987,7 +1987,7 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC8" t="n">
         <v>9.4</v>
@@ -1999,7 +1999,7 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="n">
         <v>12</v>
@@ -2023,7 +2023,7 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2035,22 +2035,22 @@
         <v>12</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX8" t="n">
         <v>7.6</v>
@@ -2059,32 +2059,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF8" t="n">
         <v>17.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -2312,10 +2312,10 @@
         <v>6.6</v>
       </c>
       <c r="G10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="I10" t="n">
         <v>1.58</v>
@@ -2324,10 +2324,10 @@
         <v>4.4</v>
       </c>
       <c r="K10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
@@ -2339,16 +2339,16 @@
         <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" t="n">
         <v>1.83</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
         <v>1.89</v>
@@ -2357,10 +2357,10 @@
         <v>1.92</v>
       </c>
       <c r="V10" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
         <v>22</v>
@@ -2432,7 +2432,7 @@
         <v>5.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV10" t="n">
         <v>4.3</v>
@@ -2468,11 +2468,11 @@
         <v>6.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>2.2</v>
@@ -2706,7 +2706,7 @@
         <v>3.85</v>
       </c>
       <c r="I12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
         <v>3.45</v>
@@ -2721,34 +2721,34 @@
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q12" t="n">
         <v>2.16</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T12" t="n">
         <v>1.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X12" t="n">
         <v>14</v>
@@ -2766,7 +2766,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>21</v>
@@ -2775,7 +2775,7 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT12" t="n">
         <v>3.75</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.45</v>
       </c>
       <c r="AU12" t="n">
         <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.95</v>
+        <v>10.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.1</v>
+        <v>17</v>
       </c>
       <c r="BA12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF12" t="n">
         <v>4.6</v>
       </c>
-      <c r="BB12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>15</v>
-      </c>
       <c r="BG12" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -2912,25 +2912,25 @@
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
         <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="P13" t="n">
         <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
         <v>1.25</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
         <v>1.25</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
         <v>34</v>
       </c>
       <c r="AF16" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG16" t="n">
         <v>12</v>
@@ -3605,7 +3605,7 @@
         <v>30</v>
       </c>
       <c r="AX16" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY16" t="n">
         <v>11</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>5.5</v>
       </c>
       <c r="G18" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="H18" t="n">
         <v>1.68</v>
@@ -3897,16 +3897,16 @@
         <v>1.74</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V18" t="n">
         <v>2.3</v>
@@ -3921,7 +3921,7 @@
         <v>10.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA18" t="n">
         <v>970</v>
@@ -3933,7 +3933,7 @@
         <v>10</v>
       </c>
       <c r="AD18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE18" t="n">
         <v>970</v>
@@ -3954,7 +3954,7 @@
         <v>160</v>
       </c>
       <c r="AK18" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AL18" t="n">
         <v>70</v>
@@ -3963,7 +3963,7 @@
         <v>120</v>
       </c>
       <c r="AN18" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AO18" t="n">
         <v>9.6</v>
@@ -3972,13 +3972,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AT18" t="n">
         <v>17</v>
@@ -3987,13 +3987,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV18" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AW18" t="n">
         <v>14.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY18" t="n">
         <v>17.5</v>
@@ -4005,26 +4005,26 @@
         <v>23</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC18" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -4073,13 +4073,13 @@
         <v>4.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O19" t="n">
         <v>1.26</v>
@@ -4142,7 +4142,7 @@
         <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ19" t="n">
         <v>38</v>
@@ -4160,19 +4160,19 @@
         <v>20</v>
       </c>
       <c r="AO19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AQ19" t="n">
         <v>9.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="AT19" t="n">
         <v>7</v>
@@ -4184,7 +4184,7 @@
         <v>9.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AX19" t="n">
         <v>9.199999999999999</v>
@@ -4196,19 +4196,19 @@
         <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BB19" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BF19" t="n">
         <v>9.199999999999999</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>2.04</v>
       </c>
       <c r="G20" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H20" t="n">
         <v>3.3</v>
       </c>
       <c r="I20" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="J20" t="n">
         <v>3.9</v>
@@ -4270,13 +4270,13 @@
         <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>2.48</v>
+        <v>5.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="P20" t="n">
         <v>2.46</v>
@@ -4285,134 +4285,134 @@
         <v>1.49</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="S20" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="V20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y20" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Z20" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA20" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF20" t="n">
         <v>20</v>
       </c>
-      <c r="AC20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD20" t="n">
+      <c r="AG20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR20" t="n">
         <v>20</v>
       </c>
-      <c r="AE20" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG20" t="n">
+      <c r="AS20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG20" t="n">
         <v>17</v>
       </c>
-      <c r="AH20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>14</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="H21" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="I21" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J21" t="n">
         <v>3.7</v>
@@ -4467,22 +4467,22 @@
         <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O21" t="n">
         <v>1.18</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R21" t="n">
         <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -4491,10 +4491,10 @@
         <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -4831,19 +4831,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G23" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="H23" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I23" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J23" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
         <v>4.1</v>
@@ -4861,10 +4861,10 @@
         <v>1.22</v>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R23" t="n">
         <v>1.35</v>
@@ -4879,10 +4879,10 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W23" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -5025,19 +5025,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G24" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H24" t="n">
         <v>3.15</v>
       </c>
       <c r="I24" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K24" t="n">
         <v>4.3</v>
@@ -5055,7 +5055,7 @@
         <v>1.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q24" t="n">
         <v>1.52</v>
@@ -5076,7 +5076,7 @@
         <v>1.39</v>
       </c>
       <c r="W24" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X24" t="n">
         <v>28</v>
@@ -5097,7 +5097,7 @@
         <v>12</v>
       </c>
       <c r="AD24" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE24" t="n">
         <v>40</v>
@@ -5130,7 +5130,7 @@
         <v>14</v>
       </c>
       <c r="AO24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP24" t="n">
         <v>16.5</v>
@@ -5142,7 +5142,7 @@
         <v>19</v>
       </c>
       <c r="AS24" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT24" t="n">
         <v>10</v>
@@ -5154,7 +5154,7 @@
         <v>10.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AX24" t="n">
         <v>12</v>
@@ -5166,10 +5166,10 @@
         <v>11</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BB24" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BC24" t="n">
         <v>15</v>
@@ -5181,14 +5181,14 @@
         <v>4</v>
       </c>
       <c r="BF24" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG24" t="n">
         <v>16.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="G25" t="n">
         <v>2.1</v>
@@ -5228,7 +5228,7 @@
         <v>4.3</v>
       </c>
       <c r="I25" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J25" t="n">
         <v>3.25</v>
@@ -5237,19 +5237,19 @@
         <v>3.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
         <v>1.39</v>
       </c>
       <c r="P25" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q25" t="n">
         <v>2.14</v>
@@ -5264,10 +5264,10 @@
         <v>1.92</v>
       </c>
       <c r="U25" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V25" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W25" t="n">
         <v>1.91</v>
@@ -5279,7 +5279,7 @@
         <v>970</v>
       </c>
       <c r="Z25" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA25" t="n">
         <v>140</v>
@@ -5324,7 +5324,7 @@
         <v>970</v>
       </c>
       <c r="AO25" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP25" t="n">
         <v>5.3</v>
@@ -5333,10 +5333,10 @@
         <v>5.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT25" t="n">
         <v>6.6</v>
@@ -5348,7 +5348,7 @@
         <v>6</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="AX25" t="n">
         <v>9.800000000000001</v>
@@ -5357,32 +5357,32 @@
         <v>4.8</v>
       </c>
       <c r="AZ25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BB25" t="n">
         <v>6.2</v>
       </c>
-      <c r="BA25" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BC25" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD25" t="n">
         <v>7.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF25" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G26" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H26" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="I26" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J26" t="n">
         <v>2.94</v>
       </c>
       <c r="K26" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5437,16 +5437,16 @@
         <v>1.12</v>
       </c>
       <c r="N26" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="O26" t="n">
         <v>1.54</v>
       </c>
       <c r="P26" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="R26" t="n">
         <v>1.12</v>
@@ -5461,10 +5461,10 @@
         <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="W26" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -5613,13 +5613,13 @@
         <v>3.45</v>
       </c>
       <c r="H27" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I27" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="K27" t="n">
         <v>3.05</v>
@@ -5628,149 +5628,149 @@
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="N27" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="O27" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="P27" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q27" t="n">
         <v>3.05</v>
       </c>
       <c r="R27" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="V27" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W27" t="n">
         <v>1.4</v>
       </c>
       <c r="X27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF27" t="n">
         <v>8</v>
       </c>
-      <c r="Y27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>1.16</v>
-      </c>
       <c r="BG27" t="n">
-        <v>1.16</v>
+        <v>7.8</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -5801,31 +5801,31 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G28" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="H28" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I28" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J28" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K28" t="n">
         <v>4.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
         <v>1.04</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O28" t="n">
         <v>1.2</v>
@@ -5834,13 +5834,13 @@
         <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R28" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -5849,16 +5849,16 @@
         <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W28" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z28" t="n">
         <v>1000</v>
@@ -5867,13 +5867,13 @@
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC28" t="n">
         <v>13</v>
       </c>
       <c r="AD28" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE28" t="n">
         <v>1000</v>
@@ -5909,62 +5909,62 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="AT28" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AU28" t="n">
         <v>2.42</v>
       </c>
-      <c r="AU28" t="n">
-        <v>2.36</v>
-      </c>
       <c r="AV28" t="n">
-        <v>15</v>
+        <v>2.66</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AX28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AY28" t="n">
         <v>2.44</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>2.38</v>
       </c>
       <c r="AZ28" t="n">
         <v>13.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BB28" t="n">
-        <v>2.58</v>
+        <v>13.5</v>
       </c>
       <c r="BC28" t="n">
         <v>12.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="BF28" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -6001,16 +6001,16 @@
         <v>1.21</v>
       </c>
       <c r="H29" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="I29" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J29" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="L29" t="n">
         <v>1.16</v>
@@ -6025,37 +6025,37 @@
         <v>1.09</v>
       </c>
       <c r="P29" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="R29" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S29" t="n">
         <v>1.72</v>
       </c>
       <c r="T29" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U29" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="X29" t="n">
         <v>60</v>
       </c>
       <c r="Y29" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="Z29" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
@@ -6115,7 +6115,7 @@
         <v>6.8</v>
       </c>
       <c r="AT29" t="n">
-        <v>13.5</v>
+        <v>5</v>
       </c>
       <c r="AU29" t="n">
         <v>5.5</v>
@@ -6127,7 +6127,7 @@
         <v>6.8</v>
       </c>
       <c r="AX29" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY29" t="n">
         <v>10.5</v>
@@ -6154,11 +6154,11 @@
         <v>2.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G30" t="n">
         <v>1.8</v>
@@ -6240,7 +6240,7 @@
         <v>1.27</v>
       </c>
       <c r="W30" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X30" t="n">
         <v>26</v>
@@ -6264,7 +6264,7 @@
         <v>18</v>
       </c>
       <c r="AE30" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF30" t="n">
         <v>14</v>
@@ -6276,10 +6276,10 @@
         <v>15.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ30" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK30" t="n">
         <v>15.5</v>
@@ -6303,10 +6303,10 @@
         <v>24</v>
       </c>
       <c r="AR30" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS30" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AT30" t="n">
         <v>13.5</v>
@@ -6339,7 +6339,7 @@
         <v>14.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE30" t="n">
         <v>50</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -6419,19 +6419,19 @@
         <v>1.42</v>
       </c>
       <c r="R31" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S31" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T31" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U31" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="V31" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W31" t="n">
         <v>2.72</v>
@@ -6464,13 +6464,13 @@
         <v>13.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH31" t="n">
         <v>17.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ31" t="n">
         <v>17</v>
@@ -6479,13 +6479,13 @@
         <v>13.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM31" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN31" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AO31" t="n">
         <v>36</v>
@@ -6497,7 +6497,7 @@
         <v>30</v>
       </c>
       <c r="AR31" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AS31" t="n">
         <v>100</v>
@@ -6512,7 +6512,7 @@
         <v>20</v>
       </c>
       <c r="AW31" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AX31" t="n">
         <v>12.5</v>
@@ -6521,7 +6521,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA31" t="n">
         <v>40</v>
@@ -6533,7 +6533,7 @@
         <v>13</v>
       </c>
       <c r="BD31" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE31" t="n">
         <v>50</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>
@@ -6580,13 +6580,13 @@
         <v>1.65</v>
       </c>
       <c r="G32" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="H32" t="n">
         <v>5.2</v>
       </c>
       <c r="I32" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
         <v>3.7</v>
@@ -6601,16 +6601,16 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="O32" t="n">
         <v>1.28</v>
       </c>
       <c r="P32" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R32" t="n">
         <v>1.28</v>
@@ -6625,10 +6625,10 @@
         <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W32" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-07 00:53:03</t>
+          <t>2026-04-07 03:02:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G2" t="n">
         <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I2" t="n">
         <v>2.28</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G3" t="n">
         <v>2.4</v>
@@ -1011,7 +1011,7 @@
         <v>11.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1095,26 +1095,26 @@
         <v>7.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BE3" t="n">
         <v>8</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BG3" t="n">
         <v>7.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M5" t="n">
         <v>1.11</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="H6" t="n">
         <v>3.3</v>
@@ -1557,7 +1557,7 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
         <v>1.24</v>
@@ -1584,13 +1584,13 @@
         <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="X6" t="n">
         <v>23</v>
       </c>
       <c r="Y6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z6" t="n">
         <v>32</v>
@@ -1605,10 +1605,10 @@
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF6" t="n">
         <v>18</v>
@@ -1635,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO6" t="n">
         <v>34</v>
@@ -1644,7 +1644,7 @@
         <v>14.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR6" t="n">
         <v>20</v>
@@ -1659,7 +1659,7 @@
         <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
         <v>4.5</v>
@@ -1674,7 +1674,7 @@
         <v>12</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB6" t="n">
         <v>20</v>
@@ -1686,7 +1686,7 @@
         <v>4.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF6" t="n">
         <v>10</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
         <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
         <v>2.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G8" t="n">
         <v>1.86</v>
@@ -1936,10 +1936,10 @@
         <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -2312,10 +2312,10 @@
         <v>6.6</v>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="I10" t="n">
         <v>1.58</v>
@@ -2327,7 +2327,7 @@
         <v>5.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
@@ -2357,7 +2357,7 @@
         <v>1.92</v>
       </c>
       <c r="V10" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="W10" t="n">
         <v>1.15</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G12" t="n">
         <v>2.2</v>
@@ -2706,7 +2706,7 @@
         <v>3.85</v>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J12" t="n">
         <v>3.45</v>
@@ -2721,13 +2721,13 @@
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
         <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q12" t="n">
         <v>2.16</v>
@@ -2745,7 +2745,7 @@
         <v>1.92</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
         <v>1.84</v>
@@ -2811,7 +2811,7 @@
         <v>4.3</v>
       </c>
       <c r="AR12" t="n">
-        <v>25</v>
+        <v>4.8</v>
       </c>
       <c r="AS12" t="n">
         <v>5.4</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -2891,58 +2891,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>1.3</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="J13" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="K13" t="n">
         <v>950</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O13" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>2.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.72</v>
       </c>
       <c r="S13" t="n">
-        <v>1.09</v>
+        <v>1.81</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2993,68 +2993,68 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>1.6</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="J14" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3109,34 +3109,34 @@
         <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>2.84</v>
       </c>
       <c r="O14" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>2.84</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.08</v>
+        <v>1.42</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.08</v>
+        <v>1.98</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M15" t="n">
         <v>1.04</v>
       </c>
-      <c r="G15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.03</v>
-      </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.17</v>
+        <v>1.56</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="S15" t="n">
-        <v>1.17</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ15" t="n">
         <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -3488,10 +3488,10 @@
         <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
@@ -3566,7 +3566,7 @@
         <v>40</v>
       </c>
       <c r="AK16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL16" t="n">
         <v>44</v>
@@ -3584,7 +3584,7 @@
         <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR16" t="n">
         <v>17.5</v>
@@ -3629,14 +3629,14 @@
         <v>38</v>
       </c>
       <c r="BF16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG16" t="n">
         <v>27</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -3870,16 +3870,16 @@
         <v>1.68</v>
       </c>
       <c r="I18" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="J18" t="n">
         <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
@@ -3900,7 +3900,7 @@
         <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T18" t="n">
         <v>1.74</v>
@@ -3909,10 +3909,10 @@
         <v>2.12</v>
       </c>
       <c r="V18" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="W18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4011,20 +4011,20 @@
         <v>8.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.4</v>
+        <v>50</v>
       </c>
       <c r="BE18" t="n">
         <v>9</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.6</v>
+        <v>50</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -4058,10 +4058,10 @@
         <v>2.04</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="H19" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="I19" t="n">
         <v>4.1</v>
@@ -4076,149 +4076,149 @@
         <v>1.32</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
         <v>1.72</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V19" t="n">
         <v>1.32</v>
       </c>
       <c r="W19" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AC19" t="n">
         <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AE19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF19" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AG19" t="n">
         <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AI19" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ19" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK19" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AO19" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.6</v>
+        <v>12.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.6</v>
+        <v>4.3</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.44</v>
+        <v>4.7</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.62</v>
+        <v>5.3</v>
       </c>
       <c r="AT19" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU19" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AY19" t="n">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
       <c r="AZ19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF19" t="n">
         <v>11</v>
       </c>
-      <c r="BA19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BG19" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
         <v>4.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M20" t="n">
         <v>1.03</v>
@@ -4288,7 +4288,7 @@
         <v>1.59</v>
       </c>
       <c r="S20" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="T20" t="n">
         <v>1.56</v>
@@ -4297,7 +4297,7 @@
         <v>2.52</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
         <v>1.83</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -4467,13 +4467,13 @@
         <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O21" t="n">
         <v>1.18</v>
       </c>
       <c r="P21" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
         <v>1.63</v>
@@ -4491,10 +4491,10 @@
         <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -4831,170 +4831,170 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G23" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H23" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I23" t="n">
         <v>3.4</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K23" t="n">
         <v>4.1</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>2.22</v>
+        <v>4.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P23" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
         <v>1.75</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V23" t="n">
         <v>1.41</v>
       </c>
       <c r="W23" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
         <v>4.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M24" t="n">
         <v>1.03</v>
@@ -5058,7 +5058,7 @@
         <v>2.42</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R24" t="n">
         <v>1.57</v>
@@ -5073,7 +5073,7 @@
         <v>2.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
         <v>1.75</v>
@@ -5094,7 +5094,7 @@
         <v>17</v>
       </c>
       <c r="AC24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD24" t="n">
         <v>17.5</v>
@@ -5154,7 +5154,7 @@
         <v>10.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AX24" t="n">
         <v>12</v>
@@ -5166,10 +5166,10 @@
         <v>11</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BB24" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BC24" t="n">
         <v>15</v>
@@ -5178,7 +5178,7 @@
         <v>20</v>
       </c>
       <c r="BE24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF24" t="n">
         <v>8.6</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -5225,13 +5225,13 @@
         <v>2.1</v>
       </c>
       <c r="H25" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I25" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K25" t="n">
         <v>3.8</v>
@@ -5267,10 +5267,10 @@
         <v>1.89</v>
       </c>
       <c r="V25" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W25" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X25" t="n">
         <v>14</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -5416,76 +5416,76 @@
         <v>4.9</v>
       </c>
       <c r="G26" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H26" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="I26" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="J26" t="n">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="K26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N26" t="n">
-        <v>1.97</v>
+        <v>2.32</v>
       </c>
       <c r="O26" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="P26" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="R26" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S26" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="V26" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="W26" t="n">
         <v>1.18</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE26" t="n">
         <v>1000</v>
@@ -5521,62 +5521,62 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -5607,25 +5607,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H27" t="n">
         <v>2.84</v>
       </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="J27" t="n">
         <v>2.66</v>
       </c>
       <c r="K27" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M27" t="n">
         <v>1.17</v>
@@ -5649,16 +5649,16 @@
         <v>6.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U27" t="n">
         <v>1.62</v>
       </c>
       <c r="V27" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W27" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X27" t="n">
         <v>6.8</v>
@@ -5679,7 +5679,7 @@
         <v>7.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
@@ -5715,16 +5715,16 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ27" t="n">
         <v>6.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT27" t="n">
         <v>6.8</v>
@@ -5736,7 +5736,7 @@
         <v>12.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX27" t="n">
         <v>16</v>
@@ -5745,32 +5745,32 @@
         <v>13</v>
       </c>
       <c r="AZ27" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BA27" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB27" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC27" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BD27" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE27" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
         <v>1.67</v>
       </c>
       <c r="G28" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="H28" t="n">
         <v>4.7</v>
@@ -5813,22 +5813,22 @@
         <v>6.2</v>
       </c>
       <c r="J28" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K28" t="n">
         <v>4.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M28" t="n">
         <v>1.04</v>
       </c>
       <c r="N28" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P28" t="n">
         <v>2.2</v>
@@ -5837,134 +5837,134 @@
         <v>1.67</v>
       </c>
       <c r="R28" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S28" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V28" t="n">
         <v>1.19</v>
       </c>
       <c r="W28" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y28" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
         <v>13.5</v>
       </c>
-      <c r="AC28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
+      <c r="AG28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
         <v>15.5</v>
       </c>
-      <c r="AG28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>2.96</v>
-      </c>
       <c r="AQ28" t="n">
-        <v>2.68</v>
+        <v>16.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.82</v>
+        <v>4.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.96</v>
+        <v>4.8</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.44</v>
+        <v>8.4</v>
       </c>
       <c r="AU28" t="n">
-        <v>2.42</v>
+        <v>7.8</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.66</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="AX28" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="AY28" t="n">
-        <v>2.44</v>
+        <v>7.8</v>
       </c>
       <c r="AZ28" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="BB28" t="n">
         <v>13.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD28" t="n">
-        <v>2.78</v>
+        <v>4.3</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.96</v>
+        <v>4.7</v>
       </c>
       <c r="BF28" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G29" t="n">
         <v>1.21</v>
       </c>
       <c r="H29" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="I29" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="L29" t="n">
         <v>1.16</v>
@@ -6043,19 +6043,19 @@
         <v>2</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="X29" t="n">
         <v>60</v>
       </c>
       <c r="Y29" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="Z29" t="n">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
@@ -6067,10 +6067,10 @@
         <v>25</v>
       </c>
       <c r="AD29" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AE29" t="n">
-        <v>350</v>
+        <v>290</v>
       </c>
       <c r="AF29" t="n">
         <v>12</v>
@@ -6082,7 +6082,7 @@
         <v>36</v>
       </c>
       <c r="AI29" t="n">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="AJ29" t="n">
         <v>12</v>
@@ -6100,31 +6100,31 @@
         <v>2.92</v>
       </c>
       <c r="AO29" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="AP29" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV29" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR29" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AW29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX29" t="n">
         <v>9.199999999999999</v>
@@ -6133,10 +6133,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BA29" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB29" t="n">
         <v>9</v>
@@ -6145,20 +6145,20 @@
         <v>11</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF29" t="n">
         <v>2.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G30" t="n">
         <v>1.8</v>
@@ -6222,13 +6222,13 @@
         <v>2.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R30" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S30" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T30" t="n">
         <v>1.57</v>
@@ -6240,7 +6240,7 @@
         <v>1.27</v>
       </c>
       <c r="W30" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X30" t="n">
         <v>26</v>
@@ -6300,10 +6300,10 @@
         <v>24</v>
       </c>
       <c r="AQ30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR30" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS30" t="n">
         <v>80</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -6428,10 +6428,10 @@
         <v>1.53</v>
       </c>
       <c r="U31" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="V31" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W31" t="n">
         <v>2.72</v>
@@ -6446,7 +6446,7 @@
         <v>55</v>
       </c>
       <c r="AA31" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="AB31" t="n">
         <v>16</v>
@@ -6464,16 +6464,16 @@
         <v>13.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>17</v>
       </c>
       <c r="AK31" t="n">
         <v>13.5</v>
@@ -6482,7 +6482,7 @@
         <v>21</v>
       </c>
       <c r="AM31" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN31" t="n">
         <v>5</v>
@@ -6497,7 +6497,7 @@
         <v>30</v>
       </c>
       <c r="AR31" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AS31" t="n">
         <v>100</v>
@@ -6512,7 +6512,7 @@
         <v>20</v>
       </c>
       <c r="AW31" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX31" t="n">
         <v>12.5</v>
@@ -6527,10 +6527,10 @@
         <v>40</v>
       </c>
       <c r="BB31" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC31" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD31" t="n">
         <v>19.5</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
         <v>1.65</v>
       </c>
       <c r="G32" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="H32" t="n">
         <v>5.2</v>
@@ -6598,37 +6598,37 @@
         <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="O32" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P32" t="n">
         <v>1.91</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V32" t="n">
         <v>1.18</v>
       </c>
       <c r="W32" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -6685,62 +6685,62 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-07 03:02:33</t>
+          <t>2026-04-07 05:12:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,19 +763,19 @@
         <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="I2" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -787,7 +787,7 @@
         <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q2" t="n">
         <v>1.85</v>
@@ -799,13 +799,13 @@
         <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U2" t="n">
         <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W2" t="n">
         <v>1.34</v>
@@ -826,7 +826,7 @@
         <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>970</v>
@@ -841,10 +841,10 @@
         <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="n">
         <v>85</v>
@@ -853,7 +853,7 @@
         <v>55</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM2" t="n">
         <v>100</v>
@@ -865,62 +865,62 @@
         <v>970</v>
       </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AU2" t="n">
         <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AX2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA2" t="n">
         <v>6.2</v>
       </c>
-      <c r="AY2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA2" t="n">
+      <c r="BB2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE2" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BF2" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.4</v>
+        <v>12.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
         <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.46</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>2.84</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.33</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -1345,13 +1345,13 @@
         <v>3.2</v>
       </c>
       <c r="H5" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="I5" t="n">
         <v>2.74</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
         <v>3.4</v>
@@ -1402,7 +1402,7 @@
         <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB5" t="n">
         <v>11</v>
@@ -1468,10 +1468,10 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AY5" t="n">
         <v>11.5</v>
@@ -1480,13 +1480,13 @@
         <v>5.6</v>
       </c>
       <c r="BA5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB5" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BC5" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6.4</v>
       </c>
       <c r="BD5" t="n">
         <v>50</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="H6" t="n">
         <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
         <v>3.65</v>
@@ -1584,7 +1584,7 @@
         <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="X6" t="n">
         <v>23</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -1730,28 +1730,28 @@
         <v>14</v>
       </c>
       <c r="G7" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="H7" t="n">
         <v>1.29</v>
       </c>
       <c r="I7" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="J7" t="n">
         <v>5.3</v>
       </c>
       <c r="K7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.3</v>
@@ -1760,7 +1760,7 @@
         <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="R7" t="n">
         <v>1.35</v>
@@ -1772,13 +1772,13 @@
         <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="V7" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
         <v>17.5</v>
@@ -1793,10 +1793,10 @@
         <v>11</v>
       </c>
       <c r="AB7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AC7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD7" t="n">
         <v>13</v>
@@ -1808,7 +1808,7 @@
         <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AH7" t="n">
         <v>46</v>
@@ -1847,7 +1847,7 @@
         <v>8</v>
       </c>
       <c r="AT7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU7" t="n">
         <v>11.5</v>
@@ -1859,38 +1859,38 @@
         <v>14.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA7" t="n">
         <v>6.4</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BB7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC7" t="n">
         <v>7</v>
       </c>
-      <c r="BC7" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG7" t="n">
         <v>5.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -1924,55 +1924,55 @@
         <v>1.71</v>
       </c>
       <c r="G8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="O8" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="P8" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="U8" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="V8" t="n">
         <v>1.14</v>
       </c>
       <c r="W8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X8" t="n">
         <v>9</v>
@@ -1993,7 +1993,7 @@
         <v>9.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2023,34 +2023,34 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
         <v>12</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AX8" t="n">
         <v>7.6</v>
@@ -2059,32 +2059,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BA8" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BF8" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -2115,64 +2115,64 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="H9" t="n">
         <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S9" t="n">
         <v>1.01</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.33</v>
-      </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2181,10 +2181,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2196,7 +2196,7 @@
         <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
         <v>1000</v>
@@ -2223,69 +2223,69 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,90 +2295,90 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12:55:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>FK Javor Ivanjica</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Zeleznicar Pancevo</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6.6</v>
+        <v>2.68</v>
       </c>
       <c r="G10" t="n">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.48</v>
+        <v>2.38</v>
       </c>
       <c r="I10" t="n">
-        <v>1.58</v>
+        <v>3.15</v>
       </c>
       <c r="J10" t="n">
-        <v>4.4</v>
+        <v>2.74</v>
       </c>
       <c r="K10" t="n">
-        <v>5.2</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>2.42</v>
       </c>
       <c r="O10" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="P10" t="n">
-        <v>2.08</v>
+        <v>1.52</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="S10" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="T10" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>2.72</v>
+        <v>1.46</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="X10" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
         <v>1000</v>
@@ -2414,72 +2414,72 @@
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,90 +2489,90 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:55:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Al-Feiha</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Radnicki Nis</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>1.57</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P11" t="n">
-        <v>1.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.27</v>
+        <v>1.83</v>
       </c>
       <c r="R11" t="n">
-        <v>1.08</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>1.27</v>
+        <v>2.92</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AB11" t="n">
         <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
@@ -2608,72 +2608,72 @@
         <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Greek Super League</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.04</v>
+        <v>1.25</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="H12" t="n">
-        <v>3.85</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>950</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
         <v>4.5</v>
       </c>
-      <c r="J12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>4.1</v>
       </c>
-      <c r="T12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="X12" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
+      <c r="AR12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV12" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AW12" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AX12" t="n">
-        <v>10.5</v>
+        <v>3.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Parnu JK Vaprus</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L13" t="n">
         <v>1.21</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I13" t="n">
-        <v>21</v>
-      </c>
-      <c r="J13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>950</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.18</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P13" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="R13" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="S13" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="T13" t="n">
-        <v>1.96</v>
+        <v>1.62</v>
       </c>
       <c r="U13" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY13" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS13" t="n">
+      <c r="AZ13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB13" t="n">
         <v>4.5</v>
       </c>
-      <c r="AT13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW13" t="n">
+      <c r="BC13" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BD13" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -3076,112 +3076,112 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nomme Utd</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.54</v>
+        <v>5.7</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="H14" t="n">
-        <v>4.6</v>
+        <v>1.52</v>
       </c>
       <c r="I14" t="n">
-        <v>8.6</v>
+        <v>1.61</v>
       </c>
       <c r="J14" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K14" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M14" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>2.84</v>
+        <v>3.65</v>
       </c>
       <c r="O14" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>2.84</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>1.98</v>
+        <v>2.72</v>
       </c>
       <c r="T14" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>2.62</v>
       </c>
       <c r="W14" t="n">
-        <v>2.66</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ14" t="n">
         <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
@@ -3190,72 +3190,72 @@
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5.7</v>
+        <v>2.02</v>
       </c>
       <c r="G15" t="n">
-        <v>8.4</v>
+        <v>2.2</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="I15" t="n">
-        <v>1.58</v>
+        <v>4.5</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="K15" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="L15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.27</v>
       </c>
-      <c r="M15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.52</v>
-      </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="U15" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="V15" t="n">
-        <v>2.72</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.84</v>
       </c>
       <c r="X15" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z15" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>32</v>
+        <v>9.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AE15" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="AG15" t="n">
-        <v>30</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
         <v>25</v>
       </c>
       <c r="AI15" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
         <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AN15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.55</v>
+        <v>5.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="AW15" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>4.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.2</v>
+        <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Radnicki Nis</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.62</v>
+        <v>1.47</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7</v>
+        <v>1.59</v>
       </c>
       <c r="H16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X16" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT16" t="n">
         <v>2.94</v>
       </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="AU16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BC16" t="n">
         <v>3.55</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>26</v>
-      </c>
       <c r="BD16" t="n">
-        <v>36</v>
+        <v>3.95</v>
       </c>
       <c r="BE16" t="n">
-        <v>38</v>
+        <v>4.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>23</v>
+        <v>3.05</v>
       </c>
       <c r="BG16" t="n">
-        <v>27</v>
+        <v>4.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Napredak</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="O17" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="P17" t="n">
-        <v>1.08</v>
+        <v>1.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.4</v>
+        <v>2.08</v>
       </c>
       <c r="R17" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>26</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Goztepe</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Viktoria Koln</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5.5</v>
+        <v>2.26</v>
       </c>
       <c r="G18" t="n">
-        <v>5.9</v>
+        <v>2.52</v>
       </c>
       <c r="H18" t="n">
-        <v>1.68</v>
+        <v>2.86</v>
       </c>
       <c r="I18" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="R18" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="T18" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>2.34</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2</v>
+        <v>1.65</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,179 +4046,179 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Umraniyespor</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>2.54</v>
       </c>
       <c r="H19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I19" t="n">
         <v>3.4</v>
-      </c>
-      <c r="I19" t="n">
-        <v>4.1</v>
       </c>
       <c r="J19" t="n">
         <v>3.45</v>
       </c>
       <c r="K19" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="T19" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="U19" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB19" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AC19" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AF19" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AJ19" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL19" t="n">
         <v>40</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN19" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AP19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX19" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>11</v>
-      </c>
       <c r="AY19" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE19" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BF19" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SSV Ulm</t>
+          <t>TSV Havelse</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.04</v>
+        <v>1.54</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="H20" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>7.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="K20" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -4434,179 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Viktoria Koln</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="G21" t="n">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="H21" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="I21" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="J21" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="S21" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TSV Havelse</t>
+          <t>SSV Ulm</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="G22" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="H22" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="I22" t="n">
-        <v>6.8</v>
+        <v>3.95</v>
       </c>
       <c r="J22" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="K22" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>FK Napredak</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.26</v>
+        <v>1.59</v>
       </c>
       <c r="G23" t="n">
-        <v>2.54</v>
+        <v>1.72</v>
       </c>
       <c r="H23" t="n">
-        <v>2.94</v>
+        <v>4.5</v>
       </c>
       <c r="I23" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
         <v>4.1</v>
       </c>
-      <c r="L23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X23" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>13</v>
-      </c>
       <c r="AQ23" t="n">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>17.5</v>
+        <v>5</v>
       </c>
       <c r="AS23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD23" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BE23" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF23" t="n">
-        <v>12.5</v>
+        <v>3.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>20</v>
+        <v>5.3</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Umraniyespor</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="G24" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="H24" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I24" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="K24" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="L24" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="M24" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="O24" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="P24" t="n">
-        <v>2.42</v>
+        <v>2.02</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="R24" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="S24" t="n">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="U24" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="X24" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Z24" t="n">
         <v>32</v>
       </c>
       <c r="AA24" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF24" t="n">
         <v>17</v>
       </c>
-      <c r="AC24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>21</v>
-      </c>
       <c r="AG24" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI24" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AJ24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK24" t="n">
         <v>26</v>
       </c>
       <c r="AL24" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AM24" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AO24" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AP24" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>19</v>
+        <v>4.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AT24" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="AX24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY24" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>15</v>
+        <v>4.3</v>
       </c>
       <c r="BD24" t="n">
-        <v>20</v>
+        <v>4.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF24" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>16.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Goztepe</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.87</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P25" t="n">
         <v>2.1</v>
       </c>
-      <c r="H25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I25" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.72</v>
-      </c>
       <c r="Q25" t="n">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="T25" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="U25" t="n">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="V25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.22</v>
       </c>
-      <c r="W25" t="n">
-        <v>1.92</v>
-      </c>
       <c r="X25" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="Z25" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="AA25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>140</v>
       </c>
-      <c r="AB25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>24</v>
-      </c>
       <c r="AK25" t="n">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="AL25" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AM25" t="n">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="AN25" t="n">
-        <v>970</v>
+        <v>70</v>
       </c>
       <c r="AO25" t="n">
-        <v>110</v>
+        <v>10.5</v>
       </c>
       <c r="AP25" t="n">
-        <v>5.3</v>
+        <v>15.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AS25" t="n">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AW25" t="n">
-        <v>3.25</v>
+        <v>15.5</v>
       </c>
       <c r="AX25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY25" t="n">
-        <v>4.8</v>
+        <v>17.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.96</v>
+        <v>27</v>
       </c>
       <c r="BB25" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.2</v>
+        <v>50</v>
       </c>
       <c r="BE25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BF25" t="n">
-        <v>5.8</v>
+        <v>50</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.97</v>
+        <v>8.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,184 +5399,184 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X26" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AX26" t="n">
         <v>4.9</v>
       </c>
-      <c r="G26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="AY26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>6</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Y26" t="n">
+      <c r="BA26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB26" t="n">
         <v>6.2</v>
       </c>
-      <c r="Z26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC26" t="n">
+      <c r="BC26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE26" t="n">
         <v>8</v>
       </c>
-      <c r="AD26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BF26" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.4</v>
+        <v>1.96</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="G27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K27" t="n">
         <v>3.35</v>
       </c>
-      <c r="H27" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="I27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2.98</v>
-      </c>
       <c r="L27" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.17</v>
       </c>
-      <c r="N27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="X27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
         <v>6.8</v>
       </c>
-      <c r="T27" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X27" t="n">
+      <c r="AQ27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>6.8</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="BA27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC27" t="n">
         <v>7.8</v>
       </c>
-      <c r="Z27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ27" t="n">
+      <c r="BD27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG27" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,179 +5792,179 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NEOM Sports Club</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L28" t="n">
         <v>1.67</v>
       </c>
-      <c r="G28" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="H28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I28" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.32</v>
-      </c>
       <c r="M28" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="N28" t="n">
-        <v>4.5</v>
+        <v>2.22</v>
       </c>
       <c r="O28" t="n">
-        <v>1.23</v>
+        <v>1.71</v>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>1.39</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.67</v>
+        <v>3.05</v>
       </c>
       <c r="R28" t="n">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="S28" t="n">
-        <v>2.66</v>
+        <v>6.8</v>
       </c>
       <c r="T28" t="n">
-        <v>1.69</v>
+        <v>2.28</v>
       </c>
       <c r="U28" t="n">
-        <v>2.16</v>
+        <v>1.62</v>
       </c>
       <c r="V28" t="n">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="W28" t="n">
-        <v>2.2</v>
+        <v>1.42</v>
       </c>
       <c r="X28" t="n">
-        <v>24</v>
+        <v>6.8</v>
       </c>
       <c r="Y28" t="n">
-        <v>25</v>
+        <v>7.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV28" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT28" t="n">
+      <c r="AW28" t="n">
         <v>8.4</v>
       </c>
-      <c r="AU28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AX28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF28" t="n">
         <v>9</v>
       </c>
-      <c r="AY28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG28" t="n">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -5986,186 +5986,186 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.17</v>
+        <v>1.68</v>
       </c>
       <c r="G29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V29" t="n">
         <v>1.21</v>
       </c>
-      <c r="H29" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="I29" t="n">
-        <v>23</v>
-      </c>
-      <c r="J29" t="n">
+      <c r="W29" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X29" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY29" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="K29" t="n">
-        <v>10</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N29" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P29" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W29" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="X29" t="n">
-        <v>60</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>110</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>250</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>25</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>85</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>290</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG29" t="n">
+      <c r="AZ29" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB29" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH29" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>190</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>250</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ29" t="n">
+      <c r="BC29" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF29" t="n">
         <v>6.8</v>
       </c>
-      <c r="AR29" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>2.5</v>
-      </c>
       <c r="BG29" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,184 +6175,184 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="F30" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>20</v>
+      </c>
+      <c r="J30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K30" t="n">
+        <v>10</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S30" t="n">
         <v>1.79</v>
       </c>
-      <c r="G30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H30" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I30" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N30" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.32</v>
-      </c>
       <c r="T30" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="U30" t="n">
-        <v>2.66</v>
+        <v>2.02</v>
       </c>
       <c r="V30" t="n">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>2.24</v>
+        <v>5.7</v>
       </c>
       <c r="X30" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="Y30" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>220</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC30" t="n">
         <v>25</v>
       </c>
-      <c r="Z30" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC30" t="n">
+      <c r="AD30" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>220</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY30" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD30" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>24</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>23</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>80</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AZ30" t="n">
-        <v>14.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA30" t="n">
-        <v>40</v>
+        <v>7.2</v>
       </c>
       <c r="BB30" t="n">
-        <v>18.5</v>
+        <v>9</v>
       </c>
       <c r="BC30" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BD30" t="n">
-        <v>22</v>
+        <v>6.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>50</v>
+        <v>7.2</v>
       </c>
       <c r="BF30" t="n">
-        <v>6.4</v>
+        <v>2.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>29</v>
+        <v>7.4</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G31" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H31" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I31" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J31" t="n">
         <v>5.2</v>
@@ -6419,7 +6419,7 @@
         <v>1.42</v>
       </c>
       <c r="R31" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S31" t="n">
         <v>2.04</v>
@@ -6431,10 +6431,10 @@
         <v>2.74</v>
       </c>
       <c r="V31" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W31" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="X31" t="n">
         <v>38</v>
@@ -6473,7 +6473,7 @@
         <v>46</v>
       </c>
       <c r="AJ31" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK31" t="n">
         <v>13.5</v>
@@ -6506,7 +6506,7 @@
         <v>14.5</v>
       </c>
       <c r="AU31" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV31" t="n">
         <v>20</v>
@@ -6533,27 +6533,27 @@
         <v>12.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE31" t="n">
         <v>50</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG31" t="n">
         <v>32</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-07 05:12:08</t>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,184 +6563,378 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Paris St-G</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="G32" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="H32" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="I32" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="J32" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="K32" t="n">
         <v>4.4</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X32" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>75</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:21:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Ecu)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M33" t="n">
         <v>1.06</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N33" t="n">
         <v>3.6</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O33" t="n">
         <v>1.3</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P33" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q33" t="n">
         <v>1.87</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R33" t="n">
         <v>1.35</v>
       </c>
-      <c r="S32" t="n">
+      <c r="S33" t="n">
         <v>3.25</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T33" t="n">
         <v>1.84</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U33" t="n">
         <v>1.94</v>
       </c>
-      <c r="V32" t="n">
+      <c r="V33" t="n">
         <v>1.18</v>
       </c>
-      <c r="W32" t="n">
+      <c r="W33" t="n">
         <v>2.18</v>
       </c>
-      <c r="X32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP32" t="n">
+      <c r="X33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
         <v>5.7</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AQ33" t="n">
         <v>6</v>
       </c>
-      <c r="AR32" t="n">
+      <c r="AR33" t="n">
         <v>7.4</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AS33" t="n">
         <v>8.4</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="AT33" t="n">
         <v>4.4</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AU33" t="n">
         <v>4.5</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AV33" t="n">
         <v>6.4</v>
       </c>
-      <c r="AW32" t="n">
+      <c r="AW33" t="n">
         <v>3.55</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="AX33" t="n">
         <v>4.9</v>
       </c>
-      <c r="AY32" t="n">
+      <c r="AY33" t="n">
         <v>4.8</v>
       </c>
-      <c r="AZ32" t="n">
+      <c r="AZ33" t="n">
         <v>6.2</v>
       </c>
-      <c r="BA32" t="n">
+      <c r="BA33" t="n">
         <v>3.55</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BB33" t="n">
         <v>14.5</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BC33" t="n">
         <v>6</v>
       </c>
-      <c r="BD32" t="n">
+      <c r="BD33" t="n">
         <v>7.2</v>
       </c>
-      <c r="BE32" t="n">
+      <c r="BE33" t="n">
         <v>2.7</v>
       </c>
-      <c r="BF32" t="n">
+      <c r="BF33" t="n">
         <v>8</v>
       </c>
-      <c r="BG32" t="n">
+      <c r="BG33" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2026-04-07 05:12:08</t>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:21:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -766,10 +766,10 @@
         <v>2.06</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>3.95</v>
@@ -790,7 +790,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="n">
         <v>1.38</v>
@@ -799,16 +799,16 @@
         <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U2" t="n">
         <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X2" t="n">
         <v>20</v>
@@ -868,16 +868,16 @@
         <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS2" t="n">
         <v>4.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="AU2" t="n">
         <v>7.6</v>
@@ -886,7 +886,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AX2" t="n">
         <v>4.3</v>
@@ -895,13 +895,13 @@
         <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC2" t="n">
         <v>4.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G3" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="I3" t="n">
         <v>3.15</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.48</v>
@@ -975,34 +975,34 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U3" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
         <v>1.47</v>
       </c>
       <c r="W3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X3" t="n">
         <v>11.5</v>
@@ -1023,28 +1023,28 @@
         <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF3" t="n">
         <v>18.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1065,10 +1065,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT3" t="n">
         <v>8.6</v>
@@ -1080,7 +1080,7 @@
         <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX3" t="n">
         <v>15.5</v>
@@ -1089,32 +1089,32 @@
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB3" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BC3" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC3" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BD3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG3" t="n">
         <v>7.6</v>
       </c>
-      <c r="BE3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G4" t="n">
         <v>2.36</v>
@@ -1163,19 +1163,19 @@
         <v>3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q4" t="n">
         <v>2.42</v>
@@ -1205,7 +1205,7 @@
         <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
@@ -1223,7 +1223,7 @@
         <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
@@ -1253,16 +1253,16 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT4" t="n">
         <v>6.6</v>
@@ -1283,13 +1283,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA4" t="n">
         <v>60</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.6</v>
+        <v>17</v>
       </c>
       <c r="BC4" t="n">
         <v>25</v>
@@ -1298,17 +1298,17 @@
         <v>44</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF4" t="n">
         <v>22</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G5" t="n">
         <v>3.3</v>
       </c>
       <c r="H5" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I5" t="n">
         <v>2.9</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.46</v>
@@ -1369,10 +1369,10 @@
         <v>1.38</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="R5" t="n">
         <v>1.3</v>
@@ -1384,25 +1384,25 @@
         <v>1.81</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
         <v>1.52</v>
       </c>
       <c r="W5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y5" t="n">
         <v>10.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA5" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB5" t="n">
         <v>11</v>
@@ -1411,7 +1411,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>85</v>
@@ -1420,22 +1420,22 @@
         <v>22</v>
       </c>
       <c r="AG5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
         <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
@@ -1450,13 +1450,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR5" t="n">
         <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AT5" t="n">
         <v>9.4</v>
@@ -1468,41 +1468,41 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="AX5" t="n">
         <v>17</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.6</v>
+        <v>40</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.6</v>
+        <v>38</v>
       </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -1545,13 +1545,13 @@
         <v>1.74</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
         <v>4.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1563,10 +1563,10 @@
         <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="R6" t="n">
         <v>1.3</v>
@@ -1575,7 +1575,7 @@
         <v>2.58</v>
       </c>
       <c r="T6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U6" t="n">
         <v>1.77</v>
@@ -1587,40 +1587,40 @@
         <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z6" t="n">
         <v>10</v>
       </c>
       <c r="AA6" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
         <v>11.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AF6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AH6" t="n">
         <v>28</v>
       </c>
       <c r="AI6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ6" t="n">
         <v>1000</v>
@@ -1638,7 +1638,7 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AP6" t="n">
         <v>5.6</v>
@@ -1653,50 +1653,50 @@
         <v>7</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.78</v>
+        <v>4.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.52</v>
+        <v>3.85</v>
       </c>
       <c r="AV6" t="n">
         <v>7</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX6" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>2.92</v>
+        <v>5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.84</v>
+        <v>4.9</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.96</v>
+        <v>5.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.58</v>
+        <v>4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -1727,25 +1727,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="H7" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="I7" t="n">
-        <v>3.65</v>
+        <v>2.72</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
@@ -1766,31 +1766,31 @@
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="U7" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="V7" t="n">
         <v>1.58</v>
       </c>
       <c r="W7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="AB7" t="n">
         <v>13</v>
@@ -1799,98 +1799,98 @@
         <v>7.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AF7" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AG7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH7" t="n">
         <v>21</v>
       </c>
-      <c r="AH7" t="n">
-        <v>29</v>
-      </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
         <v>70</v>
       </c>
       <c r="AK7" t="n">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="AL7" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AM7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
         <v>55</v>
       </c>
       <c r="AO7" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AP7" t="n">
         <v>5.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.74</v>
+        <v>4.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.74</v>
+        <v>4.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.4</v>
+        <v>3.95</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.98</v>
+        <v>5.1</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.25</v>
+        <v>6.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.25</v>
+        <v>6.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.35</v>
+        <v>7.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.25</v>
+        <v>6.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -1921,124 +1921,124 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.51</v>
+        <v>1.92</v>
       </c>
       <c r="G8" t="n">
-        <v>2.48</v>
+        <v>2.18</v>
       </c>
       <c r="H8" t="n">
-        <v>2.68</v>
+        <v>3.55</v>
       </c>
       <c r="I8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD8" t="n">
         <v>19</v>
       </c>
-      <c r="J8" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AP8" t="n">
         <v>5.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.42</v>
+        <v>7.2</v>
       </c>
       <c r="AT8" t="n">
         <v>4.4</v>
@@ -2047,44 +2047,44 @@
         <v>4.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.64</v>
+        <v>5.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.7</v>
+        <v>7</v>
       </c>
       <c r="AX8" t="n">
         <v>5.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.58</v>
+        <v>7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.66</v>
+        <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.42</v>
+        <v>7.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.67</v>
+        <v>6</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -2115,58 +2115,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="H9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>23</v>
+      </c>
+      <c r="J9" t="n">
         <v>4.7</v>
       </c>
-      <c r="I9" t="n">
-        <v>990</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.7</v>
-      </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>2.58</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.48</v>
       </c>
       <c r="V9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2181,7 +2181,7 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC9" t="n">
         <v>1000</v>
@@ -2196,7 +2196,7 @@
         <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AH9" t="n">
         <v>1000</v>
@@ -2205,7 +2205,7 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK9" t="n">
         <v>1000</v>
@@ -2217,16 +2217,16 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR9" t="n">
         <v>4.2</v>
@@ -2235,25 +2235,25 @@
         <v>4.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AW9" t="n">
         <v>4.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.43</v>
+        <v>5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="BA9" t="n">
         <v>4.2</v>
@@ -2262,23 +2262,23 @@
         <v>4.9</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.5</v>
+        <v>7.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.43</v>
+        <v>4</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.55</v>
+        <v>8.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G10" t="n">
         <v>2.28</v>
@@ -2318,7 +2318,7 @@
         <v>3.3</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J10" t="n">
         <v>3.7</v>
@@ -2336,28 +2336,28 @@
         <v>4.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P10" t="n">
         <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S10" t="n">
         <v>2.82</v>
       </c>
       <c r="T10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U10" t="n">
         <v>2.34</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
         <v>1.78</v>
@@ -2366,19 +2366,19 @@
         <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA10" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AB10" t="n">
         <v>14</v>
       </c>
       <c r="AC10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="n">
         <v>17.5</v>
@@ -2387,7 +2387,7 @@
         <v>44</v>
       </c>
       <c r="AF10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG10" t="n">
         <v>13</v>
@@ -2411,68 +2411,68 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO10" t="n">
         <v>34</v>
       </c>
       <c r="AP10" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR10" t="n">
         <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.8</v>
+        <v>25</v>
       </c>
       <c r="AT10" t="n">
         <v>10.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF10" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>10</v>
-      </c>
       <c r="BG10" t="n">
-        <v>4.4</v>
+        <v>22</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H11" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="I11" t="n">
         <v>2.72</v>
@@ -2521,16 +2521,16 @@
         <v>3.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P11" t="n">
         <v>1.61</v>
@@ -2554,10 +2554,10 @@
         <v>1.58</v>
       </c>
       <c r="W11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y11" t="n">
         <v>8.4</v>
@@ -2566,7 +2566,7 @@
         <v>16</v>
       </c>
       <c r="AA11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB11" t="n">
         <v>9.199999999999999</v>
@@ -2587,13 +2587,13 @@
         <v>14</v>
       </c>
       <c r="AH11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
         <v>380</v>
       </c>
       <c r="AJ11" t="n">
-        <v>340</v>
+        <v>60</v>
       </c>
       <c r="AK11" t="n">
         <v>44</v>
@@ -2602,7 +2602,7 @@
         <v>70</v>
       </c>
       <c r="AM11" t="n">
-        <v>170</v>
+        <v>450</v>
       </c>
       <c r="AN11" t="n">
         <v>55</v>
@@ -2617,13 +2617,13 @@
         <v>7.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AS11" t="n">
         <v>36</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU11" t="n">
         <v>7</v>
@@ -2632,10 +2632,10 @@
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX11" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY11" t="n">
         <v>12.5</v>
@@ -2644,29 +2644,29 @@
         <v>20</v>
       </c>
       <c r="BA11" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="BB11" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BC11" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="BE11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BF11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG11" t="n">
         <v>28</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="G12" t="n">
-        <v>8.800000000000001</v>
+        <v>2.98</v>
       </c>
       <c r="H12" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="I12" t="n">
-        <v>11.5</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K12" t="n">
         <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>1.27</v>
+        <v>2.72</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC12" t="n">
-        <v>42</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.17</v>
+        <v>14.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.18</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.18</v>
+        <v>15</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.18</v>
+        <v>5.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.18</v>
+        <v>10</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.18</v>
+        <v>9.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.18</v>
+        <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.18</v>
+        <v>15</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.18</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.13</v>
+        <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.18</v>
+        <v>5.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.18</v>
+        <v>5.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.18</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.18</v>
+        <v>5.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.17</v>
+        <v>5.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.55</v>
+        <v>15.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.55</v>
+        <v>16</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
         <v>17</v>
@@ -2930,37 +2930,37 @@
         <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="U13" t="n">
         <v>1.56</v>
       </c>
       <c r="V13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="W13" t="n">
         <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y13" t="n">
         <v>6.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB13" t="n">
         <v>36</v>
       </c>
       <c r="AC13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD13" t="n">
         <v>11.5</v>
@@ -3011,7 +3011,7 @@
         <v>8.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="AU13" t="n">
         <v>11</v>
@@ -3023,25 +3023,25 @@
         <v>14.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.4</v>
+        <v>46</v>
       </c>
       <c r="AZ13" t="n">
         <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BE13" t="n">
         <v>30</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -3085,49 +3085,49 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G14" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I14" t="n">
         <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K14" t="n">
         <v>3.65</v>
       </c>
       <c r="L14" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M14" t="n">
         <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="O14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P14" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
         <v>1.21</v>
       </c>
       <c r="S14" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
         <v>1.7</v>
@@ -3139,7 +3139,7 @@
         <v>2.12</v>
       </c>
       <c r="X14" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y14" t="n">
         <v>29</v>
@@ -3187,25 +3187,25 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ14" t="n">
         <v>13.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS14" t="n">
         <v>10</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU14" t="n">
         <v>7</v>
@@ -3214,41 +3214,41 @@
         <v>20</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX14" t="n">
         <v>7.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
         <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
-        <v>16.5</v>
+        <v>7.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BD14" t="n">
         <v>44</v>
       </c>
       <c r="BE14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.6</v>
+        <v>16.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>2.06</v>
       </c>
       <c r="G15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H15" t="n">
         <v>4.1</v>
@@ -3291,7 +3291,7 @@
         <v>4.9</v>
       </c>
       <c r="J15" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
         <v>3.65</v>
@@ -3306,10 +3306,10 @@
         <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P15" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q15" t="n">
         <v>2.06</v>
@@ -3318,7 +3318,7 @@
         <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="T15" t="n">
         <v>1.84</v>
@@ -3330,22 +3330,22 @@
         <v>1.26</v>
       </c>
       <c r="W15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="X15" t="n">
         <v>14.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="Z15" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC15" t="n">
         <v>9.4</v>
@@ -3387,16 +3387,16 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="AT15" t="n">
         <v>7.6</v>
@@ -3405,10 +3405,10 @@
         <v>6.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
@@ -3417,32 +3417,32 @@
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.2</v>
+        <v>13</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BG15" t="n">
         <v>10.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -3512,13 +3512,13 @@
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V16" t="n">
         <v>1.53</v>
@@ -3533,7 +3533,7 @@
         <v>9.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA16" t="n">
         <v>60</v>
@@ -3545,16 +3545,16 @@
         <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE16" t="n">
         <v>40</v>
       </c>
       <c r="AF16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH16" t="n">
         <v>21</v>
@@ -3572,28 +3572,28 @@
         <v>65</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO16" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AP16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>7.8</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>7</v>
-      </c>
       <c r="AR16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU16" t="n">
         <v>6.2</v>
@@ -3602,41 +3602,41 @@
         <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX16" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AY16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.4</v>
+        <v>46</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.4</v>
+        <v>46</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -3912,13 +3912,13 @@
         <v>1.15</v>
       </c>
       <c r="W18" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
@@ -3939,7 +3939,7 @@
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG18" t="n">
         <v>11.5</v>
@@ -3951,34 +3951,34 @@
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AQ18" t="n">
-        <v>5.7</v>
+        <v>23</v>
       </c>
       <c r="AR18" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT18" t="n">
         <v>9.6</v>
@@ -3987,44 +3987,44 @@
         <v>10</v>
       </c>
       <c r="AV18" t="n">
-        <v>19.5</v>
+        <v>6.6</v>
       </c>
       <c r="AW18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>6.2</v>
       </c>
-      <c r="AX18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BA18" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC18" t="n">
         <v>10.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -4055,25 +4055,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="G19" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="H19" t="n">
         <v>1.53</v>
       </c>
       <c r="I19" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="J19" t="n">
         <v>4.4</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
@@ -4085,7 +4085,7 @@
         <v>1.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q19" t="n">
         <v>1.74</v>
@@ -4094,34 +4094,34 @@
         <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T19" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U19" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="V19" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z19" t="n">
         <v>9.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AC19" t="n">
         <v>11</v>
@@ -4133,10 +4133,10 @@
         <v>17</v>
       </c>
       <c r="AF19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG19" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AH19" t="n">
         <v>24</v>
@@ -4151,7 +4151,7 @@
         <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
@@ -4160,16 +4160,16 @@
         <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AP19" t="n">
         <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS19" t="n">
         <v>11.5</v>
@@ -4187,38 +4187,38 @@
         <v>13.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC19" t="n">
         <v>9.6</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>9</v>
-      </c>
       <c r="BD19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BF19" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="G20" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="I20" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K20" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L20" t="n">
         <v>1.47</v>
@@ -4279,10 +4279,10 @@
         <v>1.41</v>
       </c>
       <c r="P20" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R20" t="n">
         <v>1.26</v>
@@ -4291,16 +4291,16 @@
         <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="U20" t="n">
         <v>1.94</v>
       </c>
       <c r="V20" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W20" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="X20" t="n">
         <v>14</v>
@@ -4309,22 +4309,22 @@
         <v>15.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
         <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>370</v>
+        <v>160</v>
       </c>
       <c r="AF20" t="n">
         <v>12.5</v>
@@ -4363,56 +4363,56 @@
         <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS20" t="n">
         <v>5.9</v>
       </c>
       <c r="AT20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU20" t="n">
         <v>6.6</v>
       </c>
-      <c r="AU20" t="n">
-        <v>7</v>
-      </c>
       <c r="AV20" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX20" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="AY20" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BC20" t="n">
         <v>11.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF20" t="n">
         <v>5</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.9</v>
+        <v>12</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>6.6</v>
       </c>
       <c r="G21" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="H21" t="n">
         <v>1.52</v>
@@ -4461,7 +4461,7 @@
         <v>4.9</v>
       </c>
       <c r="L21" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
@@ -4473,7 +4473,7 @@
         <v>1.26</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q21" t="n">
         <v>1.77</v>
@@ -4488,22 +4488,22 @@
         <v>1.89</v>
       </c>
       <c r="U21" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V21" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
         <v>21</v>
       </c>
       <c r="Y21" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z21" t="n">
         <v>10.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>11</v>
       </c>
       <c r="AA21" t="n">
         <v>17</v>
@@ -4518,16 +4518,16 @@
         <v>10</v>
       </c>
       <c r="AE21" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF21" t="n">
         <v>70</v>
       </c>
       <c r="AG21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AH21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI21" t="n">
         <v>36</v>
@@ -4548,13 +4548,13 @@
         <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP21" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR21" t="n">
         <v>8.4</v>
@@ -4575,7 +4575,7 @@
         <v>14</v>
       </c>
       <c r="AX21" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AY21" t="n">
         <v>22</v>
@@ -4584,29 +4584,29 @@
         <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BC21" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BG21" t="n">
         <v>7</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>1.42</v>
       </c>
       <c r="H22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I22" t="n">
         <v>11.5</v>
@@ -4718,7 +4718,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
         <v>30</v>
@@ -4727,7 +4727,7 @@
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AK22" t="n">
         <v>16</v>
@@ -4751,10 +4751,10 @@
         <v>13</v>
       </c>
       <c r="AR22" t="n">
-        <v>28</v>
+        <v>6.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT22" t="n">
         <v>7.2</v>
@@ -4766,7 +4766,7 @@
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX22" t="n">
         <v>7</v>
@@ -4778,7 +4778,7 @@
         <v>14.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB22" t="n">
         <v>9.800000000000001</v>
@@ -4790,17 +4790,17 @@
         <v>32</v>
       </c>
       <c r="BE22" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF22" t="n">
         <v>5.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="G23" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H23" t="n">
         <v>11</v>
@@ -4843,10 +4843,10 @@
         <v>18.5</v>
       </c>
       <c r="J23" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K23" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L23" t="n">
         <v>1.21</v>
@@ -4855,25 +4855,25 @@
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O23" t="n">
         <v>1.16</v>
       </c>
       <c r="P23" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="Q23" t="n">
         <v>1.47</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="S23" t="n">
         <v>2.04</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U23" t="n">
         <v>1.84</v>
@@ -4882,7 +4882,7 @@
         <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4921,7 +4921,7 @@
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK23" t="n">
         <v>1000</v>
@@ -4939,62 +4939,62 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AQ23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW23" t="n">
         <v>5</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="AX23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC23" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>4</v>
-      </c>
       <c r="BD23" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BF23" t="n">
         <v>3.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5055,7 @@
         <v>1.14</v>
       </c>
       <c r="P24" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="Q24" t="n">
         <v>1.48</v>
@@ -5133,7 +5133,7 @@
         <v>65</v>
       </c>
       <c r="AP24" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ24" t="n">
         <v>26</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
         <v>6.6</v>
       </c>
       <c r="H25" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="I25" t="n">
         <v>1.72</v>
@@ -5234,7 +5234,7 @@
         <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L25" t="n">
         <v>1.34</v>
@@ -5249,13 +5249,13 @@
         <v>1.26</v>
       </c>
       <c r="P25" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q25" t="n">
         <v>1.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
         <v>2.92</v>
@@ -5264,7 +5264,7 @@
         <v>1.8</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V25" t="n">
         <v>2.36</v>
@@ -5351,38 +5351,38 @@
         <v>10.5</v>
       </c>
       <c r="AX25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA25" t="n">
         <v>7.2</v>
       </c>
-      <c r="AY25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BB25" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE25" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG25" t="n">
         <v>7.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G26" t="n">
         <v>2.26</v>
       </c>
       <c r="H26" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J26" t="n">
         <v>3.35</v>
@@ -5440,7 +5440,7 @@
         <v>3.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="P26" t="n">
         <v>1.86</v>
@@ -5455,13 +5455,13 @@
         <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U26" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V26" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W26" t="n">
         <v>1.79</v>
@@ -5470,13 +5470,13 @@
         <v>17</v>
       </c>
       <c r="Y26" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA26" t="n">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="AB26" t="n">
         <v>11.5</v>
@@ -5488,7 +5488,7 @@
         <v>17</v>
       </c>
       <c r="AE26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF26" t="n">
         <v>16.5</v>
@@ -5500,7 +5500,7 @@
         <v>19</v>
       </c>
       <c r="AI26" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ26" t="n">
         <v>28</v>
@@ -5512,7 +5512,7 @@
         <v>40</v>
       </c>
       <c r="AM26" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN26" t="n">
         <v>17.5</v>
@@ -5521,7 +5521,7 @@
         <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>12</v>
@@ -5551,7 +5551,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA26" t="n">
         <v>5.4</v>
@@ -5563,20 +5563,20 @@
         <v>19.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE26" t="n">
         <v>5.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -5607,13 +5607,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G27" t="n">
         <v>2.66</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I27" t="n">
         <v>3.05</v>
@@ -5625,118 +5625,118 @@
         <v>3.5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M27" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="O27" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="P27" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="Q27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U27" t="n">
         <v>2.06</v>
       </c>
-      <c r="R27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.16</v>
-      </c>
       <c r="V27" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W27" t="n">
         <v>1.6</v>
       </c>
       <c r="X27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z27" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA27" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB27" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD27" t="n">
         <v>13</v>
       </c>
       <c r="AE27" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF27" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG27" t="n">
         <v>12</v>
       </c>
       <c r="AH27" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI27" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AJ27" t="n">
         <v>38</v>
       </c>
       <c r="AK27" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL27" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM27" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AN27" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AO27" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AP27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ27" t="n">
         <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS27" t="n">
         <v>42</v>
       </c>
       <c r="AT27" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV27" t="n">
         <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX27" t="n">
         <v>15.5</v>
@@ -5745,32 +5745,32 @@
         <v>11</v>
       </c>
       <c r="AZ27" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD27" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE27" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BF27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BG27" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G28" t="n">
         <v>2.22</v>
@@ -5813,52 +5813,52 @@
         <v>4.1</v>
       </c>
       <c r="J28" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K28" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L28" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M28" t="n">
         <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
         <v>1.29</v>
       </c>
       <c r="P28" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T28" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="U28" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V28" t="n">
         <v>1.32</v>
       </c>
       <c r="W28" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="X28" t="n">
         <v>34</v>
       </c>
       <c r="Y28" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="Z28" t="n">
         <v>500</v>
@@ -5867,10 +5867,10 @@
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD28" t="n">
         <v>30</v>
@@ -5885,7 +5885,7 @@
         <v>11.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AI28" t="n">
         <v>500</v>
@@ -5903,7 +5903,7 @@
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>55</v>
+        <v>18.5</v>
       </c>
       <c r="AO28" t="n">
         <v>500</v>
@@ -5915,10 +5915,10 @@
         <v>11.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS28" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT28" t="n">
         <v>8.199999999999999</v>
@@ -5930,7 +5930,7 @@
         <v>11.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX28" t="n">
         <v>11</v>
@@ -5942,29 +5942,29 @@
         <v>13</v>
       </c>
       <c r="BA28" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC28" t="n">
         <v>17</v>
       </c>
       <c r="BD28" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF28" t="n">
         <v>11.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
         <v>6.8</v>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J29" t="n">
         <v>4.4</v>
@@ -6103,7 +6103,7 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ29" t="n">
         <v>14.5</v>
@@ -6115,13 +6115,13 @@
         <v>4.2</v>
       </c>
       <c r="AT29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AU29" t="n">
         <v>5.5</v>
       </c>
       <c r="AV29" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AW29" t="n">
         <v>4.2</v>
@@ -6148,7 +6148,7 @@
         <v>8.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF29" t="n">
         <v>7</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -6192,10 +6192,10 @@
         <v>2.12</v>
       </c>
       <c r="G30" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="H30" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I30" t="n">
         <v>3.45</v>
@@ -6240,7 +6240,7 @@
         <v>1.41</v>
       </c>
       <c r="W30" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="X30" t="n">
         <v>30</v>
@@ -6303,16 +6303,16 @@
         <v>10.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AT30" t="n">
         <v>12</v>
       </c>
       <c r="AU30" t="n">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AV30" t="n">
         <v>11</v>
@@ -6321,7 +6321,7 @@
         <v>16</v>
       </c>
       <c r="AX30" t="n">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="AY30" t="n">
         <v>6.2</v>
@@ -6330,7 +6330,7 @@
         <v>11</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BB30" t="n">
         <v>13</v>
@@ -6339,20 +6339,20 @@
         <v>14</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BF30" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="BG30" t="n">
         <v>17</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="G31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H31" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="I31" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="J31" t="n">
         <v>4</v>
@@ -6401,31 +6401,31 @@
         <v>4.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M31" t="n">
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O31" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R31" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T31" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U31" t="n">
         <v>2.14</v>
@@ -6437,28 +6437,28 @@
         <v>1.25</v>
       </c>
       <c r="X31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y31" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA31" t="n">
         <v>19.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD31" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AE31" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AF31" t="n">
         <v>38</v>
@@ -6467,31 +6467,31 @@
         <v>19</v>
       </c>
       <c r="AH31" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ31" t="n">
         <v>700</v>
       </c>
       <c r="AK31" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AL31" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AM31" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AN31" t="n">
         <v>65</v>
       </c>
       <c r="AO31" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AP31" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ31" t="n">
         <v>8.199999999999999</v>
@@ -6500,10 +6500,10 @@
         <v>10</v>
       </c>
       <c r="AS31" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AT31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU31" t="n">
         <v>8.199999999999999</v>
@@ -6515,19 +6515,19 @@
         <v>16.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AY31" t="n">
         <v>16.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA31" t="n">
         <v>27</v>
       </c>
       <c r="BB31" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC31" t="n">
         <v>28</v>
@@ -6539,14 +6539,14 @@
         <v>44</v>
       </c>
       <c r="BF31" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BG31" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G32" t="n">
         <v>1.62</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -6774,13 +6774,13 @@
         <v>2.3</v>
       </c>
       <c r="G33" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="H33" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J33" t="n">
         <v>3.5</v>
@@ -6801,7 +6801,7 @@
         <v>1.25</v>
       </c>
       <c r="P33" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q33" t="n">
         <v>1.76</v>
@@ -6822,7 +6822,7 @@
         <v>1.41</v>
       </c>
       <c r="W33" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="X33" t="n">
         <v>19</v>
@@ -6834,7 +6834,7 @@
         <v>26</v>
       </c>
       <c r="AA33" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AB33" t="n">
         <v>13</v>
@@ -6843,13 +6843,13 @@
         <v>8.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE33" t="n">
         <v>36</v>
       </c>
       <c r="AF33" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG33" t="n">
         <v>12</v>
@@ -6858,28 +6858,28 @@
         <v>16.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ33" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL33" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM33" t="n">
         <v>75</v>
       </c>
       <c r="AN33" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP33" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AQ33" t="n">
         <v>13</v>
@@ -6897,7 +6897,7 @@
         <v>7.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW33" t="n">
         <v>16</v>
@@ -6912,7 +6912,7 @@
         <v>13.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>30</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB33" t="n">
         <v>24</v>
@@ -6924,17 +6924,17 @@
         <v>26</v>
       </c>
       <c r="BE33" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF33" t="n">
         <v>13.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G34" t="n">
         <v>2.42</v>
@@ -7082,7 +7082,7 @@
         <v>20</v>
       </c>
       <c r="AS34" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AT34" t="n">
         <v>11.5</v>
@@ -7118,7 +7118,7 @@
         <v>14.5</v>
       </c>
       <c r="BE34" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BF34" t="n">
         <v>11</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G35" t="n">
         <v>2.24</v>
@@ -7171,7 +7171,7 @@
         <v>3.5</v>
       </c>
       <c r="J35" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K35" t="n">
         <v>4.2</v>
@@ -7189,7 +7189,7 @@
         <v>1.17</v>
       </c>
       <c r="P35" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q35" t="n">
         <v>1.53</v>
@@ -7288,13 +7288,13 @@
         <v>7.6</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX35" t="n">
         <v>8.4</v>
       </c>
       <c r="AY35" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="AZ35" t="n">
         <v>8.4</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -7356,16 +7356,16 @@
         <v>1.81</v>
       </c>
       <c r="G36" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H36" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I36" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J36" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K36" t="n">
         <v>3.85</v>
@@ -7392,10 +7392,10 @@
         <v>1.28</v>
       </c>
       <c r="S36" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T36" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U36" t="n">
         <v>1.89</v>
@@ -7422,7 +7422,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC36" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD36" t="n">
         <v>25</v>
@@ -7464,13 +7464,13 @@
         <v>10</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AR36" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT36" t="n">
         <v>6.6</v>
@@ -7479,10 +7479,10 @@
         <v>7</v>
       </c>
       <c r="AV36" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AX36" t="n">
         <v>9.4</v>
@@ -7491,32 +7491,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ36" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA36" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BB36" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>4</v>
+        <v>18.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BE36" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF36" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -7550,19 +7550,19 @@
         <v>5.8</v>
       </c>
       <c r="G37" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="H37" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="I37" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="J37" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K37" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="L37" t="n">
         <v>1.6</v>
@@ -7571,22 +7571,22 @@
         <v>1.13</v>
       </c>
       <c r="N37" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P37" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="R37" t="n">
         <v>1.16</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T37" t="n">
         <v>2.42</v>
@@ -7595,25 +7595,25 @@
         <v>1.6</v>
       </c>
       <c r="V37" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="W37" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X37" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y37" t="n">
         <v>5.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>900</v>
+        <v>25</v>
       </c>
       <c r="AB37" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC37" t="n">
         <v>8.199999999999999</v>
@@ -7622,16 +7622,16 @@
         <v>11.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AF37" t="n">
         <v>1000</v>
       </c>
       <c r="AG37" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AH37" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="n">
         <v>1000</v>
@@ -7652,19 +7652,19 @@
         <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ37" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AR37" t="n">
         <v>8</v>
       </c>
       <c r="AS37" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AT37" t="n">
         <v>11.5</v>
@@ -7679,38 +7679,38 @@
         <v>23</v>
       </c>
       <c r="AX37" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="AY37" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ37" t="n">
         <v>28</v>
       </c>
       <c r="BA37" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB37" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE37" t="n">
         <v>10</v>
       </c>
-      <c r="BC37" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>11</v>
-      </c>
       <c r="BF37" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG37" t="n">
         <v>18.5</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -7741,170 +7741,170 @@
         </is>
       </c>
       <c r="F38" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I38" t="n">
         <v>3.1</v>
       </c>
-      <c r="G38" t="n">
+      <c r="J38" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X38" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>540</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
         <v>3.5</v>
       </c>
-      <c r="H38" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I38" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="K38" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S38" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X38" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>290</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>42</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>440</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AQ38" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AR38" t="n">
-        <v>15</v>
+        <v>1.74</v>
       </c>
       <c r="AS38" t="n">
-        <v>9.199999999999999</v>
+        <v>1.78</v>
       </c>
       <c r="AT38" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="AU38" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="AV38" t="n">
-        <v>12.5</v>
+        <v>1.72</v>
       </c>
       <c r="AW38" t="n">
-        <v>9.199999999999999</v>
+        <v>1.78</v>
       </c>
       <c r="AX38" t="n">
-        <v>8.4</v>
+        <v>1.74</v>
       </c>
       <c r="AY38" t="n">
-        <v>13.5</v>
+        <v>1.73</v>
       </c>
       <c r="AZ38" t="n">
-        <v>14.5</v>
+        <v>1.77</v>
       </c>
       <c r="BA38" t="n">
-        <v>10</v>
+        <v>1.79</v>
       </c>
       <c r="BB38" t="n">
-        <v>9.4</v>
+        <v>1.78</v>
       </c>
       <c r="BC38" t="n">
-        <v>9.4</v>
+        <v>1.78</v>
       </c>
       <c r="BD38" t="n">
-        <v>10</v>
+        <v>1.79</v>
       </c>
       <c r="BE38" t="n">
-        <v>10.5</v>
+        <v>1.78</v>
       </c>
       <c r="BF38" t="n">
-        <v>10</v>
+        <v>1.78</v>
       </c>
       <c r="BG38" t="n">
-        <v>9.6</v>
+        <v>1.77</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -7959,19 +7959,19 @@
         <v>1.05</v>
       </c>
       <c r="N39" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O39" t="n">
         <v>1.23</v>
       </c>
       <c r="P39" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R39" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S39" t="n">
         <v>2.72</v>
@@ -7983,16 +7983,16 @@
         <v>2.18</v>
       </c>
       <c r="V39" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W39" t="n">
         <v>2.28</v>
       </c>
       <c r="X39" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y39" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="Z39" t="n">
         <v>48</v>
@@ -8007,10 +8007,10 @@
         <v>10</v>
       </c>
       <c r="AD39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE39" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF39" t="n">
         <v>13.5</v>
@@ -8043,16 +8043,16 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ39" t="n">
         <v>18</v>
       </c>
       <c r="AR39" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS39" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT39" t="n">
         <v>9</v>
@@ -8064,7 +8064,7 @@
         <v>17</v>
       </c>
       <c r="AW39" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX39" t="n">
         <v>10</v>
@@ -8076,7 +8076,7 @@
         <v>15.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB39" t="n">
         <v>15</v>
@@ -8088,17 +8088,17 @@
         <v>22</v>
       </c>
       <c r="BE39" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF39" t="n">
         <v>7.8</v>
       </c>
       <c r="BG39" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="G40" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="H40" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="I40" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="K40" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="L40" t="n">
         <v>1.16</v>
@@ -8153,7 +8153,7 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="O40" t="n">
         <v>1.09</v>
@@ -8171,22 +8171,22 @@
         <v>1.73</v>
       </c>
       <c r="T40" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="U40" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V40" t="n">
         <v>1.05</v>
       </c>
       <c r="W40" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="X40" t="n">
         <v>240</v>
       </c>
       <c r="Y40" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Z40" t="n">
         <v>190</v>
@@ -8198,22 +8198,22 @@
         <v>16.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AD40" t="n">
         <v>300</v>
       </c>
       <c r="AE40" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AF40" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH40" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AI40" t="n">
         <v>460</v>
@@ -8231,19 +8231,19 @@
         <v>380</v>
       </c>
       <c r="AN40" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="AO40" t="n">
         <v>190</v>
       </c>
       <c r="AP40" t="n">
+        <v>50</v>
+      </c>
+      <c r="AQ40" t="n">
         <v>10</v>
       </c>
-      <c r="AQ40" t="n">
+      <c r="AR40" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>11</v>
       </c>
       <c r="AS40" t="n">
         <v>11.5</v>
@@ -8255,44 +8255,44 @@
         <v>19.5</v>
       </c>
       <c r="AV40" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW40" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX40" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY40" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ40" t="n">
-        <v>27</v>
+        <v>14.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB40" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC40" t="n">
         <v>11</v>
       </c>
       <c r="BD40" t="n">
-        <v>8.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="BE40" t="n">
         <v>20</v>
       </c>
       <c r="BF40" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="BG40" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -8625,62 +8625,62 @@
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AT42" t="n">
         <v>5.9</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
         <v>5.2</v>
       </c>
       <c r="L43" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M43" t="n">
         <v>1.02</v>
@@ -8744,34 +8744,34 @@
         <v>3.45</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R43" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S43" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="T43" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U43" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="V43" t="n">
         <v>1.21</v>
       </c>
       <c r="W43" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X43" t="n">
         <v>38</v>
       </c>
       <c r="Y43" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z43" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA43" t="n">
         <v>120</v>
@@ -8783,7 +8783,7 @@
         <v>13</v>
       </c>
       <c r="AD43" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE43" t="n">
         <v>55</v>
@@ -8810,13 +8810,13 @@
         <v>21</v>
       </c>
       <c r="AM43" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN43" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AO43" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP43" t="n">
         <v>36</v>
@@ -8837,7 +8837,7 @@
         <v>12.5</v>
       </c>
       <c r="AV43" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW43" t="n">
         <v>48</v>
@@ -8855,7 +8855,7 @@
         <v>42</v>
       </c>
       <c r="BB43" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC43" t="n">
         <v>12.5</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G44" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H44" t="n">
         <v>4.6</v>
@@ -8926,7 +8926,7 @@
         <v>1.27</v>
       </c>
       <c r="M44" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N44" t="n">
         <v>6.2</v>
@@ -8935,7 +8935,7 @@
         <v>1.18</v>
       </c>
       <c r="P44" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q44" t="n">
         <v>1.54</v>
@@ -8944,10 +8944,10 @@
         <v>1.72</v>
       </c>
       <c r="S44" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T44" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U44" t="n">
         <v>2.66</v>
@@ -8956,19 +8956,19 @@
         <v>1.27</v>
       </c>
       <c r="W44" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X44" t="n">
         <v>26</v>
       </c>
       <c r="Y44" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z44" t="n">
         <v>42</v>
       </c>
       <c r="AA44" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB44" t="n">
         <v>14.5</v>
@@ -8992,22 +8992,22 @@
         <v>15.5</v>
       </c>
       <c r="AI44" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ44" t="n">
         <v>19</v>
       </c>
       <c r="AK44" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL44" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM44" t="n">
         <v>55</v>
       </c>
       <c r="AN44" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO44" t="n">
         <v>34</v>
@@ -9016,7 +9016,7 @@
         <v>24</v>
       </c>
       <c r="AQ44" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR44" t="n">
         <v>38</v>
@@ -9028,10 +9028,10 @@
         <v>13.5</v>
       </c>
       <c r="AU44" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV44" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW44" t="n">
         <v>42</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
         <v>2.98</v>
       </c>
       <c r="J45" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K45" t="n">
         <v>7.6</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -9293,61 +9293,61 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="G46" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H46" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="I46" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J46" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K46" t="n">
         <v>4.4</v>
       </c>
       <c r="L46" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M46" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N46" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O46" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P46" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="Q46" t="n">
         <v>1.9</v>
       </c>
       <c r="R46" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S46" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T46" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U46" t="n">
         <v>1.93</v>
       </c>
       <c r="V46" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W46" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="X46" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y46" t="n">
         <v>1000</v>
@@ -9365,16 +9365,16 @@
         <v>9.6</v>
       </c>
       <c r="AD46" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE46" t="n">
         <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG46" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH46" t="n">
         <v>1000</v>
@@ -9395,7 +9395,7 @@
         <v>1000</v>
       </c>
       <c r="AN46" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO46" t="n">
         <v>1000</v>
@@ -9407,10 +9407,10 @@
         <v>13.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS46" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AT46" t="n">
         <v>7.2</v>
@@ -9422,7 +9422,7 @@
         <v>16.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX46" t="n">
         <v>8.6</v>
@@ -9431,32 +9431,32 @@
         <v>8.6</v>
       </c>
       <c r="AZ46" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BA46" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB46" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BC46" t="n">
         <v>13.5</v>
       </c>
       <c r="BD46" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE46" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF46" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG46" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-07 22:09:25</t>
+          <t>2026-04-08 00:19:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G2" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="H2" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="I2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
@@ -775,28 +775,28 @@
         <v>3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
         <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
         <v>1.74</v>
@@ -805,49 +805,49 @@
         <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="W2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X2" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AB2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AG2" t="n">
-        <v>18.5</v>
+        <v>80</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="n">
         <v>500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AK2" t="n">
         <v>120</v>
@@ -859,37 +859,37 @@
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>220</v>
+        <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AP2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR2" t="n">
         <v>12</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AS2" t="n">
-        <v>4.2</v>
+        <v>22</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW2" t="n">
         <v>10</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="AY2" t="n">
         <v>13</v>
@@ -898,29 +898,29 @@
         <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.4</v>
+        <v>15.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.9</v>
+        <v>13</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="G3" t="n">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="H3" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="J3" t="n">
         <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
         <v>1.48</v>
@@ -975,58 +975,58 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O3" t="n">
         <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
         <v>4.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V3" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Y3" t="n">
         <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
         <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AF3" t="n">
         <v>18.5</v>
@@ -1044,7 +1044,7 @@
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1053,68 +1053,68 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP3" t="n">
         <v>9.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="AX3" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA3" t="n">
         <v>6.6</v>
       </c>
-      <c r="BA3" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BB3" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -1145,58 +1145,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="G4" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="H4" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="J4" t="n">
         <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="O4" t="n">
         <v>1.48</v>
       </c>
       <c r="P4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="R4" t="n">
         <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T4" t="n">
         <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="X4" t="n">
         <v>10.5</v>
@@ -1205,43 +1205,43 @@
         <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4" t="n">
         <v>7.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK4" t="n">
         <v>34</v>
       </c>
-      <c r="AK4" t="n">
-        <v>32</v>
-      </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="BB4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE4" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AT4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BF4" t="n">
-        <v>22</v>
+        <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -1339,136 +1339,136 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H5" t="n">
         <v>2.56</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
         <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.38</v>
       </c>
-      <c r="P5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.3</v>
-      </c>
       <c r="S5" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="T5" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="U5" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="V5" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="W5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X5" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y5" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y5" t="n">
-        <v>10.5</v>
-      </c>
       <c r="Z5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA5" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AB5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="AF5" t="n">
         <v>22</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
         <v>130</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL5" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN5" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV5" t="n">
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="AX5" t="n">
         <v>17</v>
@@ -1477,32 +1477,32 @@
         <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BB5" t="n">
         <v>38</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="G6" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
         <v>4.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>2.58</v>
+        <v>3.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="V6" t="n">
-        <v>2.34</v>
+        <v>2.68</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA6" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AB6" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AC6" t="n">
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
         <v>11.5</v>
       </c>
-      <c r="AE6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>12</v>
-      </c>
       <c r="AP6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>5.6</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BA6" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -1727,73 +1727,73 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="G7" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="I7" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="J7" t="n">
         <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P7" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="T7" t="n">
-        <v>1.86</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="X7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB7" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
         <v>7.8</v>
@@ -1805,31 +1805,31 @@
         <v>34</v>
       </c>
       <c r="AF7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ7" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AL7" t="n">
         <v>200</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AO7" t="n">
         <v>32</v>
@@ -1838,59 +1838,59 @@
         <v>5.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7" t="n">
         <v>4.8</v>
       </c>
       <c r="AU7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>3.95</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="BA7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE7" t="n">
         <v>4.8</v>
       </c>
-      <c r="AW7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BF7" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="H8" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="U8" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="V8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Z8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AD8" t="n">
         <v>19</v>
       </c>
       <c r="AE8" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AF8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI8" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL8" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AM8" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>19.5</v>
+        <v>14</v>
       </c>
       <c r="AO8" t="n">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.7</v>
+        <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.6</v>
+        <v>15.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>6</v>
+        <v>17.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -2115,61 +2115,61 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="G9" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="H9" t="n">
-        <v>5.7</v>
+        <v>9.6</v>
       </c>
       <c r="I9" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J9" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W9" t="n">
         <v>3</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.75</v>
-      </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -2181,10 +2181,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2193,7 +2193,7 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AG9" t="n">
         <v>30</v>
@@ -2217,68 +2217,68 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY9" t="n">
         <v>5.4</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC9" t="n">
         <v>6.8</v>
       </c>
-      <c r="AR9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF9" t="n">
         <v>5.2</v>
       </c>
-      <c r="AV9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4</v>
-      </c>
       <c r="BG9" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G10" t="n">
         <v>2.28</v>
@@ -2318,43 +2318,43 @@
         <v>3.3</v>
       </c>
       <c r="I10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J10" t="n">
         <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P10" t="n">
         <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="R10" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="T10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U10" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V10" t="n">
         <v>1.38</v>
@@ -2363,25 +2363,25 @@
         <v>1.78</v>
       </c>
       <c r="X10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z10" t="n">
         <v>30</v>
       </c>
       <c r="AA10" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AB10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
         <v>44</v>
@@ -2390,7 +2390,7 @@
         <v>17</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
         <v>18.5</v>
@@ -2411,10 +2411,10 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP10" t="n">
         <v>16.5</v>
@@ -2426,7 +2426,7 @@
         <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>25</v>
+        <v>6.4</v>
       </c>
       <c r="AT10" t="n">
         <v>10.5</v>
@@ -2438,7 +2438,7 @@
         <v>13</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
         <v>13.5</v>
@@ -2450,29 +2450,29 @@
         <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.7</v>
+        <v>19.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.1</v>
+        <v>13.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.5</v>
+        <v>27</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.6</v>
+        <v>32</v>
       </c>
       <c r="BF10" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>22</v>
+        <v>5.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G11" t="n">
         <v>3.2</v>
@@ -2512,55 +2512,55 @@
         <v>2.62</v>
       </c>
       <c r="I11" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
         <v>3.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="O11" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="P11" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U11" t="n">
         <v>1.84</v>
       </c>
       <c r="V11" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X11" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Z11" t="n">
         <v>16</v>
@@ -2569,10 +2569,10 @@
         <v>42</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD11" t="n">
         <v>13</v>
@@ -2584,10 +2584,10 @@
         <v>19</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
         <v>380</v>
@@ -2596,77 +2596,77 @@
         <v>60</v>
       </c>
       <c r="AK11" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AL11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN11" t="n">
         <v>70</v>
       </c>
-      <c r="AM11" t="n">
-        <v>450</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>55</v>
-      </c>
       <c r="AO11" t="n">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS11" t="n">
         <v>36</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV11" t="n">
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="AX11" t="n">
         <v>17.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA11" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE11" t="n">
         <v>29</v>
       </c>
-      <c r="BB11" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>17</v>
-      </c>
       <c r="BF11" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="BG11" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="G12" t="n">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="H12" t="n">
-        <v>2.48</v>
+        <v>2.86</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
         <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="T12" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="U12" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
         <v>15</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA12" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AB12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
         <v>14</v>
       </c>
       <c r="AE12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ12" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AK12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM12" t="n">
         <v>80</v>
       </c>
       <c r="AN12" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AP12" t="n">
-        <v>14.5</v>
+        <v>7.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>15</v>
+        <v>6.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="AU12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA12" t="n">
         <v>7</v>
       </c>
-      <c r="AV12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW12" t="n">
+      <c r="BB12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG12" t="n">
         <v>21</v>
       </c>
-      <c r="AX12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>16</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -2891,85 +2891,85 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="G13" t="n">
         <v>17</v>
       </c>
       <c r="H13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="I13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="J13" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="K13" t="n">
         <v>6.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="R13" t="n">
         <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T13" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="U13" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="W13" t="n">
         <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="n">
         <v>6.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AB13" t="n">
         <v>36</v>
       </c>
       <c r="AC13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD13" t="n">
         <v>11.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="n">
         <v>60</v>
@@ -2993,16 +2993,16 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="AO13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AP13" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR13" t="n">
         <v>5.9</v>
@@ -3011,37 +3011,37 @@
         <v>8.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AU13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB13" t="n">
         <v>14.5</v>
       </c>
-      <c r="AX13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BC13" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BD13" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BE13" t="n">
         <v>30</v>
@@ -3050,11 +3050,11 @@
         <v>15</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -3085,64 +3085,64 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="G14" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H14" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="M14" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N14" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="O14" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="P14" t="n">
         <v>1.57</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="R14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="U14" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y14" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3151,10 +3151,10 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3163,10 +3163,10 @@
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH14" t="n">
         <v>70</v>
@@ -3175,80 +3175,80 @@
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>60</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AL14" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>20</v>
+        <v>600</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX14" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>7.8</v>
       </c>
       <c r="AY14" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB14" t="n">
         <v>10</v>
       </c>
-      <c r="BB14" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BC14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="BD14" t="n">
-        <v>44</v>
+        <v>7.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BF14" t="n">
-        <v>16.5</v>
+        <v>6.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -3282,79 +3282,79 @@
         <v>2.06</v>
       </c>
       <c r="G15" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P15" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U15" t="n">
         <v>1.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W15" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y15" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y15" t="n">
-        <v>24</v>
-      </c>
       <c r="Z15" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF15" t="n">
         <v>30</v>
@@ -3369,7 +3369,7 @@
         <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AK15" t="n">
         <v>75</v>
@@ -3381,34 +3381,34 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP15" t="n">
         <v>10</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU15" t="n">
         <v>6.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
@@ -3417,32 +3417,32 @@
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="BC15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="BG15" t="n">
         <v>10.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -3473,58 +3473,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H16" t="n">
         <v>2.7</v>
       </c>
       <c r="I16" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="J16" t="n">
         <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="M16" t="n">
         <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>1.47</v>
       </c>
       <c r="P16" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
         <v>2.36</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T16" t="n">
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V16" t="n">
         <v>1.53</v>
       </c>
       <c r="W16" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X16" t="n">
         <v>10.5</v>
@@ -3539,7 +3539,7 @@
         <v>60</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC16" t="n">
         <v>7.6</v>
@@ -3572,7 +3572,7 @@
         <v>65</v>
       </c>
       <c r="AM16" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
         <v>50</v>
@@ -3587,10 +3587,10 @@
         <v>7.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="AT16" t="n">
         <v>8.199999999999999</v>
@@ -3599,13 +3599,13 @@
         <v>6.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.6</v>
+        <v>16.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY16" t="n">
         <v>12</v>
@@ -3614,29 +3614,29 @@
         <v>17.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>46</v>
+        <v>8.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>32</v>
+        <v>17.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>46</v>
+        <v>8.6</v>
       </c>
       <c r="BE16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G17" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="H17" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="J17" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
@@ -3694,64 +3694,64 @@
         <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="U17" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W17" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y17" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="Z17" t="n">
         <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
@@ -3766,71 +3766,71 @@
         <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AS17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT17" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT17" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AU17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV17" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV17" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AW17" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>13.5</v>
+        <v>5.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.5</v>
+        <v>9.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.5</v>
+        <v>9.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.5</v>
+        <v>9.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="G18" t="n">
         <v>1.56</v>
@@ -3870,22 +3870,22 @@
         <v>6.2</v>
       </c>
       <c r="I18" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J18" t="n">
         <v>4.9</v>
       </c>
       <c r="K18" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="M18" t="n">
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O18" t="n">
         <v>1.16</v>
@@ -3894,31 +3894,31 @@
         <v>2.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="S18" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="T18" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U18" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V18" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="Y18" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
@@ -3930,10 +3930,10 @@
         <v>24</v>
       </c>
       <c r="AC18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
@@ -3942,7 +3942,7 @@
         <v>12.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH18" t="n">
         <v>1000</v>
@@ -3963,46 +3963,46 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AQ18" t="n">
         <v>23</v>
       </c>
       <c r="AR18" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AU18" t="n">
         <v>10</v>
       </c>
       <c r="AV18" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX18" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AY18" t="n">
         <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB18" t="n">
         <v>12</v>
@@ -4011,20 +4011,20 @@
         <v>10.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BG18" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -4055,61 +4055,61 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="G19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="H19" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="I19" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="J19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K19" t="n">
         <v>4.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P19" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="R19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S19" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U19" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V19" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y19" t="n">
         <v>9.4</v>
@@ -4121,7 +4121,7 @@
         <v>14.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AC19" t="n">
         <v>11</v>
@@ -4133,7 +4133,7 @@
         <v>17</v>
       </c>
       <c r="AF19" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
         <v>48</v>
@@ -4151,7 +4151,7 @@
         <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
@@ -4166,7 +4166,7 @@
         <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR19" t="n">
         <v>8.199999999999999</v>
@@ -4187,13 +4187,13 @@
         <v>13.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY19" t="n">
         <v>22</v>
       </c>
       <c r="AZ19" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA19" t="n">
         <v>14.5</v>
@@ -4211,14 +4211,14 @@
         <v>28</v>
       </c>
       <c r="BF19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -4255,49 +4255,49 @@
         <v>2.2</v>
       </c>
       <c r="H20" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K20" t="n">
         <v>3.55</v>
       </c>
       <c r="L20" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M20" t="n">
         <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P20" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U20" t="n">
         <v>1.94</v>
       </c>
       <c r="V20" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W20" t="n">
         <v>1.83</v>
@@ -4324,7 +4324,7 @@
         <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
         <v>12.5</v>
@@ -4333,7 +4333,7 @@
         <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
@@ -4366,53 +4366,53 @@
         <v>13.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AT20" t="n">
         <v>7.2</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV20" t="n">
         <v>14</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.6</v>
+        <v>42</v>
       </c>
       <c r="AX20" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY20" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB20" t="n">
         <v>23</v>
       </c>
       <c r="BC20" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="BD20" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BG20" t="n">
         <v>12</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -4443,67 +4443,67 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="G21" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="H21" t="n">
         <v>1.52</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="J21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="P21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U21" t="n">
         <v>2.12</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.97</v>
       </c>
       <c r="V21" t="n">
         <v>2.66</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA21" t="n">
         <v>17</v>
@@ -4512,49 +4512,49 @@
         <v>28</v>
       </c>
       <c r="AC21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD21" t="n">
         <v>10</v>
       </c>
       <c r="AE21" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AG21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI21" t="n">
         <v>30</v>
       </c>
-      <c r="AH21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>36</v>
-      </c>
       <c r="AJ21" t="n">
         <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM21" t="n">
         <v>110</v>
       </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO21" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AP21" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR21" t="n">
         <v>8.4</v>
@@ -4566,47 +4566,47 @@
         <v>20</v>
       </c>
       <c r="AU21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB21" t="n">
         <v>9</v>
       </c>
-      <c r="AV21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>6</v>
-      </c>
       <c r="BC21" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="BE21" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -4637,139 +4637,139 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="G22" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
       </c>
       <c r="I22" t="n">
+        <v>12</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC22" t="n">
         <v>11.5</v>
       </c>
-      <c r="J22" t="n">
-        <v>5</v>
-      </c>
-      <c r="K22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X22" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>14</v>
-      </c>
       <c r="AD22" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AK22" t="n">
         <v>16</v>
       </c>
       <c r="AL22" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AU22" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY22" t="n">
         <v>8.800000000000001</v>
@@ -4778,7 +4778,7 @@
         <v>14.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BB22" t="n">
         <v>9.800000000000001</v>
@@ -4790,17 +4790,17 @@
         <v>32</v>
       </c>
       <c r="BE22" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -4831,58 +4831,58 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="G23" t="n">
         <v>1.29</v>
       </c>
       <c r="H23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="I23" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="J23" t="n">
         <v>6.4</v>
       </c>
       <c r="K23" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P23" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R23" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="S23" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="T23" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="U23" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4897,7 +4897,7 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC23" t="n">
         <v>1000</v>
@@ -4909,7 +4909,7 @@
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
         <v>1000</v>
@@ -4933,68 +4933,68 @@
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="AQ23" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AU23" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AW23" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AX23" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="AY23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB23" t="n">
         <v>8.6</v>
       </c>
-      <c r="AZ23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BC23" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BD23" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="BE23" t="n">
-        <v>6.8</v>
+        <v>3.25</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BG23" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -5025,49 +5025,49 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G24" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H24" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K24" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="M24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P24" t="n">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="R24" t="n">
         <v>1.66</v>
       </c>
       <c r="S24" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="T24" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U24" t="n">
         <v>2.22</v>
@@ -5079,31 +5079,31 @@
         <v>2.78</v>
       </c>
       <c r="X24" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y24" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z24" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC24" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE24" t="n">
         <v>170</v>
       </c>
       <c r="AF24" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG24" t="n">
         <v>11</v>
@@ -5127,22 +5127,22 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AO24" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="AQ24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT24" t="n">
         <v>9.6</v>
@@ -5151,22 +5151,22 @@
         <v>10</v>
       </c>
       <c r="AV24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX24" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
         <v>17</v>
       </c>
       <c r="BA24" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB24" t="n">
         <v>12</v>
@@ -5175,20 +5175,20 @@
         <v>12</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="BE24" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BG24" t="n">
-        <v>7.4</v>
+        <v>55</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -5234,31 +5234,31 @@
         <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L25" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M25" t="n">
         <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O25" t="n">
         <v>1.26</v>
       </c>
       <c r="P25" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R25" t="n">
         <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T25" t="n">
         <v>1.8</v>
@@ -5267,16 +5267,16 @@
         <v>2.04</v>
       </c>
       <c r="V25" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="W25" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
         <v>970</v>
       </c>
       <c r="Y25" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Z25" t="n">
         <v>11</v>
@@ -5327,7 +5327,7 @@
         <v>27</v>
       </c>
       <c r="AP25" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="AQ25" t="n">
         <v>7.8</v>
@@ -5339,7 +5339,7 @@
         <v>7.6</v>
       </c>
       <c r="AT25" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="AU25" t="n">
         <v>8.4</v>
@@ -5348,41 +5348,41 @@
         <v>8.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AY25" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB25" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC25" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG25" t="n">
         <v>7.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -5413,91 +5413,91 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G26" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H26" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I26" t="n">
         <v>4.2</v>
       </c>
       <c r="J26" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K26" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L26" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="M26" t="n">
         <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O26" t="n">
         <v>1.32</v>
       </c>
       <c r="P26" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S26" t="n">
         <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U26" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V26" t="n">
         <v>1.31</v>
       </c>
       <c r="W26" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X26" t="n">
         <v>17</v>
       </c>
       <c r="Y26" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA26" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AB26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG26" t="n">
         <v>11.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI26" t="n">
         <v>60</v>
@@ -5530,7 +5530,7 @@
         <v>11.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AT26" t="n">
         <v>8</v>
@@ -5542,7 +5542,7 @@
         <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AX26" t="n">
         <v>11.5</v>
@@ -5554,7 +5554,7 @@
         <v>15</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BB26" t="n">
         <v>11.5</v>
@@ -5563,20 +5563,20 @@
         <v>19.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF26" t="n">
         <v>14</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -5607,61 +5607,61 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G27" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H27" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
         <v>3.05</v>
       </c>
       <c r="J27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K27" t="n">
         <v>3.45</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.5</v>
       </c>
       <c r="L27" t="n">
         <v>1.47</v>
       </c>
       <c r="M27" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P27" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U27" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V27" t="n">
         <v>1.48</v>
       </c>
       <c r="W27" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X27" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y27" t="n">
         <v>11</v>
@@ -5670,7 +5670,7 @@
         <v>19</v>
       </c>
       <c r="AA27" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB27" t="n">
         <v>9.6</v>
@@ -5685,7 +5685,7 @@
         <v>36</v>
       </c>
       <c r="AF27" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG27" t="n">
         <v>12</v>
@@ -5715,19 +5715,19 @@
         <v>36</v>
       </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR27" t="n">
         <v>18</v>
       </c>
       <c r="AS27" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT27" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU27" t="n">
         <v>7.2</v>
@@ -5745,7 +5745,7 @@
         <v>11</v>
       </c>
       <c r="AZ27" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA27" t="n">
         <v>44</v>
@@ -5754,7 +5754,7 @@
         <v>36</v>
       </c>
       <c r="BC27" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BD27" t="n">
         <v>40</v>
@@ -5763,14 +5763,14 @@
         <v>95</v>
       </c>
       <c r="BF27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG27" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="G28" t="n">
         <v>2.22</v>
@@ -5810,46 +5810,46 @@
         <v>3.7</v>
       </c>
       <c r="I28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N28" t="n">
         <v>3.85</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.8</v>
-      </c>
       <c r="O28" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P28" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S28" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="T28" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U28" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V28" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W28" t="n">
         <v>1.81</v>
@@ -5864,10 +5864,10 @@
         <v>500</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC28" t="n">
         <v>8.4</v>
@@ -5879,7 +5879,7 @@
         <v>500</v>
       </c>
       <c r="AF28" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AG28" t="n">
         <v>11.5</v>
@@ -5897,74 +5897,74 @@
         <v>65</v>
       </c>
       <c r="AL28" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>18.5</v>
+        <v>55</v>
       </c>
       <c r="AO28" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ28" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ28" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AR28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU28" t="n">
         <v>7</v>
       </c>
-      <c r="AS28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU28" t="n">
+      <c r="AV28" t="n">
         <v>6.6</v>
       </c>
-      <c r="AV28" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AW28" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AX28" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="AY28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC28" t="n">
         <v>8.4</v>
       </c>
-      <c r="AZ28" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>17</v>
-      </c>
       <c r="BD28" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF28" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -5995,64 +5995,64 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="G29" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="H29" t="n">
         <v>6.8</v>
       </c>
       <c r="I29" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J29" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K29" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O29" t="n">
         <v>1.34</v>
       </c>
-      <c r="M29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.31</v>
-      </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="T29" t="n">
         <v>2.04</v>
       </c>
       <c r="U29" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V29" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W29" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z29" t="n">
         <v>1000</v>
@@ -6061,22 +6061,22 @@
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>13</v>
+        <v>7.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>20</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AE29" t="n">
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="AG29" t="n">
-        <v>19</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH29" t="n">
         <v>65</v>
@@ -6085,80 +6085,80 @@
         <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>180</v>
+        <v>26</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>29</v>
+        <v>11.5</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="AQ29" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="AR29" t="n">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AX29" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="BB29" t="n">
         <v>12</v>
       </c>
       <c r="BC29" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BD29" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -6189,170 +6189,170 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G30" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H30" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I30" t="n">
         <v>3.45</v>
       </c>
       <c r="J30" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
         <v>4.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="M30" t="n">
         <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O30" t="n">
         <v>1.2</v>
       </c>
       <c r="P30" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S30" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="T30" t="n">
         <v>1.56</v>
       </c>
       <c r="U30" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V30" t="n">
         <v>1.41</v>
       </c>
       <c r="W30" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="X30" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="Y30" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="Z30" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AA30" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AB30" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AC30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP30" t="n">
         <v>12</v>
       </c>
-      <c r="AD30" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AQ30" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AR30" t="n">
-        <v>3.9</v>
+        <v>15</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.1</v>
+        <v>29</v>
       </c>
       <c r="AT30" t="n">
         <v>12</v>
       </c>
       <c r="AU30" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC30" t="n">
         <v>11</v>
       </c>
-      <c r="AW30" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>14</v>
-      </c>
       <c r="BD30" t="n">
-        <v>3.9</v>
+        <v>15</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -6383,91 +6383,91 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="G31" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="H31" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="I31" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="J31" t="n">
         <v>4</v>
       </c>
       <c r="K31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N31" t="n">
         <v>4.2</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N31" t="n">
-        <v>4.1</v>
       </c>
       <c r="O31" t="n">
         <v>1.29</v>
       </c>
       <c r="P31" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S31" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T31" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U31" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V31" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="W31" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X31" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AB31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH31" t="n">
         <v>18.5</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>19.5</v>
       </c>
       <c r="AI31" t="n">
         <v>34</v>
@@ -6476,31 +6476,31 @@
         <v>700</v>
       </c>
       <c r="AK31" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AL31" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AM31" t="n">
         <v>320</v>
       </c>
       <c r="AN31" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO31" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AP31" t="n">
         <v>15</v>
       </c>
       <c r="AQ31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR31" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AT31" t="n">
         <v>15</v>
@@ -6512,41 +6512,41 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW31" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX31" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AY31" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA31" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BB31" t="n">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="BC31" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="BD31" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BE31" t="n">
         <v>44</v>
       </c>
       <c r="BF31" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="BG31" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="G32" t="n">
         <v>1.62</v>
@@ -6586,13 +6586,13 @@
         <v>5.8</v>
       </c>
       <c r="I32" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J32" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K32" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -6774,55 +6774,55 @@
         <v>2.3</v>
       </c>
       <c r="G33" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H33" t="n">
         <v>3.2</v>
       </c>
       <c r="I33" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>3.5</v>
       </c>
       <c r="K33" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L33" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M33" t="n">
         <v>1.05</v>
       </c>
       <c r="N33" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O33" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P33" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="R33" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S33" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U33" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V33" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W33" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X33" t="n">
         <v>19</v>
@@ -6834,7 +6834,7 @@
         <v>26</v>
       </c>
       <c r="AA33" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AB33" t="n">
         <v>13</v>
@@ -6876,7 +6876,7 @@
         <v>16.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP33" t="n">
         <v>15.5</v>
@@ -6885,7 +6885,7 @@
         <v>13</v>
       </c>
       <c r="AR33" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AS33" t="n">
         <v>23</v>
@@ -6900,7 +6900,7 @@
         <v>12</v>
       </c>
       <c r="AW33" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="AX33" t="n">
         <v>14</v>
@@ -6912,7 +6912,7 @@
         <v>13.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BB33" t="n">
         <v>24</v>
@@ -6930,11 +6930,11 @@
         <v>13.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -6965,46 +6965,46 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G34" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H34" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I34" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J34" t="n">
         <v>3.7</v>
       </c>
       <c r="K34" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L34" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="M34" t="n">
         <v>1.04</v>
       </c>
       <c r="N34" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P34" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="R34" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S34" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="T34" t="n">
         <v>1.6</v>
@@ -7016,25 +7016,25 @@
         <v>1.43</v>
       </c>
       <c r="W34" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y34" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA34" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB34" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD34" t="n">
         <v>16.5</v>
@@ -7043,37 +7043,37 @@
         <v>38</v>
       </c>
       <c r="AF34" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI34" t="n">
         <v>44</v>
       </c>
       <c r="AJ34" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL34" t="n">
         <v>36</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>38</v>
       </c>
       <c r="AM34" t="n">
         <v>75</v>
       </c>
       <c r="AN34" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO34" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP34" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ34" t="n">
         <v>14</v>
@@ -7082,7 +7082,7 @@
         <v>20</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT34" t="n">
         <v>11.5</v>
@@ -7100,35 +7100,35 @@
         <v>15</v>
       </c>
       <c r="AY34" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AZ34" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.8</v>
+        <v>30</v>
       </c>
       <c r="BB34" t="n">
         <v>14.5</v>
       </c>
       <c r="BC34" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BD34" t="n">
         <v>14.5</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF34" t="n">
         <v>11</v>
       </c>
       <c r="BG34" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -7159,16 +7159,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G35" t="n">
         <v>2.24</v>
       </c>
       <c r="H35" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I35" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J35" t="n">
         <v>3.85</v>
@@ -7177,34 +7177,34 @@
         <v>4.2</v>
       </c>
       <c r="L35" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="M35" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N35" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O35" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P35" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="R35" t="n">
         <v>1.59</v>
       </c>
       <c r="S35" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="T35" t="n">
         <v>1.58</v>
       </c>
       <c r="U35" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V35" t="n">
         <v>1.4</v>
@@ -7213,116 +7213,116 @@
         <v>1.8</v>
       </c>
       <c r="X35" t="n">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="Y35" t="n">
         <v>22</v>
       </c>
       <c r="Z35" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA35" t="n">
-        <v>160</v>
+        <v>440</v>
       </c>
       <c r="AB35" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AC35" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG35" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>14</v>
       </c>
       <c r="AH35" t="n">
         <v>18.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="AJ35" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AK35" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="AL35" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AM35" t="n">
-        <v>75</v>
+        <v>250</v>
       </c>
       <c r="AN35" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AO35" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AP35" t="n">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="AQ35" t="n">
         <v>9</v>
       </c>
       <c r="AR35" t="n">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="AT35" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU35" t="n">
         <v>8.4</v>
       </c>
       <c r="AV35" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="AY35" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AZ35" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.4</v>
+        <v>30</v>
       </c>
       <c r="BB35" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.2</v>
+        <v>24</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="BF35" t="n">
         <v>10</v>
       </c>
       <c r="BG35" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -7353,46 +7353,46 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="G36" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="H36" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="I36" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J36" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K36" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L36" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M36" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N36" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P36" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R36" t="n">
         <v>1.28</v>
       </c>
       <c r="S36" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T36" t="n">
         <v>1.98</v>
@@ -7401,16 +7401,16 @@
         <v>1.89</v>
       </c>
       <c r="V36" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="W36" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="X36" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="Y36" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Z36" t="n">
         <v>500</v>
@@ -7419,31 +7419,31 @@
         <v>700</v>
       </c>
       <c r="AB36" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC36" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AE36" t="n">
         <v>700</v>
       </c>
       <c r="AF36" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AG36" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH36" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="AI36" t="n">
         <v>700</v>
       </c>
       <c r="AJ36" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AK36" t="n">
         <v>26</v>
@@ -7464,13 +7464,13 @@
         <v>10</v>
       </c>
       <c r="AQ36" t="n">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="AR36" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AS36" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT36" t="n">
         <v>6.6</v>
@@ -7479,10 +7479,10 @@
         <v>7</v>
       </c>
       <c r="AV36" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AW36" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="AX36" t="n">
         <v>9.4</v>
@@ -7491,32 +7491,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ36" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BA36" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BB36" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BC36" t="n">
-        <v>18.5</v>
+        <v>6</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BE36" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF36" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG36" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -7550,88 +7550,88 @@
         <v>5.8</v>
       </c>
       <c r="G37" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="H37" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="I37" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="J37" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K37" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L37" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="M37" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N37" t="n">
         <v>2.4</v>
       </c>
       <c r="O37" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="P37" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="R37" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S37" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="T37" t="n">
         <v>2.42</v>
       </c>
       <c r="U37" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="V37" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W37" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X37" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z37" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA37" t="n">
-        <v>25</v>
+        <v>900</v>
       </c>
       <c r="AB37" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD37" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AF37" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AG37" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AH37" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AI37" t="n">
         <v>1000</v>
@@ -7652,65 +7652,65 @@
         <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP37" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ37" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AR37" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS37" t="n">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="AT37" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU37" t="n">
         <v>7</v>
       </c>
       <c r="AV37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW37" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AW37" t="n">
-        <v>23</v>
-      </c>
       <c r="AX37" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AY37" t="n">
-        <v>22</v>
+        <v>9.4</v>
       </c>
       <c r="AZ37" t="n">
-        <v>28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA37" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB37" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC37" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BE37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF37" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG37" t="n">
-        <v>18.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -7744,43 +7744,43 @@
         <v>3.35</v>
       </c>
       <c r="G38" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="H38" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="I38" t="n">
         <v>3.1</v>
       </c>
       <c r="J38" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="K38" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="M38" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O38" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="P38" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="R38" t="n">
         <v>1.12</v>
       </c>
       <c r="S38" t="n">
-        <v>1.02</v>
+        <v>8.6</v>
       </c>
       <c r="T38" t="n">
         <v>1.05</v>
@@ -7792,7 +7792,7 @@
         <v>1.48</v>
       </c>
       <c r="W38" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="X38" t="n">
         <v>14</v>
@@ -7855,10 +7855,10 @@
         <v>4.2</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AT38" t="n">
         <v>4.2</v>
@@ -7867,44 +7867,44 @@
         <v>4.2</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AX38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY38" t="n">
         <v>1.74</v>
       </c>
-      <c r="AY38" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AZ38" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="BA38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB38" t="n">
         <v>1.79</v>
       </c>
-      <c r="BB38" t="n">
-        <v>1.78</v>
-      </c>
       <c r="BC38" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BD38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG38" t="n">
         <v>1.79</v>
       </c>
-      <c r="BE38" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>1.77</v>
-      </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -7935,61 +7935,61 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="G39" t="n">
         <v>1.78</v>
       </c>
       <c r="H39" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I39" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J39" t="n">
         <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L39" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M39" t="n">
         <v>1.05</v>
       </c>
       <c r="N39" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O39" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P39" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="R39" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S39" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="T39" t="n">
         <v>1.72</v>
       </c>
       <c r="U39" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V39" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W39" t="n">
         <v>2.28</v>
       </c>
       <c r="X39" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="Y39" t="n">
         <v>38</v>
@@ -8001,13 +8001,13 @@
         <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC39" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD39" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE39" t="n">
         <v>1000</v>
@@ -8028,13 +8028,13 @@
         <v>21</v>
       </c>
       <c r="AK39" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AL39" t="n">
         <v>75</v>
       </c>
       <c r="AM39" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN39" t="n">
         <v>9.6</v>
@@ -8043,16 +8043,16 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ39" t="n">
         <v>18</v>
       </c>
       <c r="AR39" t="n">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="AS39" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT39" t="n">
         <v>9</v>
@@ -8064,41 +8064,41 @@
         <v>17</v>
       </c>
       <c r="AW39" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AX39" t="n">
         <v>10</v>
       </c>
       <c r="AY39" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ39" t="n">
         <v>15.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB39" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC39" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD39" t="n">
         <v>22</v>
       </c>
       <c r="BE39" t="n">
-        <v>7.4</v>
+        <v>60</v>
       </c>
       <c r="BF39" t="n">
         <v>7.8</v>
       </c>
       <c r="BG39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -8129,58 +8129,58 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G40" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H40" t="n">
         <v>15.5</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="J40" t="n">
         <v>10</v>
       </c>
       <c r="K40" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="L40" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="M40" t="n">
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="O40" t="n">
         <v>1.09</v>
       </c>
       <c r="P40" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R40" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="S40" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="T40" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="U40" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V40" t="n">
         <v>1.05</v>
       </c>
       <c r="W40" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="X40" t="n">
         <v>240</v>
@@ -8195,7 +8195,7 @@
         <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="AC40" t="n">
         <v>28</v>
@@ -8204,13 +8204,13 @@
         <v>300</v>
       </c>
       <c r="AE40" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AF40" t="n">
         <v>11</v>
       </c>
       <c r="AG40" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH40" t="n">
         <v>46</v>
@@ -8219,10 +8219,10 @@
         <v>460</v>
       </c>
       <c r="AJ40" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK40" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="AL40" t="n">
         <v>70</v>
@@ -8231,22 +8231,22 @@
         <v>380</v>
       </c>
       <c r="AN40" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="AO40" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AP40" t="n">
         <v>50</v>
       </c>
       <c r="AQ40" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AR40" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AS40" t="n">
-        <v>11.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT40" t="n">
         <v>14</v>
@@ -8255,10 +8255,10 @@
         <v>19.5</v>
       </c>
       <c r="AV40" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX40" t="n">
         <v>9.199999999999999</v>
@@ -8270,13 +8270,13 @@
         <v>14.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BB40" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC40" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD40" t="n">
         <v>25</v>
@@ -8288,11 +8288,11 @@
         <v>2.46</v>
       </c>
       <c r="BG40" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -8517,46 +8517,46 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="G42" t="n">
-        <v>2.64</v>
+        <v>2.34</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="I42" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="J42" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K42" t="n">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M42" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N42" t="n">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="O42" t="n">
         <v>1.33</v>
       </c>
       <c r="P42" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="R42" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="S42" t="n">
-        <v>2.04</v>
+        <v>3.55</v>
       </c>
       <c r="T42" t="n">
         <v>1.11</v>
@@ -8565,10 +8565,10 @@
         <v>1.11</v>
       </c>
       <c r="V42" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="W42" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -8711,22 +8711,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="G43" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="H43" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I43" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K43" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L43" t="n">
         <v>1.22</v>
@@ -8735,46 +8735,46 @@
         <v>1.02</v>
       </c>
       <c r="N43" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O43" t="n">
         <v>1.12</v>
       </c>
       <c r="P43" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R43" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="S43" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="T43" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="U43" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="V43" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W43" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X43" t="n">
         <v>38</v>
       </c>
       <c r="Y43" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z43" t="n">
         <v>60</v>
       </c>
       <c r="AA43" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB43" t="n">
         <v>17</v>
@@ -8789,40 +8789,40 @@
         <v>55</v>
       </c>
       <c r="AF43" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG43" t="n">
         <v>10.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI43" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ43" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK43" t="n">
         <v>13.5</v>
       </c>
       <c r="AL43" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM43" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AN43" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AO43" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AP43" t="n">
         <v>36</v>
       </c>
       <c r="AQ43" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AR43" t="n">
         <v>50</v>
@@ -8834,47 +8834,47 @@
         <v>16</v>
       </c>
       <c r="AU43" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AV43" t="n">
         <v>21</v>
       </c>
       <c r="AW43" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX43" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY43" t="n">
         <v>10</v>
       </c>
       <c r="AZ43" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA43" t="n">
         <v>42</v>
       </c>
       <c r="BB43" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC43" t="n">
         <v>12.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE43" t="n">
         <v>48</v>
       </c>
       <c r="BF43" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG43" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -8905,16 +8905,16 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G44" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I44" t="n">
         <v>4.6</v>
-      </c>
-      <c r="I44" t="n">
-        <v>4.7</v>
       </c>
       <c r="J44" t="n">
         <v>4.3</v>
@@ -8929,13 +8929,13 @@
         <v>1.04</v>
       </c>
       <c r="N44" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O44" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P44" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q44" t="n">
         <v>1.54</v>
@@ -8944,58 +8944,58 @@
         <v>1.72</v>
       </c>
       <c r="S44" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T44" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U44" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V44" t="n">
         <v>1.27</v>
       </c>
       <c r="W44" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X44" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y44" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z44" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA44" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB44" t="n">
         <v>14.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE44" t="n">
         <v>46</v>
       </c>
       <c r="AF44" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG44" t="n">
         <v>10.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI44" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ44" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AK44" t="n">
         <v>16</v>
@@ -9007,7 +9007,7 @@
         <v>55</v>
       </c>
       <c r="AN44" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO44" t="n">
         <v>34</v>
@@ -9016,22 +9016,22 @@
         <v>24</v>
       </c>
       <c r="AQ44" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR44" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS44" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AT44" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU44" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV44" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW44" t="n">
         <v>42</v>
@@ -9046,13 +9046,13 @@
         <v>14.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB44" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC44" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD44" t="n">
         <v>23</v>
@@ -9061,14 +9061,14 @@
         <v>50</v>
       </c>
       <c r="BF44" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG44" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -9099,46 +9099,46 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="G45" t="n">
-        <v>3.5</v>
+        <v>110</v>
       </c>
       <c r="H45" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="I45" t="n">
         <v>2.98</v>
       </c>
       <c r="J45" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S45" t="n">
         <v>3</v>
-      </c>
-      <c r="K45" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N45" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.36</v>
       </c>
       <c r="T45" t="n">
         <v>1.11</v>
@@ -9150,7 +9150,7 @@
         <v>1.5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -9293,64 +9293,64 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="G46" t="n">
         <v>1.7</v>
       </c>
       <c r="H46" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I46" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J46" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K46" t="n">
         <v>4.4</v>
       </c>
       <c r="L46" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="M46" t="n">
         <v>1.06</v>
       </c>
       <c r="N46" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O46" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P46" t="n">
         <v>1.99</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="R46" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S46" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T46" t="n">
         <v>1.89</v>
       </c>
       <c r="U46" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V46" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W46" t="n">
         <v>2.42</v>
       </c>
       <c r="X46" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z46" t="n">
         <v>1000</v>
@@ -9365,7 +9365,7 @@
         <v>9.6</v>
       </c>
       <c r="AD46" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE46" t="n">
         <v>1000</v>
@@ -9386,7 +9386,7 @@
         <v>1000</v>
       </c>
       <c r="AK46" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL46" t="n">
         <v>1000</v>
@@ -9404,13 +9404,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ46" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AR46" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS46" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT46" t="n">
         <v>7.2</v>
@@ -9422,7 +9422,7 @@
         <v>16.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX46" t="n">
         <v>8.6</v>
@@ -9431,32 +9431,32 @@
         <v>8.6</v>
       </c>
       <c r="AZ46" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="BA46" t="n">
-        <v>8.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="BB46" t="n">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="BC46" t="n">
         <v>13.5</v>
       </c>
       <c r="BD46" t="n">
-        <v>7.8</v>
+        <v>26</v>
       </c>
       <c r="BE46" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BF46" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG46" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
         <v>1.04</v>
       </c>
       <c r="G47" t="n">
-        <v>1000</v>
+        <v>1.6</v>
       </c>
       <c r="H47" t="n">
         <v>1.04</v>
@@ -9595,62 +9595,62 @@
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-08 00:19:01</t>
+          <t>2026-04-08 02:28:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J2" t="n">
         <v>3.55</v>
       </c>
-      <c r="G2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.6</v>
-      </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.4</v>
@@ -781,67 +781,67 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V2" t="n">
         <v>1.81</v>
       </c>
       <c r="W2" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="n">
         <v>14</v>
       </c>
-      <c r="AA2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>15</v>
-      </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AF2" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AG2" t="n">
-        <v>80</v>
+        <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
         <v>500</v>
@@ -850,7 +850,7 @@
         <v>250</v>
       </c>
       <c r="AK2" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AL2" t="n">
         <v>500</v>
@@ -862,13 +862,13 @@
         <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2" t="n">
         <v>12</v>
@@ -877,50 +877,50 @@
         <v>22</v>
       </c>
       <c r="AT2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF2" t="n">
         <v>10</v>
       </c>
-      <c r="AX2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="U3" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X3" t="n">
         <v>13</v>
@@ -1011,40 +1011,40 @@
         <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB3" t="n">
         <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD3" t="n">
         <v>14.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="AF3" t="n">
         <v>18.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1056,19 +1056,19 @@
         <v>32</v>
       </c>
       <c r="AO3" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
         <v>9.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT3" t="n">
         <v>8.4</v>
@@ -1083,38 +1083,38 @@
         <v>30</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.2</v>
+        <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H4" t="n">
         <v>3.55</v>
       </c>
       <c r="I4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L4" t="n">
         <v>1.55</v>
@@ -1172,31 +1172,31 @@
         <v>2.92</v>
       </c>
       <c r="O4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P4" t="n">
         <v>1.62</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
         <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T4" t="n">
         <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X4" t="n">
         <v>10.5</v>
@@ -1205,7 +1205,7 @@
         <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="AA4" t="n">
         <v>260</v>
@@ -1223,7 +1223,7 @@
         <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="n">
         <v>12.5</v>
@@ -1238,7 +1238,7 @@
         <v>75</v>
       </c>
       <c r="AK4" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AL4" t="n">
         <v>120</v>
@@ -1256,7 +1256,7 @@
         <v>8.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR4" t="n">
         <v>21</v>
@@ -1268,7 +1268,7 @@
         <v>7</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
         <v>13.5</v>
@@ -1286,29 +1286,29 @@
         <v>18.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
         <v>16.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -1339,64 +1339,64 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S5" t="n">
         <v>2.96</v>
       </c>
-      <c r="G5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.35</v>
-      </c>
       <c r="T5" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="U5" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="V5" t="n">
         <v>1.59</v>
       </c>
       <c r="W5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z5" t="n">
         <v>19</v>
@@ -1405,16 +1405,16 @@
         <v>120</v>
       </c>
       <c r="AB5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD5" t="n">
         <v>13</v>
       </c>
-      <c r="AC5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AE5" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AF5" t="n">
         <v>22</v>
@@ -1423,86 +1423,86 @@
         <v>13.5</v>
       </c>
       <c r="AH5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>210</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR5" t="n">
         <v>16</v>
       </c>
-      <c r="AI5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>150</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>15</v>
-      </c>
       <c r="AS5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AT5" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV5" t="n">
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY5" t="n">
         <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA5" t="n">
-        <v>30</v>
+        <v>8.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>38</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="BE5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BF5" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P6" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R6" t="n">
         <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T6" t="n">
         <v>2.08</v>
@@ -1611,7 +1611,7 @@
         <v>20</v>
       </c>
       <c r="AF6" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AG6" t="n">
         <v>42</v>
@@ -1653,7 +1653,7 @@
         <v>11</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AU6" t="n">
         <v>7.6</v>
@@ -1665,16 +1665,16 @@
         <v>14.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY6" t="n">
         <v>16</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.6</v>
+        <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BB6" t="n">
         <v>6.6</v>
@@ -1683,20 +1683,20 @@
         <v>6.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF6" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6.4</v>
       </c>
       <c r="BG6" t="n">
         <v>8.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.92</v>
+        <v>2.48</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="H7" t="n">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="J7" t="n">
         <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
         <v>1.48</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
         <v>1.39</v>
@@ -1760,137 +1760,137 @@
         <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R7" t="n">
         <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
         <v>1.98</v>
       </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
         <v>7.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AE7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK7" t="n">
         <v>34</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AL7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA7" t="n">
         <v>22</v>
       </c>
-      <c r="AG7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>200</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AQ7" t="n">
+      <c r="BB7" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD7" t="n">
         <v>8</v>
       </c>
-      <c r="AR7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BE7" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.5</v>
+        <v>22</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="G8" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="H8" t="n">
         <v>4.1</v>
@@ -1933,10 +1933,10 @@
         <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.41</v>
@@ -1945,58 +1945,58 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
         <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="U8" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
         <v>1.96</v>
       </c>
       <c r="X8" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Z8" t="n">
         <v>36</v>
       </c>
       <c r="AA8" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AF8" t="n">
         <v>12.5</v>
@@ -2005,86 +2005,86 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AJ8" t="n">
         <v>23</v>
       </c>
       <c r="AK8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM8" t="n">
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="AP8" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AR8" t="n">
         <v>13.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT8" t="n">
         <v>7.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.6</v>
+        <v>25</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.8</v>
+        <v>27</v>
       </c>
       <c r="BB8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC8" t="n">
         <v>17.5</v>
       </c>
-      <c r="BC8" t="n">
-        <v>16</v>
-      </c>
       <c r="BD8" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BE8" t="n">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="BF8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG8" t="n">
         <v>10</v>
       </c>
-      <c r="BG8" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -2115,58 +2115,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="G9" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="H9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="T9" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="U9" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="X9" t="n">
         <v>14</v>
@@ -2181,7 +2181,7 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="AC9" t="n">
         <v>42</v>
@@ -2193,10 +2193,10 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>7.6</v>
+        <v>40</v>
       </c>
       <c r="AG9" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
         <v>1000</v>
@@ -2205,10 +2205,10 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU9" t="n">
         <v>5.2</v>
       </c>
-      <c r="AU9" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AV9" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BB9" t="n">
         <v>5.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G10" t="n">
         <v>2.28</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J10" t="n">
         <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
         <v>1.36</v>
@@ -2333,7 +2333,7 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.26</v>
@@ -2342,13 +2342,13 @@
         <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R10" t="n">
         <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T10" t="n">
         <v>1.67</v>
@@ -2366,25 +2366,25 @@
         <v>20</v>
       </c>
       <c r="Y10" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA10" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AB10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC10" t="n">
         <v>9.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF10" t="n">
         <v>17</v>
@@ -2402,7 +2402,7 @@
         <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL10" t="n">
         <v>36</v>
@@ -2411,34 +2411,34 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV10" t="n">
         <v>13</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>17.5</v>
       </c>
       <c r="AX10" t="n">
         <v>13.5</v>
@@ -2450,16 +2450,16 @@
         <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="BB10" t="n">
         <v>13.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="BD10" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="BE10" t="n">
         <v>32</v>
@@ -2468,11 +2468,11 @@
         <v>12.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -2503,61 +2503,61 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G11" t="n">
         <v>3.2</v>
       </c>
       <c r="H11" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="I11" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="M11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="O11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.56</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.59</v>
       </c>
       <c r="W11" t="n">
         <v>1.45</v>
       </c>
       <c r="X11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Y11" t="n">
         <v>8</v>
@@ -2566,10 +2566,10 @@
         <v>16</v>
       </c>
       <c r="AA11" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC11" t="n">
         <v>7.2</v>
@@ -2578,7 +2578,7 @@
         <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF11" t="n">
         <v>19</v>
@@ -2587,55 +2587,55 @@
         <v>14.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>380</v>
+        <v>70</v>
       </c>
       <c r="AJ11" t="n">
         <v>60</v>
       </c>
       <c r="AK11" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AL11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM11" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
         <v>70</v>
       </c>
       <c r="AO11" t="n">
-        <v>600</v>
+        <v>46</v>
       </c>
       <c r="AP11" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ11" t="n">
         <v>7.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV11" t="n">
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="AX11" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY11" t="n">
         <v>13.5</v>
@@ -2644,29 +2644,29 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BB11" t="n">
         <v>28</v>
       </c>
       <c r="BC11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="BF11" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BG11" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="G12" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="H12" t="n">
-        <v>2.86</v>
+        <v>2.64</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
         <v>3.8</v>
@@ -2721,146 +2721,146 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U12" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="W12" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="X12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF12" t="n">
         <v>21</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AG12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP12" t="n">
         <v>15</v>
       </c>
-      <c r="Z12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="AQ12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX12" t="n">
         <v>17</v>
       </c>
-      <c r="AI12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AY12" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.8</v>
+        <v>17.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -2894,19 +2894,19 @@
         <v>14.5</v>
       </c>
       <c r="G13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="I13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="J13" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
         <v>1.41</v>
@@ -2924,7 +2924,7 @@
         <v>1.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R13" t="n">
         <v>1.35</v>
@@ -2933,13 +2933,13 @@
         <v>3.55</v>
       </c>
       <c r="T13" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="U13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="V13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="W13" t="n">
         <v>1.06</v>
@@ -2948,7 +2948,7 @@
         <v>16</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Z13" t="n">
         <v>6.6</v>
@@ -2957,16 +2957,16 @@
         <v>9.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AC13" t="n">
         <v>13.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AF13" t="n">
         <v>160</v>
@@ -2987,19 +2987,19 @@
         <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="AO13" t="n">
         <v>6.8</v>
       </c>
       <c r="AP13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
         <v>6</v>
@@ -3017,7 +3017,7 @@
         <v>12</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW13" t="n">
         <v>15</v>
@@ -3026,35 +3026,35 @@
         <v>15</v>
       </c>
       <c r="AY13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ13" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="BA13" t="n">
         <v>27</v>
       </c>
       <c r="BB13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC13" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="BD13" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BE13" t="n">
         <v>30</v>
       </c>
       <c r="BF13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -3085,25 +3085,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G14" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="H14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M14" t="n">
         <v>1.12</v>
@@ -3112,10 +3112,10 @@
         <v>2.74</v>
       </c>
       <c r="O14" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q14" t="n">
         <v>2.62</v>
@@ -3124,28 +3124,28 @@
         <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="U14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V14" t="n">
         <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="X14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y14" t="n">
         <v>15</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
@@ -3157,64 +3157,64 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>900</v>
+        <v>32</v>
       </c>
       <c r="AK14" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>600</v>
+        <v>40</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR14" t="n">
         <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU14" t="n">
         <v>6.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AX14" t="n">
         <v>8.199999999999999</v>
@@ -3223,32 +3223,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="BC14" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BE14" t="n">
         <v>36</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G15" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="I15" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J15" t="n">
         <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L15" t="n">
         <v>1.46</v>
@@ -3309,7 +3309,7 @@
         <v>1.38</v>
       </c>
       <c r="P15" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q15" t="n">
         <v>2.16</v>
@@ -3318,7 +3318,7 @@
         <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T15" t="n">
         <v>1.86</v>
@@ -3327,16 +3327,16 @@
         <v>1.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X15" t="n">
         <v>12.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z15" t="n">
         <v>85</v>
@@ -3345,52 +3345,52 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD15" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>230</v>
+        <v>100</v>
       </c>
       <c r="AF15" t="n">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="AG15" t="n">
         <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AJ15" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="AK15" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO15" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AP15" t="n">
         <v>10</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR15" t="n">
         <v>13.5</v>
@@ -3405,7 +3405,7 @@
         <v>6.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW15" t="n">
         <v>20</v>
@@ -3420,7 +3420,7 @@
         <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BB15" t="n">
         <v>12</v>
@@ -3429,20 +3429,20 @@
         <v>13.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG15" t="n">
         <v>10.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -3473,52 +3473,52 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H16" t="n">
         <v>2.7</v>
       </c>
       <c r="I16" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O16" t="n">
         <v>1.51</v>
       </c>
-      <c r="M16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.47</v>
-      </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S16" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U16" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="V16" t="n">
         <v>1.53</v>
@@ -3527,73 +3527,73 @@
         <v>1.47</v>
       </c>
       <c r="X16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC16" t="n">
         <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AF16" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AG16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI16" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AJ16" t="n">
         <v>55</v>
       </c>
       <c r="AK16" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AL16" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO16" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT16" t="n">
         <v>7.8</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="AU16" t="n">
         <v>6.2</v>
@@ -3602,41 +3602,41 @@
         <v>12</v>
       </c>
       <c r="AW16" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="BC16" t="n">
         <v>17.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -3667,70 +3667,70 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.56</v>
+        <v>2.86</v>
       </c>
       <c r="G17" t="n">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="I17" t="n">
-        <v>2.96</v>
+        <v>2.64</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
         <v>1.27</v>
       </c>
       <c r="P17" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
         <v>1.81</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="X17" t="n">
         <v>90</v>
       </c>
       <c r="Y17" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="Z17" t="n">
         <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
         <v>1000</v>
@@ -3739,7 +3739,7 @@
         <v>8.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
@@ -3748,7 +3748,7 @@
         <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH17" t="n">
         <v>34</v>
@@ -3769,68 +3769,68 @@
         <v>580</v>
       </c>
       <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
         <v>55</v>
       </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS17" t="n">
+      <c r="BA17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB17" t="n">
         <v>10</v>
       </c>
-      <c r="AT17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BC17" t="n">
-        <v>17.5</v>
+        <v>9.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>1.48</v>
       </c>
       <c r="G18" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H18" t="n">
         <v>6.2</v>
@@ -3885,19 +3885,19 @@
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
         <v>1.16</v>
       </c>
       <c r="P18" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="S18" t="n">
         <v>2.24</v>
@@ -3912,7 +3912,7 @@
         <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="X18" t="n">
         <v>80</v>
@@ -4011,7 +4011,7 @@
         <v>10.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="BE18" t="n">
         <v>8.800000000000001</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="H19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="I19" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="J19" t="n">
         <v>4.5</v>
       </c>
       <c r="K19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L19" t="n">
         <v>1.36</v>
@@ -4079,7 +4079,7 @@
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O19" t="n">
         <v>1.26</v>
@@ -4088,7 +4088,7 @@
         <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R19" t="n">
         <v>1.46</v>
@@ -4097,22 +4097,22 @@
         <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U19" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V19" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="W19" t="n">
         <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z19" t="n">
         <v>9.6</v>
@@ -4133,16 +4133,16 @@
         <v>17</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AG19" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AH19" t="n">
         <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AJ19" t="n">
         <v>1000</v>
@@ -4160,65 +4160,65 @@
         <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR19" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AS19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT19" t="n">
         <v>20</v>
       </c>
       <c r="AU19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX19" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>9</v>
       </c>
       <c r="AY19" t="n">
         <v>22</v>
       </c>
       <c r="AZ19" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA19" t="n">
         <v>14.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>9.6</v>
+        <v>60</v>
       </c>
       <c r="BE19" t="n">
-        <v>28</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF19" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="H20" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I20" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J20" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K20" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L20" t="n">
         <v>1.49</v>
@@ -4279,140 +4279,140 @@
         <v>1.42</v>
       </c>
       <c r="P20" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R20" t="n">
         <v>1.27</v>
       </c>
       <c r="S20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U20" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V20" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W20" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="X20" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Y20" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD20" t="n">
         <v>15.5</v>
       </c>
-      <c r="Z20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>21</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF20" t="n">
         <v>12.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>42</v>
+        <v>19.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AJ20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK20" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL20" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM20" t="n">
         <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV20" t="n">
         <v>14</v>
       </c>
       <c r="AW20" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC20" t="n">
         <v>14</v>
       </c>
-      <c r="BA20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB20" t="n">
+      <c r="BD20" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE20" t="n">
         <v>23</v>
       </c>
-      <c r="BC20" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BF20" t="n">
-        <v>5.3</v>
+        <v>21</v>
       </c>
       <c r="BG20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -4443,67 +4443,67 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="G21" t="n">
         <v>7.2</v>
       </c>
       <c r="H21" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="I21" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="J21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L21" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M21" t="n">
         <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="O21" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P21" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="S21" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="T21" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="U21" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V21" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="W21" t="n">
         <v>1.16</v>
       </c>
       <c r="X21" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y21" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA21" t="n">
         <v>17</v>
@@ -4512,13 +4512,13 @@
         <v>28</v>
       </c>
       <c r="AC21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF21" t="n">
         <v>60</v>
@@ -4527,10 +4527,10 @@
         <v>29</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AJ21" t="n">
         <v>1000</v>
@@ -4539,34 +4539,34 @@
         <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AP21" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AS21" t="n">
         <v>12.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU21" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV21" t="n">
         <v>8.800000000000001</v>
@@ -4575,7 +4575,7 @@
         <v>13.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>8.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="AY21" t="n">
         <v>21</v>
@@ -4587,26 +4587,26 @@
         <v>25</v>
       </c>
       <c r="BB21" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD21" t="n">
         <v>55</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BF21" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -4637,64 +4637,64 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G22" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
       </c>
       <c r="I22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J22" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K22" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="O22" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="T22" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="U22" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V22" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W22" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -4703,10 +4703,10 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD22" t="n">
         <v>42</v>
@@ -4715,7 +4715,7 @@
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
@@ -4730,34 +4730,34 @@
         <v>12.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL22" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ22" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AR22" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="AS22" t="n">
         <v>10.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU22" t="n">
         <v>9.4</v>
@@ -4766,41 +4766,41 @@
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX22" t="n">
         <v>6.8</v>
       </c>
       <c r="AY22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB22" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BC22" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE22" t="n">
         <v>13</v>
       </c>
-      <c r="BD22" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>10</v>
-      </c>
       <c r="BF22" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -4831,58 +4831,58 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="G23" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="H23" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="J23" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="K23" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P23" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="S23" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="T23" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="U23" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="V23" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4897,10 +4897,10 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AD23" t="n">
         <v>1000</v>
@@ -4909,7 +4909,7 @@
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG23" t="n">
         <v>1000</v>
@@ -4921,7 +4921,7 @@
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
         <v>1000</v>
@@ -4933,68 +4933,68 @@
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="AS23" t="n">
         <v>4.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AU23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY23" t="n">
         <v>6.6</v>
       </c>
-      <c r="AV23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AZ23" t="n">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="BA23" t="n">
         <v>10</v>
       </c>
       <c r="BB23" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BC23" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE23" t="n">
-        <v>3.25</v>
+        <v>10.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.45</v>
+        <v>2.98</v>
       </c>
       <c r="BG23" t="n">
         <v>15</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="G24" t="n">
         <v>1.55</v>
@@ -5037,40 +5037,40 @@
         <v>7.2</v>
       </c>
       <c r="J24" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K24" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="L24" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M24" t="n">
         <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P24" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="R24" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="S24" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="T24" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U24" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V24" t="n">
         <v>1.16</v>
@@ -5079,28 +5079,28 @@
         <v>2.78</v>
       </c>
       <c r="X24" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y24" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Z24" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC24" t="n">
         <v>12.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE24" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
         <v>12</v>
@@ -5112,7 +5112,7 @@
         <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AJ24" t="n">
         <v>15</v>
@@ -5127,25 +5127,25 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP24" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR24" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS24" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT24" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU24" t="n">
         <v>10</v>
@@ -5154,7 +5154,7 @@
         <v>21</v>
       </c>
       <c r="AW24" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX24" t="n">
         <v>9.6</v>
@@ -5166,29 +5166,29 @@
         <v>17</v>
       </c>
       <c r="BA24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC24" t="n">
         <v>12</v>
       </c>
       <c r="BD24" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -5222,13 +5222,13 @@
         <v>5.6</v>
       </c>
       <c r="G25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H25" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="I25" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>4</v>
@@ -5249,16 +5249,16 @@
         <v>1.26</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R25" t="n">
         <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
         <v>1.8</v>
@@ -5267,7 +5267,7 @@
         <v>2.04</v>
       </c>
       <c r="V25" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="W25" t="n">
         <v>1.18</v>
@@ -5336,7 +5336,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS25" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="AT25" t="n">
         <v>18</v>
@@ -5351,28 +5351,28 @@
         <v>14.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY25" t="n">
-        <v>7.4</v>
+        <v>14</v>
       </c>
       <c r="AZ25" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="BA25" t="n">
-        <v>8.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BB25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BD25" t="n">
         <v>9</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF25" t="n">
         <v>9.199999999999999</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>2.08</v>
       </c>
       <c r="G26" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H26" t="n">
         <v>3.7</v>
@@ -5425,10 +5425,10 @@
         <v>4.2</v>
       </c>
       <c r="J26" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L26" t="n">
         <v>1.42</v>
@@ -5437,7 +5437,7 @@
         <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O26" t="n">
         <v>1.32</v>
@@ -5449,7 +5449,7 @@
         <v>1.98</v>
       </c>
       <c r="R26" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
         <v>3.4</v>
@@ -5464,7 +5464,7 @@
         <v>1.31</v>
       </c>
       <c r="W26" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X26" t="n">
         <v>17</v>
@@ -5527,7 +5527,7 @@
         <v>12</v>
       </c>
       <c r="AR26" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AS26" t="n">
         <v>6.2</v>
@@ -5542,7 +5542,7 @@
         <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX26" t="n">
         <v>11.5</v>
@@ -5557,13 +5557,13 @@
         <v>6</v>
       </c>
       <c r="BB26" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC26" t="n">
         <v>19.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.7</v>
+        <v>17.5</v>
       </c>
       <c r="BE26" t="n">
         <v>6.2</v>
@@ -5572,11 +5572,11 @@
         <v>14</v>
       </c>
       <c r="BG26" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -5613,16 +5613,16 @@
         <v>2.68</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I27" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K27" t="n">
         <v>3.4</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.45</v>
       </c>
       <c r="L27" t="n">
         <v>1.47</v>
@@ -5649,19 +5649,19 @@
         <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U27" t="n">
         <v>2.08</v>
       </c>
       <c r="V27" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W27" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y27" t="n">
         <v>11</v>
@@ -5673,10 +5673,10 @@
         <v>50</v>
       </c>
       <c r="AB27" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD27" t="n">
         <v>13</v>
@@ -5709,7 +5709,7 @@
         <v>110</v>
       </c>
       <c r="AN27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO27" t="n">
         <v>36</v>
@@ -5727,10 +5727,10 @@
         <v>44</v>
       </c>
       <c r="AT27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV27" t="n">
         <v>12</v>
@@ -5739,38 +5739,38 @@
         <v>32</v>
       </c>
       <c r="AX27" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA27" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB27" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
       </c>
       <c r="BD27" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE27" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BF27" t="n">
         <v>26</v>
       </c>
       <c r="BG27" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -5801,170 +5801,170 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="G28" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="H28" t="n">
         <v>3.7</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="J28" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K28" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P28" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R28" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T28" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="U28" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="V28" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W28" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="X28" t="n">
-        <v>34</v>
+        <v>13.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>29</v>
+        <v>14.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AA28" t="n">
-        <v>900</v>
+        <v>75</v>
       </c>
       <c r="AB28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AF28" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AG28" t="n">
         <v>11.5</v>
       </c>
       <c r="AH28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK28" t="n">
         <v>25</v>
       </c>
-      <c r="AI28" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>65</v>
-      </c>
       <c r="AL28" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN28" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="AO28" t="n">
-        <v>600</v>
+        <v>48</v>
       </c>
       <c r="AP28" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR28" t="n">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AS28" t="n">
-        <v>50</v>
+        <v>10.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="AW28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX28" t="n">
         <v>12</v>
       </c>
-      <c r="AX28" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AY28" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="BA28" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BC28" t="n">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="BD28" t="n">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="BE28" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BG28" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -5995,64 +5995,64 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="G29" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="H29" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="I29" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="J29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K29" t="n">
         <v>4.2</v>
       </c>
-      <c r="K29" t="n">
-        <v>4.7</v>
-      </c>
       <c r="L29" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O29" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P29" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="Q29" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T29" t="n">
         <v>2.02</v>
       </c>
-      <c r="R29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.04</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V29" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W29" t="n">
-        <v>2.66</v>
+        <v>2.34</v>
       </c>
       <c r="X29" t="n">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="Y29" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="Z29" t="n">
         <v>1000</v>
@@ -6064,22 +6064,22 @@
         <v>7.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD29" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AE29" t="n">
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AG29" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH29" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AI29" t="n">
         <v>1000</v>
@@ -6088,28 +6088,28 @@
         <v>26</v>
       </c>
       <c r="AK29" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ29" t="n">
         <v>11.5</v>
       </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>9</v>
-      </c>
       <c r="AR29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS29" t="n">
         <v>11.5</v>
@@ -6118,10 +6118,10 @@
         <v>6.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV29" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AW29" t="n">
         <v>11</v>
@@ -6133,7 +6133,7 @@
         <v>8.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="BA29" t="n">
         <v>11</v>
@@ -6145,20 +6145,20 @@
         <v>15</v>
       </c>
       <c r="BD29" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BE29" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF29" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BG29" t="n">
         <v>11.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -6198,13 +6198,13 @@
         <v>3.2</v>
       </c>
       <c r="I30" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L30" t="n">
         <v>1.3</v>
@@ -6342,17 +6342,17 @@
         <v>15</v>
       </c>
       <c r="BE30" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BF30" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="BG30" t="n">
         <v>11.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -6383,19 +6383,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G31" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H31" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="I31" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K31" t="n">
         <v>4.1</v>
@@ -6425,19 +6425,19 @@
         <v>3.25</v>
       </c>
       <c r="T31" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="U31" t="n">
         <v>2.16</v>
       </c>
       <c r="V31" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W31" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X31" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y31" t="n">
         <v>9.6</v>
@@ -6446,7 +6446,7 @@
         <v>12</v>
       </c>
       <c r="AA31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB31" t="n">
         <v>17</v>
@@ -6458,13 +6458,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE31" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF31" t="n">
         <v>34</v>
       </c>
       <c r="AG31" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH31" t="n">
         <v>18.5</v>
@@ -6473,7 +6473,7 @@
         <v>34</v>
       </c>
       <c r="AJ31" t="n">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="n">
         <v>150</v>
@@ -6482,37 +6482,37 @@
         <v>150</v>
       </c>
       <c r="AM31" t="n">
-        <v>320</v>
+        <v>95</v>
       </c>
       <c r="AN31" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AO31" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP31" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR31" t="n">
         <v>10.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AT31" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU31" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW31" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX31" t="n">
         <v>29</v>
@@ -6524,13 +6524,13 @@
         <v>17</v>
       </c>
       <c r="BA31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB31" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="BC31" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BD31" t="n">
         <v>50</v>
@@ -6539,14 +6539,14 @@
         <v>44</v>
       </c>
       <c r="BF31" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BG31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G32" t="n">
         <v>1.62</v>
@@ -6586,10 +6586,10 @@
         <v>5.8</v>
       </c>
       <c r="I32" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K32" t="n">
         <v>5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
         <v>2.3</v>
       </c>
       <c r="G33" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H33" t="n">
         <v>3.2</v>
@@ -6783,10 +6783,10 @@
         <v>3.4</v>
       </c>
       <c r="J33" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K33" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L33" t="n">
         <v>1.36</v>
@@ -6801,13 +6801,13 @@
         <v>1.26</v>
       </c>
       <c r="P33" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R33" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -6816,13 +6816,13 @@
         <v>1.62</v>
       </c>
       <c r="U33" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="V33" t="n">
         <v>1.42</v>
       </c>
       <c r="W33" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X33" t="n">
         <v>19</v>
@@ -6834,7 +6834,7 @@
         <v>26</v>
       </c>
       <c r="AA33" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AB33" t="n">
         <v>13</v>
@@ -6852,10 +6852,10 @@
         <v>17</v>
       </c>
       <c r="AG33" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI33" t="n">
         <v>42</v>
@@ -6870,16 +6870,16 @@
         <v>34</v>
       </c>
       <c r="AM33" t="n">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AN33" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO33" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP33" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ33" t="n">
         <v>13</v>
@@ -6900,7 +6900,7 @@
         <v>12</v>
       </c>
       <c r="AW33" t="n">
-        <v>28</v>
+        <v>16.5</v>
       </c>
       <c r="AX33" t="n">
         <v>14</v>
@@ -6924,7 +6924,7 @@
         <v>26</v>
       </c>
       <c r="BE33" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF33" t="n">
         <v>13.5</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -6968,13 +6968,13 @@
         <v>2.32</v>
       </c>
       <c r="G34" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H34" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I34" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J34" t="n">
         <v>3.7</v>
@@ -6986,40 +6986,40 @@
         <v>1.33</v>
       </c>
       <c r="M34" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O34" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P34" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R34" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="S34" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="T34" t="n">
         <v>1.6</v>
       </c>
       <c r="U34" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V34" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W34" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X34" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y34" t="n">
         <v>18.5</v>
@@ -7028,10 +7028,10 @@
         <v>28</v>
       </c>
       <c r="AA34" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AB34" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC34" t="n">
         <v>10.5</v>
@@ -7040,10 +7040,10 @@
         <v>16.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF34" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG34" t="n">
         <v>13.5</v>
@@ -7064,7 +7064,7 @@
         <v>36</v>
       </c>
       <c r="AM34" t="n">
-        <v>75</v>
+        <v>250</v>
       </c>
       <c r="AN34" t="n">
         <v>15.5</v>
@@ -7082,7 +7082,7 @@
         <v>20</v>
       </c>
       <c r="AS34" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="AT34" t="n">
         <v>11.5</v>
@@ -7094,7 +7094,7 @@
         <v>12</v>
       </c>
       <c r="AW34" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX34" t="n">
         <v>15</v>
@@ -7109,26 +7109,26 @@
         <v>30</v>
       </c>
       <c r="BB34" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC34" t="n">
         <v>19.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE34" t="n">
-        <v>5.1</v>
+        <v>23</v>
       </c>
       <c r="BF34" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -7183,28 +7183,28 @@
         <v>1.04</v>
       </c>
       <c r="N35" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O35" t="n">
         <v>1.2</v>
       </c>
       <c r="P35" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T35" t="n">
         <v>1.59</v>
       </c>
-      <c r="S35" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.58</v>
-      </c>
       <c r="U35" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V35" t="n">
         <v>1.4</v>
@@ -7246,7 +7246,7 @@
         <v>18.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AJ35" t="n">
         <v>75</v>
@@ -7270,16 +7270,16 @@
         <v>12</v>
       </c>
       <c r="AQ35" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR35" t="n">
         <v>13.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="AT35" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AU35" t="n">
         <v>8.4</v>
@@ -7288,7 +7288,7 @@
         <v>13</v>
       </c>
       <c r="AW35" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX35" t="n">
         <v>15</v>
@@ -7306,13 +7306,13 @@
         <v>14.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="BD35" t="n">
         <v>24</v>
       </c>
       <c r="BE35" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="BF35" t="n">
         <v>10</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="G36" t="n">
         <v>2.04</v>
@@ -7365,31 +7365,31 @@
         <v>4.9</v>
       </c>
       <c r="J36" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K36" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L36" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M36" t="n">
         <v>1.09</v>
       </c>
       <c r="N36" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O36" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P36" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R36" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S36" t="n">
         <v>4.2</v>
@@ -7398,7 +7398,7 @@
         <v>1.98</v>
       </c>
       <c r="U36" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V36" t="n">
         <v>1.26</v>
@@ -7437,13 +7437,13 @@
         <v>11</v>
       </c>
       <c r="AH36" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI36" t="n">
         <v>700</v>
       </c>
       <c r="AJ36" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AK36" t="n">
         <v>26</v>
@@ -7467,10 +7467,10 @@
         <v>12</v>
       </c>
       <c r="AR36" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AS36" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT36" t="n">
         <v>6.6</v>
@@ -7482,7 +7482,7 @@
         <v>5.7</v>
       </c>
       <c r="AW36" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX36" t="n">
         <v>9.4</v>
@@ -7494,29 +7494,29 @@
         <v>7.8</v>
       </c>
       <c r="BA36" t="n">
-        <v>7.2</v>
+        <v>55</v>
       </c>
       <c r="BB36" t="n">
         <v>6</v>
       </c>
       <c r="BC36" t="n">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="BD36" t="n">
         <v>6.8</v>
       </c>
       <c r="BE36" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF36" t="n">
         <v>5.6</v>
       </c>
       <c r="BG36" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -7550,19 +7550,19 @@
         <v>5.8</v>
       </c>
       <c r="G37" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="H37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I37" t="n">
         <v>1.91</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1.94</v>
       </c>
       <c r="J37" t="n">
         <v>3.2</v>
       </c>
       <c r="K37" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L37" t="n">
         <v>1.66</v>
@@ -7571,64 +7571,64 @@
         <v>1.15</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O37" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="P37" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="R37" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S37" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="T37" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="U37" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V37" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W37" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X37" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y37" t="n">
         <v>5.7</v>
       </c>
       <c r="Z37" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA37" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB37" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC37" t="n">
         <v>8</v>
       </c>
       <c r="AD37" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE37" t="n">
         <v>65</v>
       </c>
       <c r="AF37" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AG37" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AH37" t="n">
         <v>1000</v>
@@ -7652,10 +7652,10 @@
         <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP37" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ37" t="n">
         <v>5</v>
@@ -7664,10 +7664,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS37" t="n">
-        <v>19.5</v>
+        <v>7.6</v>
       </c>
       <c r="AT37" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU37" t="n">
         <v>7</v>
@@ -7679,38 +7679,38 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AX37" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY37" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ37" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BA37" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB37" t="n">
         <v>10</v>
       </c>
-      <c r="BB37" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BC37" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BD37" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BE37" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="BF37" t="n">
         <v>10.5</v>
       </c>
       <c r="BG37" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         <v>3.35</v>
       </c>
       <c r="G38" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H38" t="n">
         <v>2.94</v>
@@ -7753,28 +7753,28 @@
         <v>3.1</v>
       </c>
       <c r="J38" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="K38" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="L38" t="n">
         <v>1.78</v>
       </c>
       <c r="M38" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="N38" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O38" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="P38" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R38" t="n">
         <v>1.12</v>
@@ -7798,7 +7798,7 @@
         <v>14</v>
       </c>
       <c r="Y38" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z38" t="n">
         <v>1000</v>
@@ -7810,7 +7810,7 @@
         <v>1000</v>
       </c>
       <c r="AC38" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD38" t="n">
         <v>1000</v>
@@ -7855,10 +7855,10 @@
         <v>4.2</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AT38" t="n">
         <v>4.2</v>
@@ -7867,44 +7867,44 @@
         <v>4.2</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.8</v>
+        <v>120</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -7935,19 +7935,19 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G39" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H39" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I39" t="n">
         <v>5.2</v>
       </c>
       <c r="J39" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K39" t="n">
         <v>4.5</v>
@@ -7971,13 +7971,13 @@
         <v>1.72</v>
       </c>
       <c r="R39" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S39" t="n">
         <v>2.84</v>
       </c>
       <c r="T39" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U39" t="n">
         <v>2.2</v>
@@ -7995,7 +7995,7 @@
         <v>38</v>
       </c>
       <c r="Z39" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA39" t="n">
         <v>1000</v>
@@ -8010,10 +8010,10 @@
         <v>1000</v>
       </c>
       <c r="AE39" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF39" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG39" t="n">
         <v>10.5</v>
@@ -8022,7 +8022,7 @@
         <v>22</v>
       </c>
       <c r="AI39" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ39" t="n">
         <v>21</v>
@@ -8031,19 +8031,19 @@
         <v>30</v>
       </c>
       <c r="AL39" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AM39" t="n">
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO39" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ39" t="n">
         <v>18</v>
@@ -8052,10 +8052,10 @@
         <v>32</v>
       </c>
       <c r="AS39" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="AT39" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU39" t="n">
         <v>8.4</v>
@@ -8064,7 +8064,7 @@
         <v>17</v>
       </c>
       <c r="AW39" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AX39" t="n">
         <v>10</v>
@@ -8073,32 +8073,32 @@
         <v>9</v>
       </c>
       <c r="AZ39" t="n">
-        <v>15.5</v>
+        <v>9.4</v>
       </c>
       <c r="BA39" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BB39" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC39" t="n">
         <v>14.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="BF39" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG39" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -8132,19 +8132,19 @@
         <v>1.17</v>
       </c>
       <c r="G40" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="H40" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="I40" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="J40" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="K40" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="L40" t="n">
         <v>1.18</v>
@@ -8153,7 +8153,7 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O40" t="n">
         <v>1.09</v>
@@ -8162,7 +8162,7 @@
         <v>4.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R40" t="n">
         <v>2.24</v>
@@ -8171,43 +8171,43 @@
         <v>1.76</v>
       </c>
       <c r="T40" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="U40" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="V40" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="X40" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="Y40" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Z40" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AA40" t="n">
         <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AC40" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AD40" t="n">
         <v>300</v>
       </c>
       <c r="AE40" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="AF40" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG40" t="n">
         <v>13</v>
@@ -8219,7 +8219,7 @@
         <v>460</v>
       </c>
       <c r="AJ40" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AK40" t="n">
         <v>23</v>
@@ -8228,52 +8228,52 @@
         <v>70</v>
       </c>
       <c r="AM40" t="n">
-        <v>380</v>
+        <v>120</v>
       </c>
       <c r="AN40" t="n">
         <v>2.68</v>
       </c>
       <c r="AO40" t="n">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="AP40" t="n">
         <v>50</v>
       </c>
       <c r="AQ40" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AR40" t="n">
         <v>14</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT40" t="n">
         <v>14</v>
       </c>
       <c r="AU40" t="n">
-        <v>19.5</v>
+        <v>9.6</v>
       </c>
       <c r="AV40" t="n">
-        <v>12.5</v>
+        <v>42</v>
       </c>
       <c r="AW40" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX40" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY40" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ40" t="n">
         <v>14.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BB40" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC40" t="n">
         <v>11.5</v>
@@ -8288,11 +8288,11 @@
         <v>2.46</v>
       </c>
       <c r="BG40" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -8517,52 +8517,52 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G42" t="n">
         <v>2.34</v>
       </c>
       <c r="H42" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I42" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="J42" t="n">
         <v>3.3</v>
       </c>
       <c r="K42" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="L42" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M42" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N42" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O42" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P42" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R42" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S42" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T42" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U42" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V42" t="n">
         <v>1.35</v>
@@ -8571,116 +8571,116 @@
         <v>1.75</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z42" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB42" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF42" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK42" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL42" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM42" t="n">
         <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.08</v>
+        <v>11.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.08</v>
+        <v>11</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.08</v>
+        <v>11.5</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.08</v>
+        <v>4.1</v>
       </c>
       <c r="AT42" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.08</v>
+        <v>7</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.08</v>
+        <v>13</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.08</v>
+        <v>4.2</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.08</v>
+        <v>7</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.08</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.08</v>
+        <v>4.2</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.08</v>
+        <v>4</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.08</v>
+        <v>11.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.08</v>
+        <v>4.2</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.08</v>
+        <v>4.1</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.08</v>
+        <v>4.6</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.08</v>
+        <v>8.4</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -8717,19 +8717,19 @@
         <v>1.58</v>
       </c>
       <c r="H43" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I43" t="n">
         <v>5.9</v>
       </c>
       <c r="J43" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K43" t="n">
         <v>5.2</v>
       </c>
-      <c r="K43" t="n">
-        <v>5.3</v>
-      </c>
       <c r="L43" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M43" t="n">
         <v>1.02</v>
@@ -8741,22 +8741,22 @@
         <v>1.12</v>
       </c>
       <c r="P43" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R43" t="n">
         <v>1.99</v>
       </c>
       <c r="S43" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="T43" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U43" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="V43" t="n">
         <v>1.2</v>
@@ -8774,7 +8774,7 @@
         <v>60</v>
       </c>
       <c r="AA43" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB43" t="n">
         <v>17</v>
@@ -8804,7 +8804,7 @@
         <v>17</v>
       </c>
       <c r="AK43" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL43" t="n">
         <v>22</v>
@@ -8849,13 +8849,13 @@
         <v>10</v>
       </c>
       <c r="AZ43" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA43" t="n">
         <v>42</v>
       </c>
       <c r="BB43" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC43" t="n">
         <v>12.5</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -8905,52 +8905,52 @@
         </is>
       </c>
       <c r="F44" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G44" t="n">
         <v>1.82</v>
       </c>
-      <c r="G44" t="n">
-        <v>1.83</v>
-      </c>
       <c r="H44" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I44" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K44" t="n">
         <v>4.3</v>
       </c>
-      <c r="K44" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L44" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M44" t="n">
         <v>1.04</v>
       </c>
       <c r="N44" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O44" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P44" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R44" t="n">
         <v>1.72</v>
       </c>
       <c r="S44" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="T44" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U44" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V44" t="n">
         <v>1.27</v>
@@ -8968,7 +8968,7 @@
         <v>38</v>
       </c>
       <c r="AA44" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AB44" t="n">
         <v>14.5</v>
@@ -8983,19 +8983,19 @@
         <v>46</v>
       </c>
       <c r="AF44" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG44" t="n">
         <v>10.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI44" t="n">
         <v>42</v>
       </c>
       <c r="AJ44" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK44" t="n">
         <v>16</v>
@@ -9007,7 +9007,7 @@
         <v>55</v>
       </c>
       <c r="AN44" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO44" t="n">
         <v>34</v>
@@ -9022,16 +9022,16 @@
         <v>36</v>
       </c>
       <c r="AS44" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AT44" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU44" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV44" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW44" t="n">
         <v>42</v>
@@ -9043,13 +9043,13 @@
         <v>10</v>
       </c>
       <c r="AZ44" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA44" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB44" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC44" t="n">
         <v>15.5</v>
@@ -9064,11 +9064,11 @@
         <v>6.6</v>
       </c>
       <c r="BG44" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -9099,34 +9099,34 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G45" t="n">
-        <v>110</v>
+        <v>2.94</v>
       </c>
       <c r="H45" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="I45" t="n">
         <v>2.98</v>
       </c>
       <c r="J45" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K45" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L45" t="n">
         <v>1.37</v>
       </c>
       <c r="M45" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N45" t="n">
         <v>3.9</v>
       </c>
       <c r="O45" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P45" t="n">
         <v>2.02</v>
@@ -9141,128 +9141,128 @@
         <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="U45" t="n">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="V45" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W45" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="X45" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y45" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA45" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB45" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD45" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE45" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF45" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG45" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH45" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI45" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK45" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL45" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM45" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN45" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO45" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG45" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -9293,13 +9293,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="G46" t="n">
         <v>1.7</v>
       </c>
       <c r="H46" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I46" t="n">
         <v>6.2</v>
@@ -9308,37 +9308,37 @@
         <v>4</v>
       </c>
       <c r="K46" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L46" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M46" t="n">
         <v>1.06</v>
       </c>
       <c r="N46" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O46" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P46" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="R46" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S46" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="T46" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="U46" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V46" t="n">
         <v>1.2</v>
@@ -9347,49 +9347,49 @@
         <v>2.42</v>
       </c>
       <c r="X46" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z46" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA46" t="n">
         <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD46" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE46" t="n">
         <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG46" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH46" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI46" t="n">
         <v>1000</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK46" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AL46" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM46" t="n">
         <v>1000</v>
@@ -9401,62 +9401,62 @@
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>12.5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ46" t="n">
         <v>16</v>
       </c>
       <c r="AR46" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="AS46" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="AT46" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU46" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV46" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX46" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY46" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ46" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>55</v>
+        <v>6.2</v>
       </c>
       <c r="BB46" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC46" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BD46" t="n">
-        <v>26</v>
+        <v>6.2</v>
       </c>
       <c r="BE46" t="n">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="BF46" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG46" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>
@@ -9487,19 +9487,19 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="G47" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H47" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="I47" t="n">
         <v>1000</v>
       </c>
       <c r="J47" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="K47" t="n">
         <v>1000</v>
@@ -9511,22 +9511,22 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.25</v>
+        <v>2.52</v>
       </c>
       <c r="O47" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="P47" t="n">
-        <v>1.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="R47" t="n">
-        <v>1.18</v>
+        <v>1.51</v>
       </c>
       <c r="S47" t="n">
-        <v>1.19</v>
+        <v>2.08</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -9538,7 +9538,7 @@
         <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-08 02:28:32</t>
+          <t>2026-04-08 04:38:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -760,37 +760,37 @@
         <v>3.4</v>
       </c>
       <c r="G2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.55</v>
-      </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
         <v>4.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="R2" t="n">
         <v>1.4</v>
@@ -802,125 +802,125 @@
         <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X2" t="n">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AB2" t="n">
         <v>14</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AF2" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AG2" t="n">
         <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>16.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AJ2" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="AK2" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AL2" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AM2" t="n">
-        <v>580</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="n">
-        <v>600</v>
+        <v>36</v>
       </c>
       <c r="AO2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AP2" t="n">
         <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AT2" t="n">
         <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AX2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BC2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BD2" t="n">
         <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="BF2" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="BG2" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="I3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K3" t="n">
         <v>3.25</v>
       </c>
-      <c r="J3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.6</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q3" t="n">
         <v>2.14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T3" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U3" t="n">
         <v>2.08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X3" t="n">
         <v>13</v>
@@ -1014,107 +1014,107 @@
         <v>24</v>
       </c>
       <c r="AA3" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
         <v>14.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
         <v>18.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH3" t="n">
         <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AK3" t="n">
         <v>500</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
         <v>9.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU3" t="n">
         <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW3" t="n">
         <v>30</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC3" t="n">
         <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
         <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="G4" t="n">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="H4" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N4" t="n">
         <v>2.92</v>
@@ -1184,131 +1184,131 @@
         <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="X4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y4" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y4" t="n">
-        <v>11.5</v>
-      </c>
       <c r="Z4" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>260</v>
+        <v>65</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
         <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="AK4" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AL4" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>580</v>
+        <v>150</v>
       </c>
       <c r="AN4" t="n">
-        <v>600</v>
+        <v>36</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AS4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB4" t="n">
         <v>34</v>
       </c>
-      <c r="AT4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BC4" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="BD4" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BE4" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF4" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="BG4" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -1339,64 +1339,64 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
         <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="O5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P5" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="U5" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="V5" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="W5" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z5" t="n">
         <v>19</v>
@@ -1405,19 +1405,19 @@
         <v>120</v>
       </c>
       <c r="AB5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
         <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="AF5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
         <v>13.5</v>
@@ -1426,10 +1426,10 @@
         <v>15.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ5" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="AK5" t="n">
         <v>32</v>
@@ -1438,71 +1438,71 @@
         <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN5" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AO5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AP5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AT5" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV5" t="n">
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY5" t="n">
         <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BC5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF5" t="n">
         <v>17.5</v>
       </c>
-      <c r="BD5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF5" t="n">
+      <c r="BG5" t="n">
         <v>18.5</v>
       </c>
-      <c r="BG5" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="G6" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I6" t="n">
         <v>1.5</v>
       </c>
-      <c r="I6" t="n">
-        <v>1.59</v>
-      </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
         <v>3.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="U6" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="V6" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="n">
         <v>7.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AB6" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD6" t="n">
         <v>11</v>
       </c>
       <c r="AE6" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AG6" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AH6" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>510</v>
       </c>
       <c r="AO6" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AP6" t="n">
         <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.8</v>
+        <v>23</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="AZ6" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.48</v>
@@ -1760,7 +1760,7 @@
         <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R7" t="n">
         <v>1.27</v>
@@ -1775,28 +1775,28 @@
         <v>1.98</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y7" t="n">
         <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD7" t="n">
         <v>14.5</v>
@@ -1805,10 +1805,10 @@
         <v>42</v>
       </c>
       <c r="AF7" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
         <v>19</v>
@@ -1817,19 +1817,19 @@
         <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL7" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO7" t="n">
         <v>42</v>
@@ -1838,59 +1838,59 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS7" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="AX7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BA7" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="BB7" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="BC7" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BD7" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="BE7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BF7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G8" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="K8" t="n">
         <v>4.2</v>
@@ -1942,10 +1942,10 @@
         <v>1.41</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
         <v>1.3</v>
@@ -1954,7 +1954,7 @@
         <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R8" t="n">
         <v>1.35</v>
@@ -1963,128 +1963,128 @@
         <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="U8" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="V8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W8" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="X8" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL8" t="n">
         <v>36</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>38</v>
       </c>
       <c r="AM8" t="n">
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AO8" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AP8" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW8" t="n">
         <v>25</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA8" t="n">
         <v>27</v>
       </c>
       <c r="BB8" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BD8" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BE8" t="n">
         <v>15.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G9" t="n">
         <v>1.41</v>
       </c>
       <c r="H9" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="I9" t="n">
         <v>18</v>
       </c>
       <c r="J9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L9" t="n">
         <v>1.43</v>
@@ -2139,25 +2139,25 @@
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
         <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T9" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
         <v>1.51</v>
@@ -2217,68 +2217,68 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AV9" t="n">
         <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AY9" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BB9" t="n">
         <v>5.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BF9" t="n">
         <v>6.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -2315,10 +2315,10 @@
         <v>2.28</v>
       </c>
       <c r="H10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J10" t="n">
         <v>3.7</v>
@@ -2342,7 +2342,7 @@
         <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R10" t="n">
         <v>1.47</v>
@@ -2351,7 +2351,7 @@
         <v>2.96</v>
       </c>
       <c r="T10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U10" t="n">
         <v>2.32</v>
@@ -2360,7 +2360,7 @@
         <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X10" t="n">
         <v>20</v>
@@ -2414,10 +2414,10 @@
         <v>15.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AQ10" t="n">
         <v>13.5</v>
@@ -2426,7 +2426,7 @@
         <v>21</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -2459,10 +2459,10 @@
         <v>19</v>
       </c>
       <c r="BD10" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="BE10" t="n">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="BF10" t="n">
         <v>12.5</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K11" t="n">
         <v>3.15</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.25</v>
       </c>
       <c r="L11" t="n">
         <v>1.61</v>
@@ -2527,10 +2527,10 @@
         <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O11" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P11" t="n">
         <v>1.54</v>
@@ -2542,103 +2542,103 @@
         <v>1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="W11" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="X11" t="n">
         <v>8.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE11" t="n">
         <v>44</v>
       </c>
-      <c r="AB11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>40</v>
-      </c>
       <c r="AF11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN11" t="n">
         <v>60</v>
       </c>
-      <c r="AK11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>70</v>
-      </c>
       <c r="AO11" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AP11" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS11" t="n">
         <v>38</v>
       </c>
       <c r="AT11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU11" t="n">
         <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AX11" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AY11" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>21</v>
@@ -2647,26 +2647,26 @@
         <v>34</v>
       </c>
       <c r="BB11" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BC11" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BD11" t="n">
         <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BF11" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="BG11" t="n">
         <v>34</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="G12" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H12" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I12" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="J12" t="n">
         <v>3.6</v>
@@ -2718,7 +2718,7 @@
         <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
         <v>4.3</v>
@@ -2733,7 +2733,7 @@
         <v>1.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -2742,40 +2742,40 @@
         <v>1.64</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W12" t="n">
         <v>1.56</v>
       </c>
       <c r="X12" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
         <v>20</v>
       </c>
       <c r="AA12" t="n">
-        <v>42</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="n">
         <v>13.5</v>
@@ -2790,31 +2790,31 @@
         <v>42</v>
       </c>
       <c r="AK12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM12" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
         <v>22</v>
       </c>
       <c r="AO12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ12" t="n">
         <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>28</v>
+        <v>19.5</v>
       </c>
       <c r="AT12" t="n">
         <v>11</v>
@@ -2823,13 +2823,13 @@
         <v>7.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY12" t="n">
         <v>10.5</v>
@@ -2838,29 +2838,29 @@
         <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="BE12" t="n">
-        <v>9.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>16.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="I13" t="n">
         <v>1.33</v>
@@ -2906,22 +2906,22 @@
         <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
         <v>1.96</v>
@@ -2930,10 +2930,10 @@
         <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="U13" t="n">
         <v>1.56</v>
@@ -2984,19 +2984,19 @@
         <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AL13" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AN13" t="n">
-        <v>680</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AP13" t="n">
         <v>14</v>
@@ -3005,10 +3005,10 @@
         <v>6</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT13" t="n">
         <v>30</v>
@@ -3017,44 +3017,44 @@
         <v>12</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW13" t="n">
         <v>15</v>
       </c>
       <c r="AX13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ13" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="BA13" t="n">
         <v>27</v>
       </c>
       <c r="BB13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC13" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BD13" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BE13" t="n">
         <v>30</v>
       </c>
       <c r="BF13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BG13" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="G14" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="H14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I14" t="n">
         <v>5.7</v>
       </c>
-      <c r="I14" t="n">
-        <v>6</v>
-      </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.59</v>
@@ -3109,16 +3109,16 @@
         <v>1.12</v>
       </c>
       <c r="N14" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
         <v>1.53</v>
       </c>
       <c r="P14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="R14" t="n">
         <v>1.2</v>
@@ -3127,25 +3127,25 @@
         <v>5.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U14" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="X14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z14" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
@@ -3157,37 +3157,37 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AF14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AG14" t="n">
         <v>11.5</v>
       </c>
       <c r="AH14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL14" t="n">
         <v>60</v>
       </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>290</v>
-      </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
@@ -3196,25 +3196,25 @@
         <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AS14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX14" t="n">
         <v>8.199999999999999</v>
@@ -3223,32 +3223,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB14" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BC14" t="n">
         <v>21</v>
       </c>
       <c r="BD14" t="n">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="BE14" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BF14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG14" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="G15" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="H15" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L15" t="n">
         <v>1.46</v>
@@ -3303,76 +3303,76 @@
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
         <v>1.38</v>
       </c>
       <c r="P15" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U15" t="n">
         <v>1.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="X15" t="n">
         <v>12.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="Z15" t="n">
         <v>85</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AE15" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="AF15" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG15" t="n">
         <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AI15" t="n">
         <v>370</v>
       </c>
       <c r="AJ15" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AK15" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL15" t="n">
         <v>180</v>
@@ -3381,31 +3381,31 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AO15" t="n">
-        <v>110</v>
+        <v>270</v>
       </c>
       <c r="AP15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.5</v>
+        <v>27</v>
       </c>
       <c r="AS15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AW15" t="n">
         <v>20</v>
@@ -3417,32 +3417,32 @@
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA15" t="n">
         <v>28</v>
       </c>
       <c r="BB15" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="BC15" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF15" t="n">
         <v>13.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>17.5</v>
       </c>
       <c r="BG15" t="n">
         <v>10.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -3473,88 +3473,88 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="G16" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="I16" t="n">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="J16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M16" t="n">
         <v>1.12</v>
       </c>
       <c r="N16" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="O16" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U16" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="V16" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="W16" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="X16" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z16" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB16" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF16" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AG16" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AH16" t="n">
         <v>23</v>
@@ -3563,80 +3563,80 @@
         <v>110</v>
       </c>
       <c r="AJ16" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AK16" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AL16" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AR16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY16" t="n">
         <v>14</v>
       </c>
-      <c r="AS16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AZ16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>50</v>
+      </c>
+      <c r="BG16" t="n">
         <v>18.5</v>
       </c>
-      <c r="BA16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>36</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="G17" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="H17" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I17" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L17" t="n">
         <v>1.39</v>
@@ -3694,37 +3694,37 @@
         <v>4.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P17" t="n">
         <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U17" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V17" t="n">
         <v>1.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X17" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y17" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="Z17" t="n">
         <v>1000</v>
@@ -3778,59 +3778,59 @@
         <v>7.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.6</v>
+        <v>15.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AV17" t="n">
         <v>6.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AY17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AZ17" t="n">
         <v>7.4</v>
       </c>
       <c r="BA17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB17" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BB17" t="n">
-        <v>10</v>
-      </c>
       <c r="BC17" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BD17" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G18" t="n">
         <v>1.55</v>
@@ -3987,10 +3987,10 @@
         <v>10</v>
       </c>
       <c r="AV18" t="n">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="AW18" t="n">
-        <v>8.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="AX18" t="n">
         <v>5.5</v>
@@ -3999,7 +3999,7 @@
         <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6.6</v>
+        <v>16.5</v>
       </c>
       <c r="BA18" t="n">
         <v>8.6</v>
@@ -4011,7 +4011,7 @@
         <v>10.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="BE18" t="n">
         <v>8.800000000000001</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -4055,124 +4055,124 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="G19" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="H19" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="I19" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R19" t="n">
         <v>1.46</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="U19" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V19" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y19" t="n">
         <v>9</v>
       </c>
       <c r="Z19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AB19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AC19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF19" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AG19" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AP19" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS19" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AT19" t="n">
         <v>20</v>
@@ -4184,41 +4184,41 @@
         <v>9</v>
       </c>
       <c r="AW19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC19" t="n">
         <v>14</v>
       </c>
-      <c r="AX19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA19" t="n">
+      <c r="BD19" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE19" t="n">
         <v>14.5</v>
       </c>
-      <c r="BB19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>60</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BF19" t="n">
-        <v>10.5</v>
+        <v>48</v>
       </c>
       <c r="BG19" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -4249,37 +4249,37 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G20" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H20" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
         <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
         <v>1.42</v>
       </c>
       <c r="P20" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q20" t="n">
         <v>2.3</v>
@@ -4291,19 +4291,19 @@
         <v>4.4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U20" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V20" t="n">
         <v>1.34</v>
       </c>
       <c r="W20" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="X20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y20" t="n">
         <v>12</v>
@@ -4315,28 +4315,28 @@
         <v>80</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC20" t="n">
         <v>7.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE20" t="n">
         <v>55</v>
       </c>
       <c r="AF20" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH20" t="n">
         <v>19.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>370</v>
+        <v>70</v>
       </c>
       <c r="AJ20" t="n">
         <v>32</v>
@@ -4351,7 +4351,7 @@
         <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AO20" t="n">
         <v>65</v>
@@ -4366,22 +4366,22 @@
         <v>22</v>
       </c>
       <c r="AS20" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="AT20" t="n">
         <v>7.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV20" t="n">
         <v>14</v>
       </c>
       <c r="AW20" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AX20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY20" t="n">
         <v>10</v>
@@ -4390,29 +4390,29 @@
         <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="BB20" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="BC20" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="BD20" t="n">
         <v>40</v>
       </c>
       <c r="BE20" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BF20" t="n">
         <v>21</v>
       </c>
       <c r="BG20" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -4443,94 +4443,94 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="I21" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="J21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M21" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="P21" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="V21" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="W21" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z21" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA21" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AC21" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD21" t="n">
         <v>10.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AI21" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AJ21" t="n">
         <v>1000</v>
@@ -4542,7 +4542,7 @@
         <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
         <v>1000</v>
@@ -4551,62 +4551,62 @@
         <v>7.2</v>
       </c>
       <c r="AP21" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR21" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AU21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="AY21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>21</v>
       </c>
-      <c r="AZ21" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BA21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BB21" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC21" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD21" t="n">
-        <v>55</v>
+        <v>8.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>28</v>
+        <v>8.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="BG21" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -4643,16 +4643,16 @@
         <v>1.46</v>
       </c>
       <c r="H22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I22" t="n">
         <v>11.5</v>
       </c>
       <c r="J22" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K22" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L22" t="n">
         <v>1.45</v>
@@ -4661,25 +4661,25 @@
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.34</v>
       </c>
-      <c r="P22" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.35</v>
-      </c>
       <c r="S22" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="T22" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U22" t="n">
         <v>1.7</v>
@@ -4694,7 +4694,7 @@
         <v>16</v>
       </c>
       <c r="Y22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -4703,19 +4703,19 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC22" t="n">
         <v>11</v>
       </c>
       <c r="AD22" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
@@ -4727,19 +4727,19 @@
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AK22" t="n">
         <v>17</v>
       </c>
       <c r="AL22" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
@@ -4751,16 +4751,16 @@
         <v>22</v>
       </c>
       <c r="AR22" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="AS22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT22" t="n">
         <v>6</v>
       </c>
       <c r="AU22" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
@@ -4775,32 +4775,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="BA22" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB22" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BC22" t="n">
         <v>14</v>
       </c>
       <c r="BD22" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BE22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="G23" t="n">
         <v>1.23</v>
       </c>
       <c r="H23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="I23" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="L23" t="n">
         <v>1.22</v>
@@ -4855,28 +4855,28 @@
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P23" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="R23" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S23" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="T23" t="n">
         <v>1.98</v>
       </c>
       <c r="U23" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="V23" t="n">
         <v>1.06</v>
@@ -4897,10 +4897,10 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
         <v>1000</v>
@@ -4909,7 +4909,7 @@
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG23" t="n">
         <v>1000</v>
@@ -4921,10 +4921,10 @@
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL23" t="n">
         <v>1000</v>
@@ -4939,43 +4939,43 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR23" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="AS23" t="n">
         <v>4.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV23" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB23" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>6.2</v>
       </c>
       <c r="BC23" t="n">
         <v>11.5</v>
@@ -4984,17 +4984,17 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE23" t="n">
-        <v>10.5</v>
+        <v>29</v>
       </c>
       <c r="BF23" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="BG23" t="n">
         <v>15</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>1.47</v>
       </c>
       <c r="G24" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H24" t="n">
         <v>6</v>
@@ -5037,7 +5037,7 @@
         <v>7.2</v>
       </c>
       <c r="J24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K24" t="n">
         <v>5.7</v>
@@ -5052,31 +5052,31 @@
         <v>6.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P24" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R24" t="n">
         <v>1.75</v>
       </c>
       <c r="S24" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U24" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V24" t="n">
         <v>1.16</v>
       </c>
       <c r="W24" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="X24" t="n">
         <v>32</v>
@@ -5085,31 +5085,31 @@
         <v>34</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD24" t="n">
         <v>26</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG24" t="n">
         <v>11</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI24" t="n">
         <v>65</v>
@@ -5121,7 +5121,7 @@
         <v>15.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
@@ -5133,16 +5133,16 @@
         <v>65</v>
       </c>
       <c r="AP24" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="AQ24" t="n">
         <v>26</v>
       </c>
       <c r="AR24" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT24" t="n">
         <v>10.5</v>
@@ -5154,10 +5154,10 @@
         <v>21</v>
       </c>
       <c r="AW24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX24" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY24" t="n">
         <v>8.800000000000001</v>
@@ -5166,7 +5166,7 @@
         <v>17</v>
       </c>
       <c r="BA24" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="BB24" t="n">
         <v>12.5</v>
@@ -5175,20 +5175,20 @@
         <v>12</v>
       </c>
       <c r="BD24" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG24" t="n">
         <v>30</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -5261,10 +5261,10 @@
         <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U25" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>2.42</v>
@@ -5276,13 +5276,13 @@
         <v>970</v>
       </c>
       <c r="Y25" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z25" t="n">
         <v>11</v>
       </c>
       <c r="AA25" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AB25" t="n">
         <v>50</v>
@@ -5300,7 +5300,7 @@
         <v>220</v>
       </c>
       <c r="AG25" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AH25" t="n">
         <v>48</v>
@@ -5351,38 +5351,38 @@
         <v>14.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AY25" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ25" t="n">
         <v>14</v>
       </c>
       <c r="BA25" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="BB25" t="n">
         <v>9.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD25" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG25" t="n">
         <v>7.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -5443,7 +5443,7 @@
         <v>1.32</v>
       </c>
       <c r="P26" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q26" t="n">
         <v>1.98</v>
@@ -5452,10 +5452,10 @@
         <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T26" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U26" t="n">
         <v>2.06</v>
@@ -5476,7 +5476,7 @@
         <v>29</v>
       </c>
       <c r="AA26" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AB26" t="n">
         <v>11</v>
@@ -5488,7 +5488,7 @@
         <v>16.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="AF26" t="n">
         <v>16</v>
@@ -5539,10 +5539,10 @@
         <v>7</v>
       </c>
       <c r="AV26" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW26" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AX26" t="n">
         <v>11.5</v>
@@ -5557,7 +5557,7 @@
         <v>6</v>
       </c>
       <c r="BB26" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="BC26" t="n">
         <v>19.5</v>
@@ -5566,17 +5566,17 @@
         <v>17.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF26" t="n">
         <v>14</v>
       </c>
       <c r="BG26" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="G27" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="H27" t="n">
         <v>3.05</v>
@@ -5619,22 +5619,22 @@
         <v>3.1</v>
       </c>
       <c r="J27" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K27" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L27" t="n">
         <v>1.47</v>
       </c>
       <c r="M27" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N27" t="n">
         <v>3.5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P27" t="n">
         <v>1.83</v>
@@ -5658,7 +5658,7 @@
         <v>1.47</v>
       </c>
       <c r="W27" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X27" t="n">
         <v>12</v>
@@ -5667,7 +5667,7 @@
         <v>11</v>
       </c>
       <c r="Z27" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA27" t="n">
         <v>50</v>
@@ -5679,13 +5679,13 @@
         <v>7.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE27" t="n">
         <v>36</v>
       </c>
       <c r="AF27" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG27" t="n">
         <v>12</v>
@@ -5700,10 +5700,10 @@
         <v>38</v>
       </c>
       <c r="AK27" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL27" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -5715,13 +5715,13 @@
         <v>36</v>
       </c>
       <c r="AP27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS27" t="n">
         <v>44</v>
@@ -5733,7 +5733,7 @@
         <v>7</v>
       </c>
       <c r="AV27" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW27" t="n">
         <v>32</v>
@@ -5754,13 +5754,13 @@
         <v>34</v>
       </c>
       <c r="BC27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD27" t="n">
         <v>42</v>
       </c>
       <c r="BE27" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BF27" t="n">
         <v>26</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -5801,16 +5801,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G28" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="H28" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="I28" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="J28" t="n">
         <v>3.4</v>
@@ -5825,7 +5825,7 @@
         <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O28" t="n">
         <v>1.35</v>
@@ -5849,25 +5849,25 @@
         <v>2.02</v>
       </c>
       <c r="V28" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W28" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="X28" t="n">
         <v>13.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA28" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC28" t="n">
         <v>7.8</v>
@@ -5876,7 +5876,7 @@
         <v>16</v>
       </c>
       <c r="AE28" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AF28" t="n">
         <v>14</v>
@@ -5891,7 +5891,7 @@
         <v>60</v>
       </c>
       <c r="AJ28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK28" t="n">
         <v>25</v>
@@ -5903,10 +5903,10 @@
         <v>110</v>
       </c>
       <c r="AN28" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP28" t="n">
         <v>11.5</v>
@@ -5915,10 +5915,10 @@
         <v>12</v>
       </c>
       <c r="AR28" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AS28" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT28" t="n">
         <v>8.6</v>
@@ -5927,10 +5927,10 @@
         <v>7.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="AX28" t="n">
         <v>12</v>
@@ -5942,29 +5942,29 @@
         <v>16</v>
       </c>
       <c r="BA28" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="BB28" t="n">
         <v>25</v>
       </c>
       <c r="BC28" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BD28" t="n">
         <v>18</v>
       </c>
       <c r="BE28" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BF28" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG28" t="n">
         <v>38</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -5995,67 +5995,67 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="G29" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="H29" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="I29" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J29" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="K29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P29" t="n">
         <v>1.83</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R29" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T29" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="V29" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W29" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="X29" t="n">
-        <v>90</v>
+        <v>13.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
@@ -6073,13 +6073,13 @@
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AG29" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH29" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AI29" t="n">
         <v>1000</v>
@@ -6088,7 +6088,7 @@
         <v>26</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="n">
         <v>500</v>
@@ -6097,28 +6097,28 @@
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS29" t="n">
         <v>12</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>11.5</v>
       </c>
       <c r="AT29" t="n">
         <v>6.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV29" t="n">
         <v>14.5</v>
@@ -6127,38 +6127,38 @@
         <v>11</v>
       </c>
       <c r="AX29" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY29" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ29" t="n">
         <v>13.5</v>
       </c>
       <c r="BA29" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC29" t="n">
         <v>11</v>
       </c>
-      <c r="BB29" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>15</v>
-      </c>
       <c r="BD29" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BE29" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="BF29" t="n">
         <v>7.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6225,7 @@
         <v>1.6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S30" t="n">
         <v>2.52</v>
@@ -6243,10 +6243,10 @@
         <v>1.81</v>
       </c>
       <c r="X30" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="Y30" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z30" t="n">
         <v>75</v>
@@ -6261,13 +6261,13 @@
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE30" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AF30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG30" t="n">
         <v>11.5</v>
@@ -6279,22 +6279,22 @@
         <v>36</v>
       </c>
       <c r="AJ30" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AK30" t="n">
         <v>21</v>
       </c>
       <c r="AL30" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AM30" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AN30" t="n">
         <v>11</v>
       </c>
       <c r="AO30" t="n">
-        <v>210</v>
+        <v>42</v>
       </c>
       <c r="AP30" t="n">
         <v>12</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -6386,25 +6386,25 @@
         <v>4.5</v>
       </c>
       <c r="G31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H31" t="n">
         <v>1.88</v>
       </c>
       <c r="I31" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="J31" t="n">
         <v>3.95</v>
       </c>
       <c r="K31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L31" t="n">
         <v>1.38</v>
       </c>
       <c r="M31" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N31" t="n">
         <v>4.2</v>
@@ -6428,10 +6428,10 @@
         <v>1.77</v>
       </c>
       <c r="U31" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V31" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="W31" t="n">
         <v>1.27</v>
@@ -6449,19 +6449,19 @@
         <v>21</v>
       </c>
       <c r="AB31" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC31" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AE31" t="n">
         <v>18.5</v>
       </c>
       <c r="AF31" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG31" t="n">
         <v>17.5</v>
@@ -6470,28 +6470,28 @@
         <v>18.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ31" t="n">
         <v>100</v>
       </c>
       <c r="AK31" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AL31" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AM31" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AN31" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AO31" t="n">
         <v>12</v>
       </c>
       <c r="AP31" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ31" t="n">
         <v>8.6</v>
@@ -6500,53 +6500,53 @@
         <v>10.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AT31" t="n">
         <v>15.5</v>
       </c>
       <c r="AU31" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV31" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW31" t="n">
         <v>16.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AY31" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AZ31" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA31" t="n">
         <v>29</v>
       </c>
       <c r="BB31" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BC31" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BD31" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="BE31" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="BF31" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="BG31" t="n">
         <v>11</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G32" t="n">
         <v>1.6</v>
       </c>
-      <c r="G32" t="n">
-        <v>1.62</v>
-      </c>
       <c r="H32" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I32" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J32" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K32" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -6795,34 +6795,34 @@
         <v>1.05</v>
       </c>
       <c r="N33" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O33" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P33" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q33" t="n">
         <v>1.79</v>
       </c>
       <c r="R33" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T33" t="n">
         <v>1.62</v>
       </c>
       <c r="U33" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V33" t="n">
         <v>1.42</v>
       </c>
       <c r="W33" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X33" t="n">
         <v>19</v>
@@ -6834,7 +6834,7 @@
         <v>26</v>
       </c>
       <c r="AA33" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AB33" t="n">
         <v>13</v>
@@ -6870,7 +6870,7 @@
         <v>34</v>
       </c>
       <c r="AM33" t="n">
-        <v>320</v>
+        <v>70</v>
       </c>
       <c r="AN33" t="n">
         <v>16</v>
@@ -6924,7 +6924,7 @@
         <v>26</v>
       </c>
       <c r="BE33" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF33" t="n">
         <v>13.5</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
         <v>2.42</v>
       </c>
       <c r="H34" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I34" t="n">
         <v>3.25</v>
@@ -7028,7 +7028,7 @@
         <v>28</v>
       </c>
       <c r="AA34" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AB34" t="n">
         <v>16</v>
@@ -7052,7 +7052,7 @@
         <v>18</v>
       </c>
       <c r="AI34" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ34" t="n">
         <v>32</v>
@@ -7118,7 +7118,7 @@
         <v>15</v>
       </c>
       <c r="BE34" t="n">
-        <v>23</v>
+        <v>5.9</v>
       </c>
       <c r="BF34" t="n">
         <v>11.5</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G35" t="n">
         <v>2.24</v>
@@ -7171,7 +7171,7 @@
         <v>3.45</v>
       </c>
       <c r="J35" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K35" t="n">
         <v>4.2</v>
@@ -7198,7 +7198,7 @@
         <v>1.6</v>
       </c>
       <c r="S35" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T35" t="n">
         <v>1.59</v>
@@ -7207,13 +7207,13 @@
         <v>2.56</v>
       </c>
       <c r="V35" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W35" t="n">
         <v>1.8</v>
       </c>
       <c r="X35" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Y35" t="n">
         <v>22</v>
@@ -7222,7 +7222,7 @@
         <v>30</v>
       </c>
       <c r="AA35" t="n">
-        <v>440</v>
+        <v>160</v>
       </c>
       <c r="AB35" t="n">
         <v>14.5</v>
@@ -7243,16 +7243,16 @@
         <v>11.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI35" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ35" t="n">
         <v>75</v>
       </c>
       <c r="AK35" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AL35" t="n">
         <v>80</v>
@@ -7264,7 +7264,7 @@
         <v>11.5</v>
       </c>
       <c r="AO35" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AP35" t="n">
         <v>12</v>
@@ -7276,7 +7276,7 @@
         <v>13.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AT35" t="n">
         <v>12.5</v>
@@ -7312,7 +7312,7 @@
         <v>24</v>
       </c>
       <c r="BE35" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BF35" t="n">
         <v>10</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="G36" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="H36" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I36" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J36" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K36" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L36" t="n">
         <v>1.48</v>
@@ -7377,22 +7377,22 @@
         <v>1.09</v>
       </c>
       <c r="N36" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O36" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P36" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R36" t="n">
         <v>1.27</v>
       </c>
       <c r="S36" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T36" t="n">
         <v>1.98</v>
@@ -7401,10 +7401,10 @@
         <v>1.9</v>
       </c>
       <c r="V36" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W36" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="X36" t="n">
         <v>25</v>
@@ -7419,10 +7419,10 @@
         <v>700</v>
       </c>
       <c r="AB36" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC36" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD36" t="n">
         <v>970</v>
@@ -7431,7 +7431,7 @@
         <v>700</v>
       </c>
       <c r="AF36" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AG36" t="n">
         <v>11</v>
@@ -7443,7 +7443,7 @@
         <v>700</v>
       </c>
       <c r="AJ36" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AK36" t="n">
         <v>26</v>
@@ -7455,68 +7455,68 @@
         <v>580</v>
       </c>
       <c r="AN36" t="n">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="AO36" t="n">
         <v>700</v>
       </c>
       <c r="AP36" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AQ36" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="AR36" t="n">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="AS36" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT36" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU36" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV36" t="n">
-        <v>5.7</v>
+        <v>15</v>
       </c>
       <c r="AW36" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="AX36" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY36" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ36" t="n">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="BA36" t="n">
         <v>55</v>
       </c>
       <c r="BB36" t="n">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC36" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="BD36" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="BE36" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BF36" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BG36" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -7547,73 +7547,73 @@
         </is>
       </c>
       <c r="F37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G37" t="n">
         <v>5.8</v>
       </c>
-      <c r="G37" t="n">
-        <v>6.4</v>
-      </c>
       <c r="H37" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="I37" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="J37" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K37" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L37" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="M37" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R37" t="n">
         <v>1.15</v>
       </c>
-      <c r="N37" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.16</v>
-      </c>
       <c r="S37" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="T37" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="U37" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="V37" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="W37" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X37" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="Y37" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z37" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AA37" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AB37" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC37" t="n">
         <v>8</v>
@@ -7622,40 +7622,40 @@
         <v>12</v>
       </c>
       <c r="AE37" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AF37" t="n">
         <v>500</v>
       </c>
       <c r="AG37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO37" t="n">
         <v>30</v>
       </c>
-      <c r="AH37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>600</v>
-      </c>
       <c r="AP37" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AQ37" t="n">
         <v>5</v>
@@ -7664,10 +7664,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS37" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT37" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU37" t="n">
         <v>7</v>
@@ -7676,41 +7676,41 @@
         <v>10</v>
       </c>
       <c r="AW37" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AX37" t="n">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="AY37" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BA37" t="n">
-        <v>9.6</v>
+        <v>32</v>
       </c>
       <c r="BB37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE37" t="n">
         <v>100</v>
       </c>
       <c r="BF37" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG37" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -7741,37 +7741,37 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G38" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="H38" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="I38" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J38" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="K38" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="L38" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="M38" t="n">
         <v>1.22</v>
       </c>
       <c r="N38" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="O38" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="P38" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Q38" t="n">
         <v>3.75</v>
@@ -7792,7 +7792,7 @@
         <v>1.48</v>
       </c>
       <c r="W38" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X38" t="n">
         <v>14</v>
@@ -7855,10 +7855,10 @@
         <v>4.2</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AT38" t="n">
         <v>4.2</v>
@@ -7867,31 +7867,31 @@
         <v>4.2</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AX38" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AY38" t="n">
         <v>1.85</v>
       </c>
-      <c r="AY38" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AZ38" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BA38" t="n">
         <v>1.87</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BE38" t="n">
         <v>120</v>
@@ -7900,11 +7900,11 @@
         <v>1.87</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
         <v>1.72</v>
       </c>
       <c r="G39" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H39" t="n">
         <v>4.9</v>
@@ -7953,7 +7953,7 @@
         <v>4.5</v>
       </c>
       <c r="L39" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M39" t="n">
         <v>1.05</v>
@@ -7965,16 +7965,16 @@
         <v>1.24</v>
       </c>
       <c r="P39" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R39" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S39" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T39" t="n">
         <v>1.74</v>
@@ -7986,7 +7986,7 @@
         <v>1.23</v>
       </c>
       <c r="W39" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X39" t="n">
         <v>40</v>
@@ -8010,7 +8010,7 @@
         <v>1000</v>
       </c>
       <c r="AE39" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AF39" t="n">
         <v>12.5</v>
@@ -8040,16 +8040,16 @@
         <v>9.4</v>
       </c>
       <c r="AO39" t="n">
-        <v>700</v>
+        <v>70</v>
       </c>
       <c r="AP39" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ39" t="n">
         <v>18</v>
       </c>
       <c r="AR39" t="n">
-        <v>32</v>
+        <v>10.5</v>
       </c>
       <c r="AS39" t="n">
         <v>32</v>
@@ -8064,7 +8064,7 @@
         <v>17</v>
       </c>
       <c r="AW39" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX39" t="n">
         <v>10</v>
@@ -8076,7 +8076,7 @@
         <v>9.4</v>
       </c>
       <c r="BA39" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB39" t="n">
         <v>16</v>
@@ -8085,20 +8085,20 @@
         <v>14.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BE39" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF39" t="n">
         <v>8</v>
       </c>
       <c r="BG39" t="n">
-        <v>9.4</v>
+        <v>26</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="G40" t="n">
         <v>1.18</v>
       </c>
       <c r="H40" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="I40" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="J40" t="n">
         <v>10.5</v>
       </c>
       <c r="K40" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="L40" t="n">
         <v>1.18</v>
@@ -8171,10 +8171,10 @@
         <v>1.76</v>
       </c>
       <c r="T40" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="U40" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V40" t="n">
         <v>1.06</v>
@@ -8186,10 +8186,10 @@
         <v>1000</v>
       </c>
       <c r="Y40" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Z40" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AA40" t="n">
         <v>1000</v>
@@ -8198,13 +8198,13 @@
         <v>38</v>
       </c>
       <c r="AC40" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AD40" t="n">
         <v>300</v>
       </c>
       <c r="AE40" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AF40" t="n">
         <v>11.5</v>
@@ -8213,13 +8213,13 @@
         <v>13</v>
       </c>
       <c r="AH40" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AI40" t="n">
         <v>460</v>
       </c>
       <c r="AJ40" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK40" t="n">
         <v>23</v>
@@ -8228,49 +8228,49 @@
         <v>70</v>
       </c>
       <c r="AM40" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AN40" t="n">
         <v>2.68</v>
       </c>
       <c r="AO40" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AP40" t="n">
         <v>50</v>
       </c>
       <c r="AQ40" t="n">
-        <v>30</v>
+        <v>11.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS40" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AT40" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX40" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>42</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AY40" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ40" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB40" t="n">
         <v>9.199999999999999</v>
@@ -8279,20 +8279,20 @@
         <v>11.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="BE40" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="BF40" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BG40" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -8520,22 +8520,22 @@
         <v>2.18</v>
       </c>
       <c r="G42" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H42" t="n">
         <v>3.45</v>
       </c>
       <c r="I42" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
         <v>3.3</v>
       </c>
       <c r="K42" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L42" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M42" t="n">
         <v>1.08</v>
@@ -8544,31 +8544,31 @@
         <v>3.5</v>
       </c>
       <c r="O42" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P42" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R42" t="n">
         <v>1.32</v>
       </c>
       <c r="S42" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T42" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U42" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V42" t="n">
         <v>1.35</v>
       </c>
       <c r="W42" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X42" t="n">
         <v>16.5</v>
@@ -8580,7 +8580,7 @@
         <v>32</v>
       </c>
       <c r="AA42" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB42" t="n">
         <v>11.5</v>
@@ -8607,7 +8607,7 @@
         <v>250</v>
       </c>
       <c r="AJ42" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AK42" t="n">
         <v>32</v>
@@ -8622,55 +8622,55 @@
         <v>24</v>
       </c>
       <c r="AO42" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ42" t="n">
         <v>11</v>
       </c>
       <c r="AR42" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AT42" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU42" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV42" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX42" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY42" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ42" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB42" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="BC42" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF42" t="n">
         <v>4.6</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -8717,10 +8717,10 @@
         <v>1.58</v>
       </c>
       <c r="H43" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I43" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J43" t="n">
         <v>5.1</v>
@@ -8735,16 +8735,16 @@
         <v>1.02</v>
       </c>
       <c r="N43" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="O43" t="n">
         <v>1.12</v>
       </c>
       <c r="P43" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R43" t="n">
         <v>1.99</v>
@@ -8756,13 +8756,13 @@
         <v>1.53</v>
       </c>
       <c r="U43" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="V43" t="n">
         <v>1.2</v>
       </c>
       <c r="W43" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X43" t="n">
         <v>38</v>
@@ -8774,10 +8774,10 @@
         <v>60</v>
       </c>
       <c r="AA43" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AB43" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC43" t="n">
         <v>13</v>
@@ -8795,13 +8795,13 @@
         <v>10.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI43" t="n">
         <v>46</v>
       </c>
       <c r="AJ43" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK43" t="n">
         <v>13</v>
@@ -8813,7 +8813,7 @@
         <v>55</v>
       </c>
       <c r="AN43" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AO43" t="n">
         <v>40</v>
@@ -8828,7 +8828,7 @@
         <v>50</v>
       </c>
       <c r="AS43" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AT43" t="n">
         <v>16</v>
@@ -8855,26 +8855,26 @@
         <v>42</v>
       </c>
       <c r="BB43" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC43" t="n">
         <v>12.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE43" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF43" t="n">
         <v>4.5</v>
       </c>
       <c r="BG43" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -8905,22 +8905,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="G44" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="H44" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I44" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J44" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K44" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L44" t="n">
         <v>1.28</v>
@@ -8938,52 +8938,52 @@
         <v>2.76</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R44" t="n">
         <v>1.72</v>
       </c>
       <c r="S44" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T44" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U44" t="n">
         <v>2.66</v>
       </c>
       <c r="V44" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W44" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="X44" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y44" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z44" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA44" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB44" t="n">
         <v>14.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE44" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF44" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG44" t="n">
         <v>10.5</v>
@@ -8992,10 +8992,10 @@
         <v>15.5</v>
       </c>
       <c r="AI44" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK44" t="n">
         <v>16</v>
@@ -9007,49 +9007,49 @@
         <v>55</v>
       </c>
       <c r="AN44" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO44" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP44" t="n">
         <v>24</v>
       </c>
       <c r="AQ44" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR44" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AS44" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AT44" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU44" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV44" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW44" t="n">
         <v>42</v>
       </c>
       <c r="AX44" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY44" t="n">
         <v>10</v>
       </c>
       <c r="AZ44" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB44" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC44" t="n">
         <v>15.5</v>
@@ -9064,11 +9064,11 @@
         <v>6.6</v>
       </c>
       <c r="BG44" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -9099,16 +9099,16 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.56</v>
+        <v>2.94</v>
       </c>
       <c r="G45" t="n">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="H45" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="I45" t="n">
-        <v>2.98</v>
+        <v>2.58</v>
       </c>
       <c r="J45" t="n">
         <v>3.35</v>
@@ -9123,146 +9123,146 @@
         <v>1.06</v>
       </c>
       <c r="N45" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O45" t="n">
         <v>1.27</v>
       </c>
       <c r="P45" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R45" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U45" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V45" t="n">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="W45" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="X45" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z45" t="n">
         <v>20</v>
       </c>
-      <c r="Y45" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>24</v>
-      </c>
       <c r="AA45" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AB45" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE45" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AF45" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AG45" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AH45" t="n">
         <v>19.5</v>
       </c>
       <c r="AI45" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ45" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AK45" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AL45" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM45" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN45" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AO45" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AP45" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ45" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR45" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AS45" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AT45" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AU45" t="n">
         <v>6.2</v>
       </c>
       <c r="AV45" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AW45" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AX45" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AY45" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AZ45" t="n">
         <v>11.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BB45" t="n">
         <v>4</v>
       </c>
       <c r="BC45" t="n">
-        <v>20</v>
+        <v>3.85</v>
       </c>
       <c r="BD45" t="n">
         <v>3.95</v>
       </c>
       <c r="BE45" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BF45" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BG45" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -9299,13 +9299,13 @@
         <v>1.7</v>
       </c>
       <c r="H46" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="I46" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J46" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K46" t="n">
         <v>4.5</v>
@@ -9317,31 +9317,31 @@
         <v>1.06</v>
       </c>
       <c r="N46" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O46" t="n">
         <v>1.3</v>
       </c>
       <c r="P46" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R46" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S46" t="n">
         <v>3.2</v>
       </c>
       <c r="T46" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U46" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="V46" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W46" t="n">
         <v>2.42</v>
@@ -9350,7 +9350,7 @@
         <v>19.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z46" t="n">
         <v>60</v>
@@ -9359,7 +9359,7 @@
         <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC46" t="n">
         <v>10</v>
@@ -9377,7 +9377,7 @@
         <v>11</v>
       </c>
       <c r="AH46" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI46" t="n">
         <v>1000</v>
@@ -9386,7 +9386,7 @@
         <v>18</v>
       </c>
       <c r="AK46" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL46" t="n">
         <v>38</v>
@@ -9401,16 +9401,16 @@
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>5.4</v>
+        <v>14</v>
       </c>
       <c r="AQ46" t="n">
         <v>16</v>
       </c>
       <c r="AR46" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AS46" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT46" t="n">
         <v>7.6</v>
@@ -9422,7 +9422,7 @@
         <v>18.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX46" t="n">
         <v>8.800000000000001</v>
@@ -9434,7 +9434,7 @@
         <v>17.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB46" t="n">
         <v>14.5</v>
@@ -9443,20 +9443,20 @@
         <v>15</v>
       </c>
       <c r="BD46" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE46" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF46" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG46" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
         <v>1.2</v>
       </c>
       <c r="G47" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H47" t="n">
         <v>7.6</v>
@@ -9538,7 +9538,7 @@
         <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-08 04:38:00</t>
+          <t>2026-04-08 06:48:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BH4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Platense FC</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Genesis Huracan</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>1.93</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>1.98</v>
       </c>
       <c r="H2" t="n">
-        <v>1.25</v>
+        <v>6.6</v>
       </c>
       <c r="I2" t="n">
-        <v>1.27</v>
+        <v>6.8</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="K2" t="n">
-        <v>8.6</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="N2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P2" t="n">
         <v>1.25</v>
       </c>
-      <c r="O2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Q2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="S2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>400</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>370</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>280</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>270</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV2" t="n">
         <v>36</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="S2" t="n">
-        <v>100</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V2" t="n">
-        <v>5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>350</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>29</v>
-      </c>
       <c r="AW2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>55</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>320</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>44</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>180</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF2" t="n">
         <v>42</v>
       </c>
-      <c r="AX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG2" t="n">
-        <v>95</v>
+        <v>370</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Westchester SC</t>
+          <t>CD Olimpia</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sarasota Paradise</t>
+          <t>CD Victoria</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.58</v>
+        <v>1.14</v>
       </c>
       <c r="G3" t="n">
-        <v>2.92</v>
+        <v>1.18</v>
       </c>
       <c r="H3" t="n">
-        <v>2.62</v>
+        <v>22</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="L3" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="P3" t="n">
-        <v>2.16</v>
+        <v>2.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="S3" t="n">
-        <v>2.92</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.68</v>
+        <v>2.44</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5</v>
+        <v>1.03</v>
       </c>
       <c r="W3" t="n">
-        <v>1.52</v>
+        <v>6.4</v>
       </c>
       <c r="X3" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>20</v>
       </c>
-      <c r="Y3" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AR3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS3" t="n">
         <v>10</v>
       </c>
-      <c r="AD3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ3" t="n">
+      <c r="AT3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC3" t="n">
         <v>12</v>
       </c>
-      <c r="AR3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>23</v>
-      </c>
       <c r="BD3" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.9</v>
+        <v>2.32</v>
       </c>
       <c r="BF3" t="n">
-        <v>16</v>
+        <v>2.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>16</v>
+        <v>2.32</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,572 +1131,184 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Orange County Blues</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>San Antonio FC</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.62</v>
+        <v>2.68</v>
       </c>
       <c r="G4" t="n">
-        <v>1.65</v>
+        <v>2.84</v>
       </c>
       <c r="H4" t="n">
-        <v>5.9</v>
+        <v>3.1</v>
       </c>
       <c r="I4" t="n">
-        <v>6.4</v>
+        <v>3.25</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>1.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.89</v>
+        <v>2.44</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="U4" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="V4" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>2.5</v>
+        <v>1.54</v>
       </c>
       <c r="X4" t="n">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="Z4" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>210</v>
+        <v>60</v>
       </c>
       <c r="AB4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP4" t="n">
         <v>8.6</v>
       </c>
-      <c r="AC4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>18.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>16</v>
+        <v>9.4</v>
       </c>
       <c r="AT4" t="n">
         <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="AW4" t="n">
         <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>8.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>14.5</v>
+        <v>9.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>14.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC4" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>30</v>
+        <v>9.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-08 20:04:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Honduras Liga Nacional</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CD Olimpia</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CD Victoria</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="H5" t="n">
-        <v>18</v>
-      </c>
-      <c r="I5" t="n">
-        <v>29</v>
-      </c>
-      <c r="J5" t="n">
-        <v>9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>40</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2026-04-08 20:04:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>US United Soccer League</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>23:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Orange County Blues</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>San Antonio FC</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>2026-04-08 20:04:15</t>
+          <t>2026-04-08 22:19:56</t>
         </is>
       </c>
     </row>
